--- a/data/excel_sql/2.-tables_db.xlsx
+++ b/data/excel_sql/2.-tables_db.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IPPI 11\Documents\GitHub\REDIM_1\data\excel_sql\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\GitHub\REDIM_1\data\excel_sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56BED94-61B1-436C-9278-98BFF62C467E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168E3940-4A56-42B1-9486-A3B44C07EBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YEARS" sheetId="8" r:id="rId1"/>
@@ -19,20 +19,28 @@
     <sheet name="CATEGORIES" sheetId="14" r:id="rId4"/>
     <sheet name="CENTERS" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="957">
   <si>
     <t>Aborto</t>
   </si>
@@ -2060,6 +2068,849 @@
   </si>
   <si>
     <t>Tráfico de indocumentados</t>
+  </si>
+  <si>
+    <t>Trata de personas</t>
+  </si>
+  <si>
+    <t>Trata de personas - No especificado</t>
+  </si>
+  <si>
+    <t>Trata de personas - No identificado</t>
+  </si>
+  <si>
+    <t>Trata de personas - Trata de personas con otros fines</t>
+  </si>
+  <si>
+    <t>Trata de personas con otros fines</t>
+  </si>
+  <si>
+    <t>Trata de personas con otros fines de explotación</t>
+  </si>
+  <si>
+    <t>Trata de personas - Trata de personas con fines de explotación sexual</t>
+  </si>
+  <si>
+    <t>Trata de personas con fines de explotación sexual</t>
+  </si>
+  <si>
+    <t>Trata de personas - Trata de personas con fines de trabajo o servicios forzados</t>
+  </si>
+  <si>
+    <t>Trata de personas con fines de trabajo o servicios forzados</t>
+  </si>
+  <si>
+    <t>Trata de personas - Trata de personas con fines de tráfico de órganos</t>
+  </si>
+  <si>
+    <t>Trata de personas con fines de tráfico de órganos</t>
+  </si>
+  <si>
+    <t>Allanamiento de morada</t>
+  </si>
+  <si>
+    <t>Amenazas</t>
+  </si>
+  <si>
+    <t>Asociación delictuosa</t>
+  </si>
+  <si>
+    <t>Armas y objetos prohibidos</t>
+  </si>
+  <si>
+    <t>Delitos en materia de armas de fuego, explosivos y otros materiales destructivos</t>
+  </si>
+  <si>
+    <t>Delitos en materia de armas y objetos prohibidos</t>
+  </si>
+  <si>
+    <t> Delitos en materia de armas, explosivos y otros materiales destructivos</t>
+  </si>
+  <si>
+    <t> Delitos en materia de armas, explosivos y otros materiales destructivos - No especificado</t>
+  </si>
+  <si>
+    <t>Delitos en materia de armas, explosivos y otros materiales destructivos - No identificado</t>
+  </si>
+  <si>
+    <t>Delitos en materia de armas, explosivos y otros materiales destructivos - Otros delitos en materia de armas, explosivos y otros materiales destructivos</t>
+  </si>
+  <si>
+    <t>Delitos previstos en la Ley Federal de Armas de Fuego y Explosivos</t>
+  </si>
+  <si>
+    <t>Delitos Previstos en la Ley Federal de Armas de Fuego y Explosivos</t>
+  </si>
+  <si>
+    <t>Ley Federal de Armas de Fuego y Explosivos</t>
+  </si>
+  <si>
+    <t>Otros delitos en materia de armas, explosivos y otros materiales destructivos</t>
+  </si>
+  <si>
+    <t>Acopio ilícito de armas</t>
+  </si>
+  <si>
+    <t> Delitos en materia de armas, explosivos y otros materiales destructivos - Acopio ilícito de armas</t>
+  </si>
+  <si>
+    <t> Delitos en materia de armas, explosivos y otros materiales destructivos - Portación ilícita de armas</t>
+  </si>
+  <si>
+    <t>Delitos en materia de armas, explosivos y otros materiales destructivos - Posesión ilícita de armas, cartuchos y cargadores</t>
+  </si>
+  <si>
+    <t>Portación ilícita de armas</t>
+  </si>
+  <si>
+    <t>Posesión ilícita de armas, cartuchos y cargadores</t>
+  </si>
+  <si>
+    <t>Otros delitos que privan de la vida</t>
+  </si>
+  <si>
+    <t>Privación de la libertad</t>
+  </si>
+  <si>
+    <t>Privación Ilegal de la Libertad y de otras Garantías</t>
+  </si>
+  <si>
+    <t>Corrupción de menores</t>
+  </si>
+  <si>
+    <t>Corrupción de menores e incapaces</t>
+  </si>
+  <si>
+    <t>Corrupción de menores incapaces</t>
+  </si>
+  <si>
+    <t>Delitos contra el libre desarrollo de la personalidad - Corrupción de menores e incapaces</t>
+  </si>
+  <si>
+    <t>Delitos en materia de instituciones de crédito, inversión, fianzas y seguros</t>
+  </si>
+  <si>
+    <t>Delitos en materia de Instituciones de crédito, inversión, fianzas y seguros</t>
+  </si>
+  <si>
+    <t>Delitos Previstos en las Leyes en materia de delitos bancarios y financieros</t>
+  </si>
+  <si>
+    <t>Legislación de Instituciones de Crédito, Inversión, Fianzas y Seguros</t>
+  </si>
+  <si>
+    <t>Contra el Libre Desarrollo de la Personalidad</t>
+  </si>
+  <si>
+    <t>Contra el libre desarrollo de la personalidad - No especificado</t>
+  </si>
+  <si>
+    <t>Delitos contra el libre desarrollo de la personalidad</t>
+  </si>
+  <si>
+    <t>Delitos Contra el libre desarrollo de la personalidad</t>
+  </si>
+  <si>
+    <t>Delitos contra el libre desarrollo de la personalidad - No especificado</t>
+  </si>
+  <si>
+    <t>Delitos contra el libre desarrollo de la personalidad - No identificado</t>
+  </si>
+  <si>
+    <t>Delitos contra el libre desarrollo de la personalidad - Otros delitos contra el libre desarrollo de la personalidad</t>
+  </si>
+  <si>
+    <t>La libertad personal</t>
+  </si>
+  <si>
+    <t>Otros delitos contra el libre desarrollo de la personalidad</t>
+  </si>
+  <si>
+    <t>Otros delitos contra la libertad personal</t>
+  </si>
+  <si>
+    <t>Otros delitos que atentan contra la libertad personal</t>
+  </si>
+  <si>
+    <t>Otros Delitos que atentan contra la libertad personal</t>
+  </si>
+  <si>
+    <t>Otros delitos que atentan contra la libertad personal con fines de lucro</t>
+  </si>
+  <si>
+    <t>Otros delitos que atentan contra la libertad personal sin fines de lucro</t>
+  </si>
+  <si>
+    <t>Contra de las Personas en su Patrimonio</t>
+  </si>
+  <si>
+    <t>Daño a la propiedad</t>
+  </si>
+  <si>
+    <t>Daño en la propiedad</t>
+  </si>
+  <si>
+    <t>Delitos en contra de las personas en su patrimonio</t>
+  </si>
+  <si>
+    <t>Delitos en Contra de las Personas en su Patrimonio</t>
+  </si>
+  <si>
+    <t>El patrimonio</t>
+  </si>
+  <si>
+    <t>Otros delitos contra el patrimonio</t>
+  </si>
+  <si>
+    <t>Otros Delitos contra el patrimonio</t>
+  </si>
+  <si>
+    <t>Otros delitos que atentan contra el patrimonio</t>
+  </si>
+  <si>
+    <t>Otros delitos que atenten contra el patrimonio</t>
+  </si>
+  <si>
+    <t>Cometidos contra la Administración de Justicia</t>
+  </si>
+  <si>
+    <t>Delitos Cometidos contra la administración de justicia</t>
+  </si>
+  <si>
+    <t>Delitos contra la administración de justicia</t>
+  </si>
+  <si>
+    <t>Delitos contra la administración de justicia - En materia de amparo</t>
+  </si>
+  <si>
+    <t>Delitos contra la administración de justicia - No especificado</t>
+  </si>
+  <si>
+    <t>Delitos contra la administración de justicia - No identificado</t>
+  </si>
+  <si>
+    <t>Delitos contra la administración de justicia - Otros delitos contra la administración de justicia</t>
+  </si>
+  <si>
+    <t>Otros delitos contra la administración de justicia</t>
+  </si>
+  <si>
+    <t>Cometidos contra servidores públicos</t>
+  </si>
+  <si>
+    <t>Contra el servicio público - No especificado</t>
+  </si>
+  <si>
+    <t>Contra la Autoridad</t>
+  </si>
+  <si>
+    <t>Delitos contra la autoridad</t>
+  </si>
+  <si>
+    <t>Delitos Contra la Autoridad</t>
+  </si>
+  <si>
+    <t>Acceso ilícito a sistemas o equipos informáticos</t>
+  </si>
+  <si>
+    <t>Daños a datos informáticos</t>
+  </si>
+  <si>
+    <t>Delitos contra la seguridad de los datos y/o sistemas o equipos informáticos</t>
+  </si>
+  <si>
+    <t>Delitos contra la seguridad de los datos y/o sistemas o equipos informáticos - Acceso ilícito a sistemas o equipos informáticos</t>
+  </si>
+  <si>
+    <t>Delitos contra la seguridad de los datos y/o sistemas o equipos informáticos - Daños a datos informáticos</t>
+  </si>
+  <si>
+    <t>Delitos contra la seguridad de los datos y/o sistemas o equipos informáticos - Interferir en el buen funcionamiento de sistemas o equipos informáticos</t>
+  </si>
+  <si>
+    <t>Delitos contra la seguridad de los datos y/o sistemas o equipos informáticos - No especificado</t>
+  </si>
+  <si>
+    <t>Delitos contra la seguridad de los datos y/o sistemas o equipos informáticos - No identificado</t>
+  </si>
+  <si>
+    <t>Delitos contra la seguridad de los datos y/o sistemas o equipos informáticos - Otros delitos contra la seguridad de los datos y/o sistemas o equipos informáticos</t>
+  </si>
+  <si>
+    <t>Delitos contra la seguridad de los sistemas y-o equipos informáticos</t>
+  </si>
+  <si>
+    <t>Interferir en el buen funcionamiento de sistemas o equipos informáticos</t>
+  </si>
+  <si>
+    <t>Otros delitos contra la seguridad de los datos y-o sistemas o equipos informáticos</t>
+  </si>
+  <si>
+    <t>Revelación de secretos y acceso ilícito a sistemas y equipos de informática</t>
+  </si>
+  <si>
+    <t>Contra la Seguridad de la Nación</t>
+  </si>
+  <si>
+    <t>Contra la Seguridad Pública</t>
+  </si>
+  <si>
+    <t>Delitos contra la seguridad de la nación</t>
+  </si>
+  <si>
+    <t>Delitos contra la Seguridad de la Nación</t>
+  </si>
+  <si>
+    <t>Delitos Contra la Seguridad Pública</t>
+  </si>
+  <si>
+    <t>La seguridad pública y la seguridad del Estado</t>
+  </si>
+  <si>
+    <t>Otros delitos contra la seguridad pública</t>
+  </si>
+  <si>
+    <t>Otros delitos contra la seguridad pública y la seguridad del Estado</t>
+  </si>
+  <si>
+    <t>Otros delitos que atentan contra la seguridad pública</t>
+  </si>
+  <si>
+    <t>Otros delitos que atenten contra la Seguridad Pública</t>
+  </si>
+  <si>
+    <t>Contra la Paz y Seguridad de las Personas</t>
+  </si>
+  <si>
+    <t>Contra la Vida y la Integridad Corporal</t>
+  </si>
+  <si>
+    <t>Delitos Contra la Paz y Seguridad de las Personas</t>
+  </si>
+  <si>
+    <t>Delitos contra la vida y la integridad corporal</t>
+  </si>
+  <si>
+    <t>Delitos Contra la Vida y la Integridad Corporal</t>
+  </si>
+  <si>
+    <t>La vida y la integridad corporal</t>
+  </si>
+  <si>
+    <t>Otros delitos que atentan contra la integridad corporal</t>
+  </si>
+  <si>
+    <t>Otros delitos que atentan contra la vida y la integridad corporal</t>
+  </si>
+  <si>
+    <t>Otros Delitos que atentan contra la vida y la integridad corporal</t>
+  </si>
+  <si>
+    <t>Delitos electorales</t>
+  </si>
+  <si>
+    <t>Delitos electorales (Previstos en el Código Penal Federal y en el Código Federal de Instituciones y Procedimientos Electorales)</t>
+  </si>
+  <si>
+    <t>Delitos Electorales y en Materia de Registro Nacional de Ciudadanos</t>
+  </si>
+  <si>
+    <t>Electorales</t>
+  </si>
+  <si>
+    <t>Electorales y en Materia de Registro Nacional de Ciudadanos</t>
+  </si>
+  <si>
+    <t>Ataque a las vías de comunicación</t>
+  </si>
+  <si>
+    <t>Delitos en materia de vías de comunicación y correspondencia</t>
+  </si>
+  <si>
+    <t>Delitos en Materia de Vías de Comunicación y Correspondencia</t>
+  </si>
+  <si>
+    <t>En Materia de Vías de Comunicación y Correspondencia</t>
+  </si>
+  <si>
+    <t>Ley de Vías Generales de Comunicación</t>
+  </si>
+  <si>
+    <t>Código Fiscal de la Federación</t>
+  </si>
+  <si>
+    <t>Delitos en materia fiscal</t>
+  </si>
+  <si>
+    <t>Delitos previstos en el Código Fiscal de la Federación</t>
+  </si>
+  <si>
+    <t>Delitos Previstos en el Código Fiscal de la Federación</t>
+  </si>
+  <si>
+    <t>Despojo</t>
+  </si>
+  <si>
+    <t>Delitos Contra la Dignidad de las Personas (Capítulo Único, Discriminación)</t>
+  </si>
+  <si>
+    <t>Discriminación</t>
+  </si>
+  <si>
+    <t>Evasión de presos</t>
+  </si>
+  <si>
+    <t>Incumplimiento de obligaciones de asistencia familiar</t>
+  </si>
+  <si>
+    <t>Incumplimiento de obligaciones familiares</t>
+  </si>
+  <si>
+    <t>Lesiones culposas</t>
+  </si>
+  <si>
+    <t>Conductas antisociales del fuero federal</t>
+  </si>
+  <si>
+    <t>Conductas antisociales del Fuero Federal</t>
+  </si>
+  <si>
+    <t>Contra el Derecho Internacional</t>
+  </si>
+  <si>
+    <t>Contra la Economía Pública</t>
+  </si>
+  <si>
+    <t>Contra la Humanidad</t>
+  </si>
+  <si>
+    <t>Delitos Contra el Derecho Internacional</t>
+  </si>
+  <si>
+    <t>Delitos Contra el Estado Civil y Bigamia</t>
+  </si>
+  <si>
+    <t>Delitos Contra el Honor</t>
+  </si>
+  <si>
+    <t>Delitos Contra la Economía Pública</t>
+  </si>
+  <si>
+    <t>Delitos Contra la Humanidad</t>
+  </si>
+  <si>
+    <t>Delitos en Materia de Inhumaciones y Exhumaciones</t>
+  </si>
+  <si>
+    <t>Delitos Previstos en la Ley de Concursos Mercantiles</t>
+  </si>
+  <si>
+    <t>Delitos Previstos en la Ley Federal sobre Monumentos y Zonas Arqueológicos, Artísticos e Históricos</t>
+  </si>
+  <si>
+    <t>Delitos previstos en la Ley General de Población</t>
+  </si>
+  <si>
+    <t>Delitos Previstos en la Ley General de Población</t>
+  </si>
+  <si>
+    <t>Delitos Previstos en la Ley sobre Delitos de Imprenta</t>
+  </si>
+  <si>
+    <t>En materia de amparo</t>
+  </si>
+  <si>
+    <t>En Materia de Inhumaciones y Exhumaciones</t>
+  </si>
+  <si>
+    <t>La administración del Estado</t>
+  </si>
+  <si>
+    <t>La familia</t>
+  </si>
+  <si>
+    <t>La sociedad</t>
+  </si>
+  <si>
+    <t>Ley Federal sobre Monumentos y Zonas Arqueológicos, Artísticos e Históricos</t>
+  </si>
+  <si>
+    <t>Ley sobre Delitos de Imprenta</t>
+  </si>
+  <si>
+    <t>Ninguno</t>
+  </si>
+  <si>
+    <t>No especificado delito del fuero común</t>
+  </si>
+  <si>
+    <t>Otros (bienes jurídicos)</t>
+  </si>
+  <si>
+    <t>Otros delitos</t>
+  </si>
+  <si>
+    <t>Otros delitos cometidos contra el servicio público</t>
+  </si>
+  <si>
+    <t>Otros Delitos contenidos en el Código Penal Federal</t>
+  </si>
+  <si>
+    <t>Otros delitos contra la administración del Estado</t>
+  </si>
+  <si>
+    <t>Otros delitos contra la familia</t>
+  </si>
+  <si>
+    <t>Otros Delitos contra la familia</t>
+  </si>
+  <si>
+    <t>Otros delitos contra la sociedad</t>
+  </si>
+  <si>
+    <t>Otros Delitos contra la sociedad</t>
+  </si>
+  <si>
+    <t>Otros delitos del fuero común</t>
+  </si>
+  <si>
+    <t>Otros delitos del Fuero Común</t>
+  </si>
+  <si>
+    <t>Otros Delitos del Fuero Común</t>
+  </si>
+  <si>
+    <t>Responsabilidad Profesional</t>
+  </si>
+  <si>
+    <t>Código de Justicia Militar</t>
+  </si>
+  <si>
+    <t>Cometidos por servidores públicos</t>
+  </si>
+  <si>
+    <t>Cometidos por Servidores Públicos</t>
+  </si>
+  <si>
+    <t>Delitos cometidos por servidores públicos</t>
+  </si>
+  <si>
+    <t>Delitos Cometidos por Servidores Públicos</t>
+  </si>
+  <si>
+    <t>Responsabilidad de servidores públicos</t>
+  </si>
+  <si>
+    <t>Caza, pesca o tala ilegal de flora o fauna silvestres</t>
+  </si>
+  <si>
+    <t>Caza, pesca o tala ilegal de flora o fauna silvestres en peligro de extinción, amenazadas o sujetas a protección</t>
+  </si>
+  <si>
+    <t>Contra el Ambiente y la Gestión Ambiental</t>
+  </si>
+  <si>
+    <t>Contra el medio ambiente y equilibrio ecológico</t>
+  </si>
+  <si>
+    <t>Daños a los ecosistemas o sus elementos</t>
+  </si>
+  <si>
+    <t>Delitos ambientales</t>
+  </si>
+  <si>
+    <t>Delitos ambientales (Previstos en el Código Penal Federal y en la Ley General del Equilibrio Ecológico y la Protección al Ambiente)</t>
+  </si>
+  <si>
+    <t>Delitos Contra el Ambiente y la Gestión Ambiental</t>
+  </si>
+  <si>
+    <t>Delitos contra el medio ambiente, el equilibrio ecológico y la gestión ambiental</t>
+  </si>
+  <si>
+    <t>Delitos contra el medio ambiente, el equilibrio ecológico y la gestión ambiental - Caza, pesca o tala ilegal de flora o fauna silvestres en peligro de extinción, amenazadas o sujetas a protección</t>
+  </si>
+  <si>
+    <t>Delitos contra el medio ambiente, el equilibrio ecológico y la gestión ambiental - Daños a los ecosistemas o sus elementos</t>
+  </si>
+  <si>
+    <t>Delitos contra el medio ambiente, el equilibrio ecológico y la gestión ambiental - No especificado</t>
+  </si>
+  <si>
+    <t>Delitos contra el medio ambiente, el equilibrio ecológico y la gestión ambiental - No identificado</t>
+  </si>
+  <si>
+    <t>Delitos contra el medio ambiente, el equilibrio ecológico y la gestión ambiental - Otros delitos contra el medio ambiente, el equilibrio ecológico y la gestión ambiental</t>
+  </si>
+  <si>
+    <t>Delitos contra el medio ambiente, el equilibrio ecológico y la gestión ambiental - Transporte o manejo de residuos peligrosos</t>
+  </si>
+  <si>
+    <t>Otros delitos contra el medio ambiente, el equilibrio ecológico y la gestión ambiental</t>
+  </si>
+  <si>
+    <t>Transporte o manejo de residuos peligrosos</t>
+  </si>
+  <si>
+    <t>Contra la Salud - No especificado</t>
+  </si>
+  <si>
+    <t>Delitos Contra la Salud</t>
+  </si>
+  <si>
+    <t>Delitos contra la salud en todas sus modalidades (Previstos en el Código Penal Federal y en la Ley General de Salud)</t>
+  </si>
+  <si>
+    <t>Delitos contra la salud no relacionados con narcóticos</t>
+  </si>
+  <si>
+    <t>Delitos en contra de la salud en todas sus modalidades</t>
+  </si>
+  <si>
+    <t>Otros delitos contra la salud</t>
+  </si>
+  <si>
+    <t>Otros delitos previstos en la Ley General de Salud</t>
+  </si>
+  <si>
+    <t>Delitos en materia de migración</t>
+  </si>
+  <si>
+    <t>Delitos en materia de migración - No especificado</t>
+  </si>
+  <si>
+    <t>Delitos en materia de migración - No identificado</t>
+  </si>
+  <si>
+    <t>Delitos en materia de migración - Otros delitos en materia de migración</t>
+  </si>
+  <si>
+    <t>Delitos Previstos en la Ley de Migración</t>
+  </si>
+  <si>
+    <t>Ley de Migración</t>
+  </si>
+  <si>
+    <t>Otros delitos en materia de migración</t>
+  </si>
+  <si>
+    <t>Abuso de autoridad</t>
+  </si>
+  <si>
+    <t>Cohecho</t>
+  </si>
+  <si>
+    <t>Delitos por hechos de corrupción</t>
+  </si>
+  <si>
+    <t>Delitos por hechos de corrupción - Abuso de autoridad</t>
+  </si>
+  <si>
+    <t>Delitos por hechos de corrupción - Cohecho</t>
+  </si>
+  <si>
+    <t>Delitos por hechos de corrupción - Ejercicio abusivo de funciones</t>
+  </si>
+  <si>
+    <t>Delitos por hechos de corrupción - Ejercicio indebido del servicio público</t>
+  </si>
+  <si>
+    <t>Delitos por hechos de corrupción - No especificado</t>
+  </si>
+  <si>
+    <t>Delitos por hechos de corrupción - No identificado</t>
+  </si>
+  <si>
+    <t>Delitos por hechos de corrupción - Otros delitos por hechos de corrupción</t>
+  </si>
+  <si>
+    <t>Delitos por hechos de corrupción - Tráfico de influencias</t>
+  </si>
+  <si>
+    <t>Ejercicio abusivo de funciones</t>
+  </si>
+  <si>
+    <t>Ejercicio indebido del servicio público</t>
+  </si>
+  <si>
+    <t>Otros delitos por hechos de corrupción</t>
+  </si>
+  <si>
+    <t>Tráfico de influencia</t>
+  </si>
+  <si>
+    <t>Tráfico de influencias</t>
+  </si>
+  <si>
+    <t>Homicidio culposo</t>
+  </si>
+  <si>
+    <t>Otros robos</t>
+  </si>
+  <si>
+    <t>Robo</t>
+  </si>
+  <si>
+    <t>Robo - No especificado</t>
+  </si>
+  <si>
+    <t>Robo - No identificado</t>
+  </si>
+  <si>
+    <t>Robo - Otros robos</t>
+  </si>
+  <si>
+    <t>Robo - Robo a casa habitación</t>
+  </si>
+  <si>
+    <t>Robo - Robo a institución bancaria</t>
+  </si>
+  <si>
+    <t>Robo - Robo a negocio</t>
+  </si>
+  <si>
+    <t>Robo - Robo a persona en un lugar privado</t>
+  </si>
+  <si>
+    <t>Robo - Robo a transeúnte en espacio abierto al público</t>
+  </si>
+  <si>
+    <t>Robo - Robo a transeúnte en vía pública</t>
+  </si>
+  <si>
+    <t>Robo - Robo a transportista</t>
+  </si>
+  <si>
+    <t>Robo - Robo de autopartes</t>
+  </si>
+  <si>
+    <t>Robo - Robo de energía eléctrica</t>
+  </si>
+  <si>
+    <t>Robo - Robo de ganado</t>
+  </si>
+  <si>
+    <t>Robo - Robo de maquinaria</t>
+  </si>
+  <si>
+    <t>Robo - Robo en transporte individual</t>
+  </si>
+  <si>
+    <t>Robo - Robo en transporte público colectivo</t>
+  </si>
+  <si>
+    <t>Robo - Robo en transporte público individual</t>
+  </si>
+  <si>
+    <t>Robo - Robo simple</t>
+  </si>
+  <si>
+    <t>Robo a casa habitación</t>
+  </si>
+  <si>
+    <t>Robo a institución bancaria</t>
+  </si>
+  <si>
+    <t>Robo a instituciones bancarias</t>
+  </si>
+  <si>
+    <t>Robo a negocio</t>
+  </si>
+  <si>
+    <t>Robo a persona en un lugar privado</t>
+  </si>
+  <si>
+    <t>Robo a transeúnte</t>
+  </si>
+  <si>
+    <t>Robo a transeúnte en espacio abierto al público</t>
+  </si>
+  <si>
+    <t>Robo a transeúnte en un lugar privado</t>
+  </si>
+  <si>
+    <t>Robo a transeúnte en vía pública</t>
+  </si>
+  <si>
+    <t>Robo a transportista</t>
+  </si>
+  <si>
+    <t>Robo de autopartes</t>
+  </si>
+  <si>
+    <t>Robo de energía eléctrica</t>
+  </si>
+  <si>
+    <t>Robo de ganado</t>
+  </si>
+  <si>
+    <t>Robo de maquinaria</t>
+  </si>
+  <si>
+    <t>Robo de menor</t>
+  </si>
+  <si>
+    <t>Robo en carretera</t>
+  </si>
+  <si>
+    <t>Robo en transporte individual</t>
+  </si>
+  <si>
+    <t>Robo en transporte publico colectivo</t>
+  </si>
+  <si>
+    <t>Robo en transporte público colectivo</t>
+  </si>
+  <si>
+    <t>Robo en transporte publico individual</t>
+  </si>
+  <si>
+    <t>Robo en transporte público individual</t>
+  </si>
+  <si>
+    <t>Robo simple</t>
+  </si>
+  <si>
+    <t>Delitos en materia de hidrocarburos y sus derivados - Posesión ilícita de hidrocarburos y sus derivados</t>
+  </si>
+  <si>
+    <t>Posesión ilícita de hidrocarburos y sus derivados</t>
+  </si>
+  <si>
+    <t>Delitos contra la salud relacionados con narcóticos en su modalidad de narcomenudeo - Posesión simple de narcóticos</t>
+  </si>
+  <si>
+    <t>Delitos federales contra la salud relacionados con narcóticos - Posesión de narcóticos</t>
+  </si>
+  <si>
+    <t>Narcomenudeo en modalidad de posesión simple</t>
+  </si>
+  <si>
+    <t>Posesión de narcóticos</t>
+  </si>
+  <si>
+    <t>Posesión de Narcóticos</t>
+  </si>
+  <si>
+    <t>Posesión simple</t>
+  </si>
+  <si>
+    <t>Posesión simple de narcóticos</t>
+  </si>
+  <si>
+    <t>Retención o sustracción de menores e incapaces</t>
+  </si>
+  <si>
+    <t>Suplantación y usurpación de identidad</t>
+  </si>
+  <si>
+    <t>Violencia de género en todas sus modalidades</t>
+  </si>
+  <si>
+    <t>Violencia de género en todas sus modalidades distinta a la violencia familiar</t>
+  </si>
+  <si>
+    <t>Violencia familiar</t>
   </si>
 </sst>
 </file>
@@ -2103,13 +2954,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2209,10 +3059,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2D779FAC-E2C1-4E1E-A93F-554CB1A16E27}" name="Tabla5" displayName="Tabla5" ref="A1:E145" totalsRowShown="0">
-  <autoFilter ref="A1:E145" xr:uid="{2D779FAC-E2C1-4E1E-A93F-554CB1A16E27}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D49">
-    <sortCondition ref="A1:A49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2D779FAC-E2C1-4E1E-A93F-554CB1A16E27}" name="Tabla5" displayName="Tabla5" ref="A1:E438" totalsRowShown="0">
+  <autoFilter ref="A1:E438" xr:uid="{2D779FAC-E2C1-4E1E-A93F-554CB1A16E27}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E438">
+    <sortCondition ref="A1:A438"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{4C99E144-E72B-4E1E-A1B0-6EE3FE3B2E9B}" name="id"/>
@@ -2510,9 +3360,9 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>483</v>
       </c>
@@ -2523,7 +3373,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2534,7 +3384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2545,7 +3395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2556,7 +3406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2567,7 +3417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2578,7 +3428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2589,7 +3439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2600,7 +3450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2611,7 +3461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2622,7 +3472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2633,7 +3483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2644,7 +3494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2655,7 +3505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2666,7 +3516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2677,7 +3527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2688,7 +3538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2699,7 +3549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2710,7 +3560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2721,7 +3571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2732,7 +3582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2743,7 +3593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2754,7 +3604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2765,7 +3615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2776,7 +3626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2787,7 +3637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2798,7 +3648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2823,13 +3673,13 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="30.5703125" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>483</v>
       </c>
@@ -2849,7 +3699,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2869,7 +3719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2889,7 +3739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2909,7 +3759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2929,7 +3779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2949,7 +3799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2969,7 +3819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2989,7 +3839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3009,7 +3859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3029,7 +3879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3049,7 +3899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3069,7 +3919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3089,7 +3939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3109,7 +3959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3129,7 +3979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3149,7 +3999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3169,7 +4019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3189,7 +4039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3209,7 +4059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3229,7 +4079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3249,7 +4099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3269,7 +4119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3289,7 +4139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3309,7 +4159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3329,7 +4179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3349,7 +4199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3369,7 +4219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3389,7 +4239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3409,7 +4259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3429,7 +4279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3449,7 +4299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3469,7 +4319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3503,12 +4353,12 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>483</v>
       </c>
@@ -3519,7 +4369,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3530,7 +4380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3541,7 +4391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3552,7 +4402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3563,7 +4413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3587,14 +4437,14 @@
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:E145"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E436"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="56.85546875" customWidth="1"/>
+    <col min="2" max="2" width="56.88671875" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>483</v>
       </c>
@@ -3611,7 +4461,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3619,7 +4469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3627,7 +4477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3635,7 +4485,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3643,7 +4493,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3651,7 +4501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3659,7 +4509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3667,7 +4517,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -3675,7 +4525,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10</v>
       </c>
@@ -3683,1087 +4533,3412 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>15</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B14" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>16</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B15" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>17</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B16" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>19</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B17" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>20</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B18" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>22</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B19" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>23</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B20" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>24</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B21" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>27</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>28</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>29</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>30</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>32</v>
+      </c>
+      <c r="B27" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>37</v>
+      </c>
+      <c r="B32" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>40</v>
+      </c>
+      <c r="B35" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37">
         <v>43</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B37" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38">
         <v>44</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B38" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39">
         <v>46</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40">
         <v>47</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B40" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41">
         <v>48</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B41" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42">
         <v>49</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B42" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43">
         <v>50</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B43" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44">
         <v>51</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B44" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45">
         <v>52</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B45" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46">
         <v>53</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B46" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47">
         <v>56</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B47" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48">
         <v>57</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B48" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49">
         <v>58</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B49" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50">
         <v>59</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B50" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51">
         <v>60</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B51" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52">
         <v>63</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53">
         <v>64</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B53" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54">
         <v>65</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B54" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55">
         <v>66</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B55" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56">
         <v>67</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B56" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57">
         <v>68</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B57" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58">
         <v>69</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B58" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59">
         <v>72</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B59" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60">
         <v>73</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B60" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61">
         <v>75</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B61" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C47" s="3"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62">
         <v>77</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B62" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="3"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>78</v>
+      </c>
+      <c r="B63" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>82</v>
+      </c>
+      <c r="B64" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>83</v>
+      </c>
+      <c r="B65" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>84</v>
+      </c>
+      <c r="B66" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>85</v>
+      </c>
+      <c r="B67" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>86</v>
+      </c>
+      <c r="B68" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>87</v>
+      </c>
+      <c r="B69" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>88</v>
+      </c>
+      <c r="B70" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>100</v>
+      </c>
+      <c r="B71" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>102</v>
+      </c>
+      <c r="B72" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>103</v>
+      </c>
+      <c r="B73" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>106</v>
+      </c>
+      <c r="B74" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>107</v>
+      </c>
+      <c r="B75" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>108</v>
+      </c>
+      <c r="B76" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>109</v>
+      </c>
+      <c r="B77" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>110</v>
+      </c>
+      <c r="B78" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>112</v>
+      </c>
+      <c r="B79" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>113</v>
+      </c>
+      <c r="B80" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>114</v>
+      </c>
+      <c r="B81" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>115</v>
+      </c>
+      <c r="B82" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>116</v>
+      </c>
+      <c r="B83" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>117</v>
+      </c>
+      <c r="B84" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>118</v>
+      </c>
+      <c r="B85" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>119</v>
+      </c>
+      <c r="B86" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>121</v>
+      </c>
+      <c r="B87" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>122</v>
+      </c>
+      <c r="B88" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>124</v>
+      </c>
+      <c r="B89" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>125</v>
+      </c>
+      <c r="B90" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>128</v>
+      </c>
+      <c r="B91" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>129</v>
+      </c>
+      <c r="B92" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>130</v>
+      </c>
+      <c r="B93" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>131</v>
+      </c>
+      <c r="B94" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>132</v>
+      </c>
+      <c r="B95" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>133</v>
+      </c>
+      <c r="B96" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>134</v>
+      </c>
+      <c r="B97" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>135</v>
+      </c>
+      <c r="B98" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>136</v>
+      </c>
+      <c r="B99" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>137</v>
+      </c>
+      <c r="B100" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>138</v>
+      </c>
+      <c r="B101" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>139</v>
+      </c>
+      <c r="B102" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>140</v>
+      </c>
+      <c r="B103" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>141</v>
+      </c>
+      <c r="B104" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>142</v>
+      </c>
+      <c r="B105" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>143</v>
+      </c>
+      <c r="B106" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>144</v>
+      </c>
+      <c r="B107" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>145</v>
+      </c>
+      <c r="B108" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>146</v>
+      </c>
+      <c r="B109" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>148</v>
+      </c>
+      <c r="B110" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>149</v>
+      </c>
+      <c r="B111" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>152</v>
+      </c>
+      <c r="B112" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>153</v>
+      </c>
+      <c r="B113" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>154</v>
+      </c>
+      <c r="B114" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>155</v>
+      </c>
+      <c r="B115" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>156</v>
+      </c>
+      <c r="B116" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>157</v>
+      </c>
+      <c r="B117" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>158</v>
+      </c>
+      <c r="B118" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>159</v>
+      </c>
+      <c r="B119" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>160</v>
+      </c>
+      <c r="B120" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>161</v>
+      </c>
+      <c r="B121" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>162</v>
+      </c>
+      <c r="B122" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>163</v>
+      </c>
+      <c r="B123" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>164</v>
+      </c>
+      <c r="B124" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>165</v>
+      </c>
+      <c r="B125" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>166</v>
+      </c>
+      <c r="B126" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>167</v>
+      </c>
+      <c r="B127" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>168</v>
+      </c>
+      <c r="B128" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>169</v>
+      </c>
+      <c r="B129" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>170</v>
+      </c>
+      <c r="B130" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>171</v>
+      </c>
+      <c r="B131" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>172</v>
+      </c>
+      <c r="B132" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>173</v>
+      </c>
+      <c r="B133" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>174</v>
+      </c>
+      <c r="B134" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>175</v>
+      </c>
+      <c r="B135" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>176</v>
+      </c>
+      <c r="B136" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>177</v>
+      </c>
+      <c r="B137" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>178</v>
+      </c>
+      <c r="B138" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>179</v>
+      </c>
+      <c r="B139" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>180</v>
+      </c>
+      <c r="B140" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>181</v>
+      </c>
+      <c r="B141" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>182</v>
+      </c>
+      <c r="B142" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>183</v>
+      </c>
+      <c r="B143" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>184</v>
+      </c>
+      <c r="B144" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>185</v>
+      </c>
+      <c r="B145" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>186</v>
+      </c>
+      <c r="B146" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>187</v>
+      </c>
+      <c r="B147" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>188</v>
+      </c>
+      <c r="B148" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>189</v>
+      </c>
+      <c r="B149" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>190</v>
+      </c>
+      <c r="B150" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>191</v>
+      </c>
+      <c r="B151" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>192</v>
+      </c>
+      <c r="B152" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>193</v>
+      </c>
+      <c r="B153" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>195</v>
+      </c>
+      <c r="B154" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>196</v>
+      </c>
+      <c r="B155" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>197</v>
+      </c>
+      <c r="B156" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>199</v>
+      </c>
+      <c r="B157" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>200</v>
+      </c>
+      <c r="B158" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>205</v>
+      </c>
+      <c r="B159" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>206</v>
+      </c>
+      <c r="B160" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>207</v>
+      </c>
+      <c r="B161" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>208</v>
+      </c>
+      <c r="B162" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>209</v>
+      </c>
+      <c r="B163" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>210</v>
+      </c>
+      <c r="B164" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>211</v>
+      </c>
+      <c r="B165" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>212</v>
+      </c>
+      <c r="B166" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>213</v>
+      </c>
+      <c r="B167" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>214</v>
+      </c>
+      <c r="B168" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>215</v>
+      </c>
+      <c r="B169" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>216</v>
+      </c>
+      <c r="B170" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>217</v>
+      </c>
+      <c r="B171" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>218</v>
+      </c>
+      <c r="B172" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>219</v>
+      </c>
+      <c r="B173" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>220</v>
+      </c>
+      <c r="B174" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175">
         <v>221</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B175" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="3"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>78</v>
-      </c>
-      <c r="B50" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>82</v>
-      </c>
-      <c r="B51" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>83</v>
-      </c>
-      <c r="B52" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>84</v>
-      </c>
-      <c r="B53" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>85</v>
-      </c>
-      <c r="B54" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>86</v>
-      </c>
-      <c r="B55" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>87</v>
-      </c>
-      <c r="B56" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>88</v>
-      </c>
-      <c r="B57" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>100</v>
-      </c>
-      <c r="B58" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>102</v>
-      </c>
-      <c r="B59" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>103</v>
-      </c>
-      <c r="B60" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>106</v>
-      </c>
-      <c r="B61" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>107</v>
-      </c>
-      <c r="B62" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>108</v>
-      </c>
-      <c r="B63" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>109</v>
-      </c>
-      <c r="B64" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>110</v>
-      </c>
-      <c r="B65" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>112</v>
-      </c>
-      <c r="B66" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>113</v>
-      </c>
-      <c r="B67" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>114</v>
-      </c>
-      <c r="B68" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>115</v>
-      </c>
-      <c r="B69" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>116</v>
-      </c>
-      <c r="B70" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>117</v>
-      </c>
-      <c r="B71" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>118</v>
-      </c>
-      <c r="B72" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>119</v>
-      </c>
-      <c r="B73" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>121</v>
-      </c>
-      <c r="B74" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>122</v>
-      </c>
-      <c r="B75" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>124</v>
-      </c>
-      <c r="B76" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>125</v>
-      </c>
-      <c r="B77" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>128</v>
-      </c>
-      <c r="B78" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>129</v>
-      </c>
-      <c r="B79" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>130</v>
-      </c>
-      <c r="B80" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>131</v>
-      </c>
-      <c r="B81" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>132</v>
-      </c>
-      <c r="B82" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>133</v>
-      </c>
-      <c r="B83" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>134</v>
-      </c>
-      <c r="B84" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>135</v>
-      </c>
-      <c r="B85" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>136</v>
-      </c>
-      <c r="B86" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>137</v>
-      </c>
-      <c r="B87" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>138</v>
-      </c>
-      <c r="B88" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>139</v>
-      </c>
-      <c r="B89" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>140</v>
-      </c>
-      <c r="B90" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>141</v>
-      </c>
-      <c r="B91" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>142</v>
-      </c>
-      <c r="B92" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>143</v>
-      </c>
-      <c r="B93" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>144</v>
-      </c>
-      <c r="B94" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>145</v>
-      </c>
-      <c r="B95" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>146</v>
-      </c>
-      <c r="B96" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>148</v>
-      </c>
-      <c r="B97" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>149</v>
-      </c>
-      <c r="B98" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>152</v>
-      </c>
-      <c r="B99" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>153</v>
-      </c>
-      <c r="B100" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>154</v>
-      </c>
-      <c r="B101" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>155</v>
-      </c>
-      <c r="B102" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>156</v>
-      </c>
-      <c r="B103" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>157</v>
-      </c>
-      <c r="B104" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>158</v>
-      </c>
-      <c r="B105" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>159</v>
-      </c>
-      <c r="B106" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>160</v>
-      </c>
-      <c r="B107" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>161</v>
-      </c>
-      <c r="B108" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>162</v>
-      </c>
-      <c r="B109" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>163</v>
-      </c>
-      <c r="B110" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>164</v>
-      </c>
-      <c r="B111" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>165</v>
-      </c>
-      <c r="B112" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>166</v>
-      </c>
-      <c r="B113" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>167</v>
-      </c>
-      <c r="B114" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <v>168</v>
-      </c>
-      <c r="B115" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <v>169</v>
-      </c>
-      <c r="B116" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>170</v>
-      </c>
-      <c r="B117" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <v>171</v>
-      </c>
-      <c r="B118" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <v>172</v>
-      </c>
-      <c r="B119" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120">
-        <v>173</v>
-      </c>
-      <c r="B120" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <v>174</v>
-      </c>
-      <c r="B121" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <v>175</v>
-      </c>
-      <c r="B122" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <v>176</v>
-      </c>
-      <c r="B123" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>177</v>
-      </c>
-      <c r="B124" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>178</v>
-      </c>
-      <c r="B125" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <v>179</v>
-      </c>
-      <c r="B126" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <v>180</v>
-      </c>
-      <c r="B127" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <v>181</v>
-      </c>
-      <c r="B128" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <v>182</v>
-      </c>
-      <c r="B129" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130">
-        <v>183</v>
-      </c>
-      <c r="B130" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <v>184</v>
-      </c>
-      <c r="B131" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <v>185</v>
-      </c>
-      <c r="B132" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <v>186</v>
-      </c>
-      <c r="B133" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134">
-        <v>187</v>
-      </c>
-      <c r="B134" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <v>188</v>
-      </c>
-      <c r="B135" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>189</v>
-      </c>
-      <c r="B136" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>190</v>
-      </c>
-      <c r="B137" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <v>191</v>
-      </c>
-      <c r="B138" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A139">
-        <v>192</v>
-      </c>
-      <c r="B139" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A140">
-        <v>193</v>
-      </c>
-      <c r="B140" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A141">
-        <v>195</v>
-      </c>
-      <c r="B141" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142">
-        <v>196</v>
-      </c>
-      <c r="B142" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143">
-        <v>197</v>
-      </c>
-      <c r="B143" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144">
-        <v>199</v>
-      </c>
-      <c r="B144" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145">
-        <v>200</v>
-      </c>
-      <c r="B145" t="s">
-        <v>675</v>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>225</v>
+      </c>
+      <c r="B176" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>226</v>
+      </c>
+      <c r="B177" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>227</v>
+      </c>
+      <c r="B178" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>228</v>
+      </c>
+      <c r="B179" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>229</v>
+      </c>
+      <c r="B180" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>230</v>
+      </c>
+      <c r="B181" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>231</v>
+      </c>
+      <c r="B182" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>232</v>
+      </c>
+      <c r="B183" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>233</v>
+      </c>
+      <c r="B184" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>234</v>
+      </c>
+      <c r="B185" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>235</v>
+      </c>
+      <c r="B186" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>236</v>
+      </c>
+      <c r="B187" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>237</v>
+      </c>
+      <c r="B188" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>238</v>
+      </c>
+      <c r="B189" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>239</v>
+      </c>
+      <c r="B190" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>240</v>
+      </c>
+      <c r="B191" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>241</v>
+      </c>
+      <c r="B192" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>242</v>
+      </c>
+      <c r="B193" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>243</v>
+      </c>
+      <c r="B194" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>244</v>
+      </c>
+      <c r="B195" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>245</v>
+      </c>
+      <c r="B196" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>246</v>
+      </c>
+      <c r="B197" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>247</v>
+      </c>
+      <c r="B198" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>248</v>
+      </c>
+      <c r="B199" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>249</v>
+      </c>
+      <c r="B200" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>250</v>
+      </c>
+      <c r="B201" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>251</v>
+      </c>
+      <c r="B202" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>252</v>
+      </c>
+      <c r="B203" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>253</v>
+      </c>
+      <c r="B204" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>254</v>
+      </c>
+      <c r="B205" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>255</v>
+      </c>
+      <c r="B206" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>256</v>
+      </c>
+      <c r="B207" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>257</v>
+      </c>
+      <c r="B208" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>258</v>
+      </c>
+      <c r="B209" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>259</v>
+      </c>
+      <c r="B210" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>260</v>
+      </c>
+      <c r="B211" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>261</v>
+      </c>
+      <c r="B212" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>262</v>
+      </c>
+      <c r="B213" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>263</v>
+      </c>
+      <c r="B214" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>264</v>
+      </c>
+      <c r="B215" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>265</v>
+      </c>
+      <c r="B216" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>266</v>
+      </c>
+      <c r="B217" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>267</v>
+      </c>
+      <c r="B218" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>268</v>
+      </c>
+      <c r="B219" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>269</v>
+      </c>
+      <c r="B220" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>270</v>
+      </c>
+      <c r="B221" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>271</v>
+      </c>
+      <c r="B222" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>272</v>
+      </c>
+      <c r="B223" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <v>273</v>
+      </c>
+      <c r="B224" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <v>274</v>
+      </c>
+      <c r="B225" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <v>275</v>
+      </c>
+      <c r="B226" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <v>276</v>
+      </c>
+      <c r="B227" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <v>277</v>
+      </c>
+      <c r="B228" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <v>278</v>
+      </c>
+      <c r="B229" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <v>279</v>
+      </c>
+      <c r="B230" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <v>280</v>
+      </c>
+      <c r="B231" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <v>281</v>
+      </c>
+      <c r="B232" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <v>282</v>
+      </c>
+      <c r="B233" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <v>283</v>
+      </c>
+      <c r="B234" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <v>284</v>
+      </c>
+      <c r="B235" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <v>285</v>
+      </c>
+      <c r="B236" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <v>286</v>
+      </c>
+      <c r="B237" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <v>287</v>
+      </c>
+      <c r="B238" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <v>288</v>
+      </c>
+      <c r="B239" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <v>289</v>
+      </c>
+      <c r="B240" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <v>290</v>
+      </c>
+      <c r="B241" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242">
+        <v>291</v>
+      </c>
+      <c r="B242" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <v>292</v>
+      </c>
+      <c r="B243" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <v>293</v>
+      </c>
+      <c r="B244" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245">
+        <v>294</v>
+      </c>
+      <c r="B245" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246">
+        <v>295</v>
+      </c>
+      <c r="B246" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247">
+        <v>296</v>
+      </c>
+      <c r="B247" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248">
+        <v>297</v>
+      </c>
+      <c r="B248" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249">
+        <v>298</v>
+      </c>
+      <c r="B249" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250">
+        <v>299</v>
+      </c>
+      <c r="B250" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251">
+        <v>300</v>
+      </c>
+      <c r="B251" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252">
+        <v>301</v>
+      </c>
+      <c r="B252" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253">
+        <v>302</v>
+      </c>
+      <c r="B253" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <v>303</v>
+      </c>
+      <c r="B254" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255">
+        <v>304</v>
+      </c>
+      <c r="B255" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256">
+        <v>305</v>
+      </c>
+      <c r="B256" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257">
+        <v>306</v>
+      </c>
+      <c r="B257" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258">
+        <v>307</v>
+      </c>
+      <c r="B258" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259">
+        <v>308</v>
+      </c>
+      <c r="B259" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260">
+        <v>309</v>
+      </c>
+      <c r="B260" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261">
+        <v>310</v>
+      </c>
+      <c r="B261" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262">
+        <v>311</v>
+      </c>
+      <c r="B262" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263">
+        <v>312</v>
+      </c>
+      <c r="B263" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264">
+        <v>313</v>
+      </c>
+      <c r="B264" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265">
+        <v>314</v>
+      </c>
+      <c r="B265" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266">
+        <v>315</v>
+      </c>
+      <c r="B266" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267">
+        <v>316</v>
+      </c>
+      <c r="B267" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268">
+        <v>317</v>
+      </c>
+      <c r="B268" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269">
+        <v>318</v>
+      </c>
+      <c r="B269" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270">
+        <v>319</v>
+      </c>
+      <c r="B270" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271">
+        <v>320</v>
+      </c>
+      <c r="B271" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272">
+        <v>321</v>
+      </c>
+      <c r="B272" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273">
+        <v>322</v>
+      </c>
+      <c r="B273" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274">
+        <v>323</v>
+      </c>
+      <c r="B274" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A275">
+        <v>324</v>
+      </c>
+      <c r="B275" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A276">
+        <v>325</v>
+      </c>
+      <c r="B276" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A277">
+        <v>326</v>
+      </c>
+      <c r="B277" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A278">
+        <v>327</v>
+      </c>
+      <c r="B278" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A279">
+        <v>328</v>
+      </c>
+      <c r="B279" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A280">
+        <v>329</v>
+      </c>
+      <c r="B280" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A281">
+        <v>331</v>
+      </c>
+      <c r="B281" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A282">
+        <v>332</v>
+      </c>
+      <c r="B282" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A283">
+        <v>333</v>
+      </c>
+      <c r="B283" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A284">
+        <v>334</v>
+      </c>
+      <c r="B284" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A285">
+        <v>335</v>
+      </c>
+      <c r="B285" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A286">
+        <v>336</v>
+      </c>
+      <c r="B286" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A287">
+        <v>337</v>
+      </c>
+      <c r="B287" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A288">
+        <v>338</v>
+      </c>
+      <c r="B288" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289">
+        <v>339</v>
+      </c>
+      <c r="B289" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290">
+        <v>340</v>
+      </c>
+      <c r="B290" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291">
+        <v>341</v>
+      </c>
+      <c r="B291" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292">
+        <v>342</v>
+      </c>
+      <c r="B292" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293">
+        <v>343</v>
+      </c>
+      <c r="B293" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294">
+        <v>344</v>
+      </c>
+      <c r="B294" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295">
+        <v>345</v>
+      </c>
+      <c r="B295" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296">
+        <v>346</v>
+      </c>
+      <c r="B296" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297">
+        <v>347</v>
+      </c>
+      <c r="B297" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298">
+        <v>348</v>
+      </c>
+      <c r="B298" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299">
+        <v>349</v>
+      </c>
+      <c r="B299" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300">
+        <v>350</v>
+      </c>
+      <c r="B300" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301">
+        <v>351</v>
+      </c>
+      <c r="B301" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302">
+        <v>352</v>
+      </c>
+      <c r="B302" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A303">
+        <v>353</v>
+      </c>
+      <c r="B303" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304">
+        <v>354</v>
+      </c>
+      <c r="B304" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305">
+        <v>355</v>
+      </c>
+      <c r="B305" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306">
+        <v>356</v>
+      </c>
+      <c r="B306" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307">
+        <v>357</v>
+      </c>
+      <c r="B307" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308">
+        <v>358</v>
+      </c>
+      <c r="B308" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309">
+        <v>359</v>
+      </c>
+      <c r="B309" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310">
+        <v>360</v>
+      </c>
+      <c r="B310" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311">
+        <v>361</v>
+      </c>
+      <c r="B311" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312">
+        <v>362</v>
+      </c>
+      <c r="B312" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313">
+        <v>363</v>
+      </c>
+      <c r="B313" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314">
+        <v>364</v>
+      </c>
+      <c r="B314" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315">
+        <v>365</v>
+      </c>
+      <c r="B315" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316">
+        <v>366</v>
+      </c>
+      <c r="B316" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317">
+        <v>367</v>
+      </c>
+      <c r="B317" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318">
+        <v>368</v>
+      </c>
+      <c r="B318" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319">
+        <v>369</v>
+      </c>
+      <c r="B319" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320">
+        <v>370</v>
+      </c>
+      <c r="B320" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321">
+        <v>371</v>
+      </c>
+      <c r="B321" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322">
+        <v>372</v>
+      </c>
+      <c r="B322" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323">
+        <v>373</v>
+      </c>
+      <c r="B323" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324">
+        <v>374</v>
+      </c>
+      <c r="B324" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325">
+        <v>375</v>
+      </c>
+      <c r="B325" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326">
+        <v>376</v>
+      </c>
+      <c r="B326" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327">
+        <v>377</v>
+      </c>
+      <c r="B327" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328">
+        <v>378</v>
+      </c>
+      <c r="B328" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329">
+        <v>379</v>
+      </c>
+      <c r="B329" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330">
+        <v>380</v>
+      </c>
+      <c r="B330" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331">
+        <v>381</v>
+      </c>
+      <c r="B331" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332">
+        <v>382</v>
+      </c>
+      <c r="B332" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333">
+        <v>383</v>
+      </c>
+      <c r="B333" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334">
+        <v>384</v>
+      </c>
+      <c r="B334" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335">
+        <v>385</v>
+      </c>
+      <c r="B335" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336">
+        <v>386</v>
+      </c>
+      <c r="B336" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337">
+        <v>387</v>
+      </c>
+      <c r="B337" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338">
+        <v>388</v>
+      </c>
+      <c r="B338" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A339">
+        <v>389</v>
+      </c>
+      <c r="B339" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A340">
+        <v>390</v>
+      </c>
+      <c r="B340" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A341">
+        <v>391</v>
+      </c>
+      <c r="B341" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342">
+        <v>392</v>
+      </c>
+      <c r="B342" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343">
+        <v>393</v>
+      </c>
+      <c r="B343" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344">
+        <v>394</v>
+      </c>
+      <c r="B344" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345">
+        <v>395</v>
+      </c>
+      <c r="B345" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346">
+        <v>396</v>
+      </c>
+      <c r="B346" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347">
+        <v>397</v>
+      </c>
+      <c r="B347" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348">
+        <v>398</v>
+      </c>
+      <c r="B348" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A349">
+        <v>399</v>
+      </c>
+      <c r="B349" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A350">
+        <v>400</v>
+      </c>
+      <c r="B350" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A351">
+        <v>401</v>
+      </c>
+      <c r="B351" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A352">
+        <v>402</v>
+      </c>
+      <c r="B352" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A353">
+        <v>403</v>
+      </c>
+      <c r="B353" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A354">
+        <v>404</v>
+      </c>
+      <c r="B354" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A355">
+        <v>405</v>
+      </c>
+      <c r="B355" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A356">
+        <v>406</v>
+      </c>
+      <c r="B356" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A357">
+        <v>407</v>
+      </c>
+      <c r="B357" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A358">
+        <v>408</v>
+      </c>
+      <c r="B358" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A359">
+        <v>409</v>
+      </c>
+      <c r="B359" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A360">
+        <v>410</v>
+      </c>
+      <c r="B360" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A361">
+        <v>411</v>
+      </c>
+      <c r="B361" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A362">
+        <v>412</v>
+      </c>
+      <c r="B362" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A363">
+        <v>413</v>
+      </c>
+      <c r="B363" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A364">
+        <v>414</v>
+      </c>
+      <c r="B364" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A365">
+        <v>415</v>
+      </c>
+      <c r="B365" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A366">
+        <v>416</v>
+      </c>
+      <c r="B366" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A367">
+        <v>417</v>
+      </c>
+      <c r="B367" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A368">
+        <v>418</v>
+      </c>
+      <c r="B368" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A369">
+        <v>419</v>
+      </c>
+      <c r="B369" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A370">
+        <v>420</v>
+      </c>
+      <c r="B370" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A371">
+        <v>421</v>
+      </c>
+      <c r="B371" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A372">
+        <v>422</v>
+      </c>
+      <c r="B372" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A373">
+        <v>423</v>
+      </c>
+      <c r="B373" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A374">
+        <v>424</v>
+      </c>
+      <c r="B374" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A375">
+        <v>425</v>
+      </c>
+      <c r="B375" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A376">
+        <v>426</v>
+      </c>
+      <c r="B376" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A377">
+        <v>427</v>
+      </c>
+      <c r="B377" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A378">
+        <v>429</v>
+      </c>
+      <c r="B378" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A379">
+        <v>430</v>
+      </c>
+      <c r="B379" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A380">
+        <v>431</v>
+      </c>
+      <c r="B380" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A381">
+        <v>432</v>
+      </c>
+      <c r="B381" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A382">
+        <v>433</v>
+      </c>
+      <c r="B382" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A383">
+        <v>434</v>
+      </c>
+      <c r="B383" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A384">
+        <v>435</v>
+      </c>
+      <c r="B384" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A385">
+        <v>436</v>
+      </c>
+      <c r="B385" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A386">
+        <v>437</v>
+      </c>
+      <c r="B386" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A387">
+        <v>438</v>
+      </c>
+      <c r="B387" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A388">
+        <v>439</v>
+      </c>
+      <c r="B388" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A389">
+        <v>440</v>
+      </c>
+      <c r="B389" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A390">
+        <v>441</v>
+      </c>
+      <c r="B390" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A391">
+        <v>442</v>
+      </c>
+      <c r="B391" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A392">
+        <v>443</v>
+      </c>
+      <c r="B392" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A393">
+        <v>444</v>
+      </c>
+      <c r="B393" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A394">
+        <v>445</v>
+      </c>
+      <c r="B394" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A395">
+        <v>446</v>
+      </c>
+      <c r="B395" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A396">
+        <v>447</v>
+      </c>
+      <c r="B396" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A397">
+        <v>448</v>
+      </c>
+      <c r="B397" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A398">
+        <v>449</v>
+      </c>
+      <c r="B398" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A399">
+        <v>450</v>
+      </c>
+      <c r="B399" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A400">
+        <v>451</v>
+      </c>
+      <c r="B400" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A401">
+        <v>452</v>
+      </c>
+      <c r="B401" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A402">
+        <v>453</v>
+      </c>
+      <c r="B402" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A403">
+        <v>454</v>
+      </c>
+      <c r="B403" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A404">
+        <v>455</v>
+      </c>
+      <c r="B404" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A405">
+        <v>456</v>
+      </c>
+      <c r="B405" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A406">
+        <v>457</v>
+      </c>
+      <c r="B406" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A407">
+        <v>458</v>
+      </c>
+      <c r="B407" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A408">
+        <v>459</v>
+      </c>
+      <c r="B408" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A409">
+        <v>460</v>
+      </c>
+      <c r="B409" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A410">
+        <v>461</v>
+      </c>
+      <c r="B410" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A411">
+        <v>462</v>
+      </c>
+      <c r="B411" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A412">
+        <v>463</v>
+      </c>
+      <c r="B412" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A413">
+        <v>464</v>
+      </c>
+      <c r="B413" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A414">
+        <v>465</v>
+      </c>
+      <c r="B414" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A415">
+        <v>466</v>
+      </c>
+      <c r="B415" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A416">
+        <v>467</v>
+      </c>
+      <c r="B416" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A417">
+        <v>468</v>
+      </c>
+      <c r="B417" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A418">
+        <v>469</v>
+      </c>
+      <c r="B418" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A419">
+        <v>470</v>
+      </c>
+      <c r="B419" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A420">
+        <v>471</v>
+      </c>
+      <c r="B420" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A421">
+        <v>472</v>
+      </c>
+      <c r="B421" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A422">
+        <v>473</v>
+      </c>
+      <c r="B422" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A423">
+        <v>474</v>
+      </c>
+      <c r="B423" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A424">
+        <v>475</v>
+      </c>
+      <c r="B424" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A425">
+        <v>476</v>
+      </c>
+      <c r="B425" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A426">
+        <v>477</v>
+      </c>
+      <c r="B426" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A427">
+        <v>478</v>
+      </c>
+      <c r="B427" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A428">
+        <v>479</v>
+      </c>
+      <c r="B428" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A429">
+        <v>480</v>
+      </c>
+      <c r="B429" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A430">
+        <v>481</v>
+      </c>
+      <c r="B430" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A431">
+        <v>482</v>
+      </c>
+      <c r="B431" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A432">
+        <v>483</v>
+      </c>
+      <c r="B432" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A433">
+        <v>484</v>
+      </c>
+      <c r="B433" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A434">
+        <v>485</v>
+      </c>
+      <c r="B434" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A435">
+        <v>486</v>
+      </c>
+      <c r="B435" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A436">
+        <v>487</v>
+      </c>
+      <c r="B436" t="s">
+        <v>956</v>
       </c>
     </row>
   </sheetData>
@@ -4778,14 +7953,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040BF47F-E9DD-47FE-8A77-28B9CE7118A4}">
   <dimension ref="B1:E421"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="80.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" customWidth="1"/>
+    <col min="3" max="3" width="80.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>33</v>
       </c>
@@ -4799,7 +7974,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>288</v>
       </c>
@@ -4811,7 +7986,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>282</v>
       </c>
@@ -4823,7 +7998,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>318</v>
       </c>
@@ -4835,7 +8010,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>288</v>
       </c>
@@ -4847,7 +8022,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>231</v>
       </c>
@@ -4859,7 +8034,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>288</v>
       </c>
@@ -4871,7 +8046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>318</v>
       </c>
@@ -4883,7 +8058,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>318</v>
       </c>
@@ -4895,7 +8070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>318</v>
       </c>
@@ -4907,7 +8082,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>318</v>
       </c>
@@ -4919,7 +8094,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>318</v>
       </c>
@@ -4931,7 +8106,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>318</v>
       </c>
@@ -4943,7 +8118,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>318</v>
       </c>
@@ -4955,7 +8130,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>180</v>
       </c>
@@ -4967,7 +8142,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>152</v>
       </c>
@@ -4979,7 +8154,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>231</v>
       </c>
@@ -4991,7 +8166,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>115</v>
       </c>
@@ -5003,7 +8178,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>115</v>
       </c>
@@ -5015,7 +8190,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>282</v>
       </c>
@@ -5027,7 +8202,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>264</v>
       </c>
@@ -5039,7 +8214,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>330</v>
       </c>
@@ -5051,7 +8226,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>330</v>
       </c>
@@ -5063,7 +8238,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>335</v>
       </c>
@@ -5075,7 +8250,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>71</v>
       </c>
@@ -5087,7 +8262,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>71</v>
       </c>
@@ -5099,7 +8274,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>61</v>
       </c>
@@ -5111,7 +8286,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>71</v>
       </c>
@@ -5123,7 +8298,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>71</v>
       </c>
@@ -5135,7 +8310,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>86</v>
       </c>
@@ -5147,7 +8322,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>86</v>
       </c>
@@ -5159,7 +8334,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>67</v>
       </c>
@@ -5171,7 +8346,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>139</v>
       </c>
@@ -5183,7 +8358,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>166</v>
       </c>
@@ -5195,7 +8370,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>52</v>
       </c>
@@ -5207,7 +8382,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>52</v>
       </c>
@@ -5219,7 +8394,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>195</v>
       </c>
@@ -5231,7 +8406,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>52</v>
       </c>
@@ -5243,7 +8418,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>238</v>
       </c>
@@ -5255,7 +8430,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>243</v>
       </c>
@@ -5267,7 +8442,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>360</v>
       </c>
@@ -5279,7 +8454,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>243</v>
       </c>
@@ -5291,7 +8466,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>180</v>
       </c>
@@ -5303,7 +8478,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>152</v>
       </c>
@@ -5315,7 +8490,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>335</v>
       </c>
@@ -5327,7 +8502,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>166</v>
       </c>
@@ -5339,7 +8514,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>335</v>
       </c>
@@ -5351,7 +8526,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>166</v>
       </c>
@@ -5363,7 +8538,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>330</v>
       </c>
@@ -5375,7 +8550,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>231</v>
       </c>
@@ -5387,7 +8562,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>152</v>
       </c>
@@ -5399,7 +8574,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>238</v>
       </c>
@@ -5411,7 +8586,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>335</v>
       </c>
@@ -5423,7 +8598,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>152</v>
       </c>
@@ -5435,7 +8610,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>152</v>
       </c>
@@ -5447,7 +8622,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>335</v>
       </c>
@@ -5459,7 +8634,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
         <v>335</v>
       </c>
@@ -5471,7 +8646,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>152</v>
       </c>
@@ -5483,7 +8658,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>270</v>
       </c>
@@ -5495,7 +8670,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>308</v>
       </c>
@@ -5507,7 +8682,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>270</v>
       </c>
@@ -5519,7 +8694,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>80</v>
       </c>
@@ -5531,7 +8706,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>308</v>
       </c>
@@ -5543,7 +8718,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>270</v>
       </c>
@@ -5555,7 +8730,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>308</v>
       </c>
@@ -5567,7 +8742,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>308</v>
       </c>
@@ -5579,7 +8754,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>80</v>
       </c>
@@ -5591,7 +8766,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>355</v>
       </c>
@@ -5603,7 +8778,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>308</v>
       </c>
@@ -5615,7 +8790,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>355</v>
       </c>
@@ -5627,7 +8802,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>308</v>
       </c>
@@ -5639,7 +8814,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>355</v>
       </c>
@@ -5651,7 +8826,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>260</v>
       </c>
@@ -5663,7 +8838,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>260</v>
       </c>
@@ -5675,7 +8850,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>260</v>
       </c>
@@ -5687,7 +8862,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>260</v>
       </c>
@@ -5699,7 +8874,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>260</v>
       </c>
@@ -5711,7 +8886,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>260</v>
       </c>
@@ -5723,7 +8898,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>260</v>
       </c>
@@ -5735,7 +8910,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
         <v>260</v>
       </c>
@@ -5747,7 +8922,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
         <v>260</v>
       </c>
@@ -5759,7 +8934,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
         <v>260</v>
       </c>
@@ -5771,7 +8946,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
         <v>260</v>
       </c>
@@ -5783,7 +8958,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
         <v>260</v>
       </c>
@@ -5795,7 +8970,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
         <v>260</v>
       </c>
@@ -5807,7 +8982,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
         <v>218</v>
       </c>
@@ -5819,7 +8994,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
         <v>218</v>
       </c>
@@ -5831,7 +9006,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
         <v>218</v>
       </c>
@@ -5843,7 +9018,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
         <v>103</v>
       </c>
@@ -5855,7 +9030,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90" t="s">
         <v>103</v>
       </c>
@@ -5867,7 +9042,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
         <v>103</v>
       </c>
@@ -5879,7 +9054,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
         <v>103</v>
       </c>
@@ -5891,7 +9066,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
         <v>103</v>
       </c>
@@ -5903,7 +9078,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
         <v>103</v>
       </c>
@@ -5915,7 +9090,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
         <v>103</v>
       </c>
@@ -5927,7 +9102,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
         <v>103</v>
       </c>
@@ -5939,7 +9114,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>103</v>
       </c>
@@ -5951,7 +9126,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>243</v>
       </c>
@@ -5963,7 +9138,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>231</v>
       </c>
@@ -5975,7 +9150,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>330</v>
       </c>
@@ -5987,7 +9162,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>238</v>
       </c>
@@ -5999,7 +9174,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>103</v>
       </c>
@@ -6011,7 +9186,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>103</v>
       </c>
@@ -6023,7 +9198,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>166</v>
       </c>
@@ -6035,7 +9210,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>335</v>
       </c>
@@ -6047,7 +9222,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>166</v>
       </c>
@@ -6059,7 +9234,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>152</v>
       </c>
@@ -6071,7 +9246,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>166</v>
       </c>
@@ -6083,7 +9258,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>166</v>
       </c>
@@ -6095,7 +9270,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
         <v>335</v>
       </c>
@@ -6107,7 +9282,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>218</v>
       </c>
@@ -6119,7 +9294,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B112" t="s">
         <v>152</v>
       </c>
@@ -6131,7 +9306,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B113" t="s">
         <v>218</v>
       </c>
@@ -6143,7 +9318,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B114" t="s">
         <v>218</v>
       </c>
@@ -6155,7 +9330,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B115" t="s">
         <v>335</v>
       </c>
@@ -6167,7 +9342,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>166</v>
       </c>
@@ -6179,7 +9354,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>166</v>
       </c>
@@ -6191,7 +9366,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
         <v>103</v>
       </c>
@@ -6203,7 +9378,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
         <v>103</v>
       </c>
@@ -6215,7 +9390,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>103</v>
       </c>
@@ -6227,7 +9402,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>103</v>
       </c>
@@ -6239,7 +9414,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>103</v>
       </c>
@@ -6251,7 +9426,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>103</v>
       </c>
@@ -6263,7 +9438,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>103</v>
       </c>
@@ -6275,7 +9450,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>133</v>
       </c>
@@ -6287,7 +9462,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>243</v>
       </c>
@@ -6299,7 +9474,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>243</v>
       </c>
@@ -6311,7 +9486,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>243</v>
       </c>
@@ -6323,7 +9498,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>152</v>
       </c>
@@ -6335,7 +9510,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>335</v>
       </c>
@@ -6347,7 +9522,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>166</v>
       </c>
@@ -6359,7 +9534,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>335</v>
       </c>
@@ -6371,7 +9546,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>335</v>
       </c>
@@ -6383,7 +9558,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>335</v>
       </c>
@@ -6395,7 +9570,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>260</v>
       </c>
@@ -6407,7 +9582,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>260</v>
       </c>
@@ -6419,7 +9594,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B137" t="s">
         <v>260</v>
       </c>
@@ -6431,7 +9606,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
         <v>218</v>
       </c>
@@ -6443,7 +9618,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>335</v>
       </c>
@@ -6455,7 +9630,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>218</v>
       </c>
@@ -6467,7 +9642,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>335</v>
       </c>
@@ -6479,7 +9654,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>152</v>
       </c>
@@ -6491,7 +9666,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>152</v>
       </c>
@@ -6503,7 +9678,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>166</v>
       </c>
@@ -6515,7 +9690,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>152</v>
       </c>
@@ -6527,7 +9702,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>330</v>
       </c>
@@ -6539,7 +9714,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>166</v>
       </c>
@@ -6551,7 +9726,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>166</v>
       </c>
@@ -6563,7 +9738,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>335</v>
       </c>
@@ -6575,7 +9750,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
         <v>238</v>
       </c>
@@ -6587,7 +9762,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>335</v>
       </c>
@@ -6599,7 +9774,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
         <v>218</v>
       </c>
@@ -6611,7 +9786,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
         <v>152</v>
       </c>
@@ -6623,7 +9798,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
         <v>335</v>
       </c>
@@ -6635,7 +9810,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
         <v>270</v>
       </c>
@@ -6647,7 +9822,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B156" t="s">
         <v>133</v>
       </c>
@@ -6659,7 +9834,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B157" t="s">
         <v>133</v>
       </c>
@@ -6671,7 +9846,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B158" t="s">
         <v>231</v>
       </c>
@@ -6683,7 +9858,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B159" t="s">
         <v>231</v>
       </c>
@@ -6695,7 +9870,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
         <v>288</v>
       </c>
@@ -6707,7 +9882,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
         <v>288</v>
       </c>
@@ -6719,7 +9894,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>288</v>
       </c>
@@ -6731,7 +9906,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
         <v>288</v>
       </c>
@@ -6743,7 +9918,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
         <v>288</v>
       </c>
@@ -6755,7 +9930,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
         <v>288</v>
       </c>
@@ -6767,7 +9942,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
         <v>288</v>
       </c>
@@ -6779,7 +9954,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B167" t="s">
         <v>115</v>
       </c>
@@ -6791,7 +9966,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B168" t="s">
         <v>288</v>
       </c>
@@ -6803,7 +9978,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B169" t="s">
         <v>103</v>
       </c>
@@ -6815,7 +9990,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B170" t="s">
         <v>103</v>
       </c>
@@ -6827,7 +10002,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
         <v>103</v>
       </c>
@@ -6839,7 +10014,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B172" t="s">
         <v>103</v>
       </c>
@@ -6851,7 +10026,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
         <v>133</v>
       </c>
@@ -6863,7 +10038,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
         <v>133</v>
       </c>
@@ -6875,7 +10050,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
         <v>355</v>
       </c>
@@ -6887,7 +10062,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
         <v>249</v>
       </c>
@@ -6899,7 +10074,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>103</v>
       </c>
@@ -6911,7 +10086,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>103</v>
       </c>
@@ -6923,7 +10098,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>115</v>
       </c>
@@ -6935,7 +10110,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>115</v>
       </c>
@@ -6947,7 +10122,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>115</v>
       </c>
@@ -6959,7 +10134,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>139</v>
       </c>
@@ -6971,7 +10146,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>139</v>
       </c>
@@ -6983,7 +10158,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>139</v>
       </c>
@@ -6995,7 +10170,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>139</v>
       </c>
@@ -7007,7 +10182,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>139</v>
       </c>
@@ -7019,7 +10194,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>139</v>
       </c>
@@ -7031,7 +10206,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>139</v>
       </c>
@@ -7043,7 +10218,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>139</v>
       </c>
@@ -7055,7 +10230,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>139</v>
       </c>
@@ -7067,7 +10242,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>139</v>
       </c>
@@ -7079,7 +10254,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>139</v>
       </c>
@@ -7091,7 +10266,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>274</v>
       </c>
@@ -7103,7 +10278,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>274</v>
       </c>
@@ -7115,7 +10290,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
         <v>274</v>
       </c>
@@ -7127,7 +10302,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
         <v>274</v>
       </c>
@@ -7139,7 +10314,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
         <v>86</v>
       </c>
@@ -7151,7 +10326,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
         <v>86</v>
       </c>
@@ -7163,7 +10338,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
         <v>86</v>
       </c>
@@ -7175,7 +10350,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
         <v>86</v>
       </c>
@@ -7187,7 +10362,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
         <v>86</v>
       </c>
@@ -7199,7 +10374,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
         <v>86</v>
       </c>
@@ -7211,7 +10386,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
         <v>86</v>
       </c>
@@ -7223,7 +10398,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B204" t="s">
         <v>86</v>
       </c>
@@ -7235,7 +10410,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
         <v>86</v>
       </c>
@@ -7247,7 +10422,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B206" t="s">
         <v>86</v>
       </c>
@@ -7259,7 +10434,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B207" t="s">
         <v>86</v>
       </c>
@@ -7271,7 +10446,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B208" t="s">
         <v>86</v>
       </c>
@@ -7283,7 +10458,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="209" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B209" t="s">
         <v>86</v>
       </c>
@@ -7295,7 +10470,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="210" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>274</v>
       </c>
@@ -7307,7 +10482,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="211" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>274</v>
       </c>
@@ -7319,7 +10494,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="212" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>360</v>
       </c>
@@ -7331,7 +10506,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="213" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>231</v>
       </c>
@@ -7343,7 +10518,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="214" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>231</v>
       </c>
@@ -7355,7 +10530,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="215" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>51</v>
       </c>
@@ -7370,7 +10545,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="216" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>86</v>
       </c>
@@ -7382,7 +10557,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="217" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>35</v>
       </c>
@@ -7394,7 +10569,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="218" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>35</v>
       </c>
@@ -7406,7 +10581,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="219" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B219" t="s">
         <v>35</v>
       </c>
@@ -7418,7 +10593,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="220" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B220" t="s">
         <v>35</v>
       </c>
@@ -7430,7 +10605,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="221" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B221" t="s">
         <v>35</v>
       </c>
@@ -7442,7 +10617,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="222" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B222" t="s">
         <v>35</v>
       </c>
@@ -7454,7 +10629,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="223" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B223" t="s">
         <v>35</v>
       </c>
@@ -7466,7 +10641,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="224" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B224" t="s">
         <v>35</v>
       </c>
@@ -7478,7 +10653,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="225" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B225" t="s">
         <v>35</v>
       </c>
@@ -7490,7 +10665,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="226" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B226" t="s">
         <v>35</v>
       </c>
@@ -7502,7 +10677,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="227" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B227" t="s">
         <v>35</v>
       </c>
@@ -7514,7 +10689,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="228" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B228" t="s">
         <v>35</v>
       </c>
@@ -7526,7 +10701,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="229" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B229" t="s">
         <v>35</v>
       </c>
@@ -7538,7 +10713,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="230" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B230" t="s">
         <v>35</v>
       </c>
@@ -7550,7 +10725,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="231" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B231" t="s">
         <v>35</v>
       </c>
@@ -7562,7 +10737,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="232" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B232" t="s">
         <v>35</v>
       </c>
@@ -7574,7 +10749,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="233" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B233" t="s">
         <v>35</v>
       </c>
@@ -7586,7 +10761,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="234" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B234" t="s">
         <v>35</v>
       </c>
@@ -7598,7 +10773,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="235" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B235" t="s">
         <v>35</v>
       </c>
@@ -7610,7 +10785,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="236" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B236" t="s">
         <v>35</v>
       </c>
@@ -7622,7 +10797,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="237" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B237" t="s">
         <v>35</v>
       </c>
@@ -7634,7 +10809,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="238" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B238" t="s">
         <v>35</v>
       </c>
@@ -7646,7 +10821,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="239" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B239" t="s">
         <v>35</v>
       </c>
@@ -7658,7 +10833,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="240" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B240" t="s">
         <v>35</v>
       </c>
@@ -7670,7 +10845,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="241" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B241" t="s">
         <v>35</v>
       </c>
@@ -7682,7 +10857,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="242" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B242" t="s">
         <v>115</v>
       </c>
@@ -7694,7 +10869,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="243" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B243" t="s">
         <v>80</v>
       </c>
@@ -7706,7 +10881,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="244" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B244" t="s">
         <v>115</v>
       </c>
@@ -7718,7 +10893,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="245" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B245" t="s">
         <v>318</v>
       </c>
@@ -7730,7 +10905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="246" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B246" t="s">
         <v>180</v>
       </c>
@@ -7742,7 +10917,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="247" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B247" t="s">
         <v>180</v>
       </c>
@@ -7754,7 +10929,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="248" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B248" t="s">
         <v>180</v>
       </c>
@@ -7766,7 +10941,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="249" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B249" t="s">
         <v>180</v>
       </c>
@@ -7778,7 +10953,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="250" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B250" t="s">
         <v>180</v>
       </c>
@@ -7790,7 +10965,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="251" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B251" t="s">
         <v>180</v>
       </c>
@@ -7802,7 +10977,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="252" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B252" t="s">
         <v>318</v>
       </c>
@@ -7814,7 +10989,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B253" t="s">
         <v>318</v>
       </c>
@@ -7826,7 +11001,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="254" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B254" t="s">
         <v>282</v>
       </c>
@@ -7838,7 +11013,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="255" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B255" t="s">
         <v>218</v>
       </c>
@@ -7850,7 +11025,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="256" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B256" t="s">
         <v>67</v>
       </c>
@@ -7862,7 +11037,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="257" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B257" t="s">
         <v>61</v>
       </c>
@@ -7874,7 +11049,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="258" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B258" t="s">
         <v>264</v>
       </c>
@@ -7886,7 +11061,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="259" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B259" t="s">
         <v>264</v>
       </c>
@@ -7898,7 +11073,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="260" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B260" t="s">
         <v>264</v>
       </c>
@@ -7910,7 +11085,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="261" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B261" t="s">
         <v>264</v>
       </c>
@@ -7922,7 +11097,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="262" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B262" t="s">
         <v>218</v>
       </c>
@@ -7934,7 +11109,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="263" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B263" t="s">
         <v>218</v>
       </c>
@@ -7946,7 +11121,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="264" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B264" t="s">
         <v>260</v>
       </c>
@@ -7958,7 +11133,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="265" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B265" t="s">
         <v>249</v>
       </c>
@@ -7970,7 +11145,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="266" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B266" t="s">
         <v>260</v>
       </c>
@@ -7982,7 +11157,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="267" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B267" t="s">
         <v>249</v>
       </c>
@@ -7994,7 +11169,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="268" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B268" t="s">
         <v>249</v>
       </c>
@@ -8006,7 +11181,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="269" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B269" t="s">
         <v>249</v>
       </c>
@@ -8018,7 +11193,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="270" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B270" t="s">
         <v>249</v>
       </c>
@@ -8030,7 +11205,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="271" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B271" t="s">
         <v>260</v>
       </c>
@@ -8042,7 +11217,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="272" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B272" t="s">
         <v>249</v>
       </c>
@@ -8054,7 +11229,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="273" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B273" t="s">
         <v>360</v>
       </c>
@@ -8066,7 +11241,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="274" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B274" t="s">
         <v>360</v>
       </c>
@@ -8078,7 +11253,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="275" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B275" t="s">
         <v>360</v>
       </c>
@@ -8090,7 +11265,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="276" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B276" t="s">
         <v>360</v>
       </c>
@@ -8102,7 +11277,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="277" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B277" t="s">
         <v>360</v>
       </c>
@@ -8114,7 +11289,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="278" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B278" t="s">
         <v>360</v>
       </c>
@@ -8126,7 +11301,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="279" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B279" t="s">
         <v>360</v>
       </c>
@@ -8138,7 +11313,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="280" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B280" t="s">
         <v>360</v>
       </c>
@@ -8150,7 +11325,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="281" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B281" t="s">
         <v>360</v>
       </c>
@@ -8162,7 +11337,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="282" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B282" t="s">
         <v>360</v>
       </c>
@@ -8174,7 +11349,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="283" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B283" t="s">
         <v>282</v>
       </c>
@@ -8186,7 +11361,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="284" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B284" t="s">
         <v>51</v>
       </c>
@@ -8201,7 +11376,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="285" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B285" t="s">
         <v>51</v>
       </c>
@@ -8216,7 +11391,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="286" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B286" t="s">
         <v>51</v>
       </c>
@@ -8231,7 +11406,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="287" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B287" t="s">
         <v>35</v>
       </c>
@@ -8243,7 +11418,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="288" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B288" t="s">
         <v>35</v>
       </c>
@@ -8255,7 +11430,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="289" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B289" t="s">
         <v>35</v>
       </c>
@@ -8267,7 +11442,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="290" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B290" t="s">
         <v>35</v>
       </c>
@@ -8279,7 +11454,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="291" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B291" t="s">
         <v>71</v>
       </c>
@@ -8291,7 +11466,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="292" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B292" t="s">
         <v>249</v>
       </c>
@@ -8303,7 +11478,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="293" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B293" t="s">
         <v>71</v>
       </c>
@@ -8315,7 +11490,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="294" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B294" t="s">
         <v>71</v>
       </c>
@@ -8327,7 +11502,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="295" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B295" t="s">
         <v>71</v>
       </c>
@@ -8339,7 +11514,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="296" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B296" t="s">
         <v>282</v>
       </c>
@@ -8351,7 +11526,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="297" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B297" t="s">
         <v>218</v>
       </c>
@@ -8363,7 +11538,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="298" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B298" t="s">
         <v>61</v>
       </c>
@@ -8375,7 +11550,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="299" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B299" t="s">
         <v>218</v>
       </c>
@@ -8387,7 +11562,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="300" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B300" t="s">
         <v>218</v>
       </c>
@@ -8399,7 +11574,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="301" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B301" t="s">
         <v>218</v>
       </c>
@@ -8411,7 +11586,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="302" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B302" t="s">
         <v>218</v>
       </c>
@@ -8423,7 +11598,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="303" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B303" t="s">
         <v>218</v>
       </c>
@@ -8435,7 +11610,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="304" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B304" t="s">
         <v>218</v>
       </c>
@@ -8447,7 +11622,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="305" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B305" t="s">
         <v>260</v>
       </c>
@@ -8459,7 +11634,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="306" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B306" t="s">
         <v>71</v>
       </c>
@@ -8471,7 +11646,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="307" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B307" t="s">
         <v>282</v>
       </c>
@@ -8483,7 +11658,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="308" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B308" t="s">
         <v>308</v>
       </c>
@@ -8495,7 +11670,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="309" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B309" t="s">
         <v>308</v>
       </c>
@@ -8507,7 +11682,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="310" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B310" t="s">
         <v>67</v>
       </c>
@@ -8519,7 +11694,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="311" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B311" t="s">
         <v>61</v>
       </c>
@@ -8531,7 +11706,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="312" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B312" t="s">
         <v>61</v>
       </c>
@@ -8543,7 +11718,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="313" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B313" t="s">
         <v>218</v>
       </c>
@@ -8555,7 +11730,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="314" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B314" t="s">
         <v>71</v>
       </c>
@@ -8567,7 +11742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="315" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B315" t="s">
         <v>249</v>
       </c>
@@ -8579,7 +11754,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="316" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B316" t="s">
         <v>71</v>
       </c>
@@ -8591,7 +11766,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="317" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B317" t="s">
         <v>71</v>
       </c>
@@ -8603,7 +11778,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="318" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B318" t="s">
         <v>71</v>
       </c>
@@ -8615,7 +11790,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="319" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B319" t="s">
         <v>71</v>
       </c>
@@ -8627,7 +11802,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="320" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B320" t="s">
         <v>195</v>
       </c>
@@ -8639,7 +11814,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B321" t="s">
         <v>195</v>
       </c>
@@ -8651,7 +11826,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="322" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B322" t="s">
         <v>195</v>
       </c>
@@ -8663,7 +11838,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="323" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B323" t="s">
         <v>195</v>
       </c>
@@ -8675,7 +11850,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="324" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B324" t="s">
         <v>195</v>
       </c>
@@ -8687,7 +11862,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="325" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B325" t="s">
         <v>195</v>
       </c>
@@ -8699,7 +11874,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="326" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B326" t="s">
         <v>195</v>
       </c>
@@ -8711,7 +11886,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="327" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B327" t="s">
         <v>195</v>
       </c>
@@ -8723,7 +11898,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="328" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B328" t="s">
         <v>195</v>
       </c>
@@ -8735,7 +11910,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="329" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B329" t="s">
         <v>195</v>
       </c>
@@ -8747,7 +11922,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="330" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B330" t="s">
         <v>195</v>
       </c>
@@ -8759,7 +11934,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="331" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B331" t="s">
         <v>195</v>
       </c>
@@ -8771,7 +11946,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="332" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B332" t="s">
         <v>195</v>
       </c>
@@ -8783,7 +11958,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="333" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B333" t="s">
         <v>195</v>
       </c>
@@ -8795,7 +11970,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="334" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B334" t="s">
         <v>195</v>
       </c>
@@ -8807,7 +11982,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="335" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B335" t="s">
         <v>195</v>
       </c>
@@ -8819,7 +11994,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="336" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B336" t="s">
         <v>195</v>
       </c>
@@ -8831,7 +12006,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="337" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B337" t="s">
         <v>195</v>
       </c>
@@ -8843,7 +12018,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="338" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B338" t="s">
         <v>195</v>
       </c>
@@ -8855,7 +12030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="339" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B339" t="s">
         <v>195</v>
       </c>
@@ -8867,7 +12042,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="340" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B340" t="s">
         <v>218</v>
       </c>
@@ -8879,7 +12054,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="341" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B341" t="s">
         <v>218</v>
       </c>
@@ -8891,7 +12066,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="342" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B342" t="s">
         <v>308</v>
       </c>
@@ -8903,7 +12078,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="343" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B343" t="s">
         <v>318</v>
       </c>
@@ -8915,7 +12090,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="344" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B344" t="s">
         <v>318</v>
       </c>
@@ -8927,7 +12102,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="345" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B345" t="s">
         <v>318</v>
       </c>
@@ -8939,7 +12114,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="346" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B346" t="s">
         <v>318</v>
       </c>
@@ -8951,7 +12126,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="347" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B347" t="s">
         <v>318</v>
       </c>
@@ -8963,7 +12138,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="348" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B348" t="s">
         <v>360</v>
       </c>
@@ -8975,7 +12150,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="349" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B349" t="s">
         <v>360</v>
       </c>
@@ -8987,7 +12162,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="350" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B350" t="s">
         <v>308</v>
       </c>
@@ -8999,7 +12174,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="351" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B351" t="s">
         <v>318</v>
       </c>
@@ -9011,7 +12186,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="352" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B352" t="s">
         <v>115</v>
       </c>
@@ -9023,7 +12198,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="353" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B353" t="s">
         <v>115</v>
       </c>
@@ -9035,7 +12210,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="354" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B354" t="s">
         <v>115</v>
       </c>
@@ -9047,7 +12222,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="355" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B355" t="s">
         <v>115</v>
       </c>
@@ -9059,7 +12234,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="356" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B356" t="s">
         <v>152</v>
       </c>
@@ -9071,7 +12246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="357" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B357" t="s">
         <v>152</v>
       </c>
@@ -9083,7 +12258,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="358" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B358" t="s">
         <v>152</v>
       </c>
@@ -9095,7 +12270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="359" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B359" t="s">
         <v>152</v>
       </c>
@@ -9107,7 +12282,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="360" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B360" t="s">
         <v>152</v>
       </c>
@@ -9119,7 +12294,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="361" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B361" t="s">
         <v>52</v>
       </c>
@@ -9131,7 +12306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="362" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B362" t="s">
         <v>52</v>
       </c>
@@ -9143,7 +12318,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="363" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B363" t="s">
         <v>52</v>
       </c>
@@ -9155,7 +12330,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="364" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B364" t="s">
         <v>152</v>
       </c>
@@ -9167,7 +12342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="365" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B365" t="s">
         <v>152</v>
       </c>
@@ -9179,7 +12354,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="366" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B366" t="s">
         <v>52</v>
       </c>
@@ -9191,7 +12366,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="367" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B367" t="s">
         <v>152</v>
       </c>
@@ -9203,7 +12378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="368" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B368" t="s">
         <v>152</v>
       </c>
@@ -9215,7 +12390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="369" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B369" t="s">
         <v>152</v>
       </c>
@@ -9227,7 +12402,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="370" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B370" t="s">
         <v>52</v>
       </c>
@@ -9239,7 +12414,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="371" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B371" t="s">
         <v>152</v>
       </c>
@@ -9251,7 +12426,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="372" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B372" t="s">
         <v>152</v>
       </c>
@@ -9263,7 +12438,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="373" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B373" t="s">
         <v>52</v>
       </c>
@@ -9275,7 +12450,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="374" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B374" t="s">
         <v>52</v>
       </c>
@@ -9287,7 +12462,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="375" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B375" t="s">
         <v>52</v>
       </c>
@@ -9299,7 +12474,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="376" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B376" t="s">
         <v>288</v>
       </c>
@@ -9311,7 +12486,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="377" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B377" t="s">
         <v>180</v>
       </c>
@@ -9323,7 +12498,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="378" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B378" t="s">
         <v>180</v>
       </c>
@@ -9335,7 +12510,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="379" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B379" t="s">
         <v>180</v>
       </c>
@@ -9347,7 +12522,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="380" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B380" t="s">
         <v>180</v>
       </c>
@@ -9359,7 +12534,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="381" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B381" t="s">
         <v>274</v>
       </c>
@@ -9371,7 +12546,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="382" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B382" t="s">
         <v>318</v>
       </c>
@@ -9383,7 +12558,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="383" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B383" t="s">
         <v>318</v>
       </c>
@@ -9395,7 +12570,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="384" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B384" t="s">
         <v>318</v>
       </c>
@@ -9407,7 +12582,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="385" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B385" t="s">
         <v>318</v>
       </c>
@@ -9419,7 +12594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B386" t="s">
         <v>318</v>
       </c>
@@ -9431,7 +12606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="387" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B387" t="s">
         <v>308</v>
       </c>
@@ -9443,7 +12618,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="388" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B388" t="s">
         <v>249</v>
       </c>
@@ -9455,7 +12630,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="389" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B389" t="s">
         <v>195</v>
       </c>
@@ -9467,7 +12642,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="390" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B390" t="s">
         <v>274</v>
       </c>
@@ -9479,7 +12654,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="391" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B391" t="s">
         <v>282</v>
       </c>
@@ -9491,7 +12666,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="392" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B392" t="s">
         <v>282</v>
       </c>
@@ -9503,7 +12678,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="393" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B393" t="s">
         <v>288</v>
       </c>
@@ -9515,7 +12690,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B394" t="s">
         <v>288</v>
       </c>
@@ -9527,7 +12702,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="395" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B395" t="s">
         <v>288</v>
       </c>
@@ -9539,7 +12714,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="396" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B396" t="s">
         <v>288</v>
       </c>
@@ -9551,7 +12726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="397" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B397" t="s">
         <v>115</v>
       </c>
@@ -9563,7 +12738,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="398" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B398" t="s">
         <v>80</v>
       </c>
@@ -9575,7 +12750,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="399" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B399" t="s">
         <v>288</v>
       </c>
@@ -9587,7 +12762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="400" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B400" t="s">
         <v>318</v>
       </c>
@@ -9599,7 +12774,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="401" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B401" t="s">
         <v>335</v>
       </c>
@@ -9611,7 +12786,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="402" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B402" t="s">
         <v>288</v>
       </c>
@@ -9623,7 +12798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="403" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B403" t="s">
         <v>288</v>
       </c>
@@ -9635,7 +12810,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="404" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B404" t="s">
         <v>288</v>
       </c>
@@ -9647,7 +12822,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="405" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B405" t="s">
         <v>318</v>
       </c>
@@ -9659,7 +12834,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="406" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B406" t="s">
         <v>115</v>
       </c>
@@ -9671,7 +12846,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="407" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B407" t="s">
         <v>288</v>
       </c>
@@ -9683,7 +12858,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="408" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B408" t="s">
         <v>180</v>
       </c>
@@ -9695,7 +12870,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="409" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B409" t="s">
         <v>80</v>
       </c>
@@ -9707,7 +12882,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="410" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B410" t="s">
         <v>115</v>
       </c>
@@ -9719,7 +12894,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="411" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B411" t="s">
         <v>115</v>
       </c>
@@ -9731,7 +12906,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="412" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B412" t="s">
         <v>115</v>
       </c>
@@ -9743,7 +12918,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="413" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B413" t="s">
         <v>180</v>
       </c>
@@ -9755,7 +12930,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="414" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B414" t="s">
         <v>282</v>
       </c>
@@ -9767,7 +12942,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="415" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B415" t="s">
         <v>318</v>
       </c>
@@ -9779,7 +12954,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="416" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B416" t="s">
         <v>288</v>
       </c>
@@ -9791,7 +12966,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="417" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B417" t="s">
         <v>34</v>
       </c>
@@ -9803,7 +12978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B418" t="s">
         <v>67</v>
       </c>
@@ -9815,7 +12990,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="419" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B419" t="s">
         <v>218</v>
       </c>
@@ -9827,7 +13002,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="420" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B420" t="s">
         <v>318</v>
       </c>
@@ -9839,7 +13014,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="421" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B421" t="s">
         <v>34</v>
       </c>

--- a/data/excel_sql/2.-tables_db.xlsx
+++ b/data/excel_sql/2.-tables_db.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\GitHub\REDIM_1\data\excel_sql\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IPPI 11\Documents\GitHub\REDIM_1\data\excel_sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DA79FB-9FF2-4B7B-8E52-DC3A2315F589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0D229D-F092-42E2-AC34-65BBBFE18B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YEARS" sheetId="8" r:id="rId1"/>
@@ -19,28 +19,20 @@
     <sheet name="CATEGORIES" sheetId="14" r:id="rId4"/>
     <sheet name="CENTERS" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="993">
   <si>
     <t>Aborto</t>
   </si>
@@ -2977,6 +2969,48 @@
   </si>
   <si>
     <t>[2011, 2012]</t>
+  </si>
+  <si>
+    <t>[2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024]</t>
+  </si>
+  <si>
+    <t>[2013, 2014, 2015]</t>
+  </si>
+  <si>
+    <t>[2011, 2012, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024]</t>
+  </si>
+  <si>
+    <t>[2018, 2019, 2020, 2021, 2022, 2023, 2024]</t>
+  </si>
+  <si>
+    <t>[2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024]</t>
+  </si>
+  <si>
+    <t>[2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018]</t>
+  </si>
+  <si>
+    <t>[2014, 2015, 2016]</t>
+  </si>
+  <si>
+    <t>[2015, 2016]</t>
+  </si>
+  <si>
+    <t>[2011, 2012, 2013, 2014, 2024]</t>
+  </si>
+  <si>
+    <t>[2015, 2016, 2017, 2018, 2019, 2024]</t>
+  </si>
+  <si>
+    <t>[2012, 2013, 2014, 2015, 2016, 2017, 2018]</t>
+  </si>
+  <si>
+    <t>[2016, 2017]</t>
+  </si>
+  <si>
+    <t>[2018]</t>
+  </si>
+  <si>
+    <t>[2017]</t>
   </si>
 </sst>
 </file>
@@ -3038,7 +3072,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3055,6 +3089,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3474,9 +3512,9 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>483</v>
       </c>
@@ -3487,7 +3525,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3498,7 +3536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3509,7 +3547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3520,7 +3558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3531,7 +3569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3542,7 +3580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3553,7 +3591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3564,7 +3602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3575,7 +3613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3586,7 +3624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3597,7 +3635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3608,7 +3646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3619,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3630,7 +3668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3641,7 +3679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3652,7 +3690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3663,7 +3701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3674,7 +3712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3685,7 +3723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3696,7 +3734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3707,7 +3745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3718,7 +3756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3729,7 +3767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3740,7 +3778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3751,7 +3789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3762,7 +3800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3787,13 +3825,13 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="30.5546875" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>483</v>
       </c>
@@ -3813,7 +3851,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3833,7 +3871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3853,7 +3891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3873,7 +3911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3893,7 +3931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3913,7 +3951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3933,7 +3971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3953,7 +3991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3973,7 +4011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3993,7 +4031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4013,7 +4051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4033,7 +4071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4053,7 +4091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4073,7 +4111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4093,7 +4131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4113,7 +4151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4133,7 +4171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4153,7 +4191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4173,7 +4211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4193,7 +4231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4213,7 +4251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4233,7 +4271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4253,7 +4291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4273,7 +4311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4293,7 +4331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4313,7 +4351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4333,7 +4371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4353,7 +4391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4373,7 +4411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4393,7 +4431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4413,7 +4451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4433,7 +4471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4467,12 +4505,12 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.88671875" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>483</v>
       </c>
@@ -4483,7 +4521,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4494,7 +4532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4505,7 +4543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4516,7 +4554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4527,7 +4565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4552,16 +4590,16 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:I438"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.21875" customWidth="1"/>
-    <col min="2" max="2" width="56.88671875" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" customWidth="1"/>
+    <col min="2" max="2" width="56.85546875" customWidth="1"/>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="4" max="5" width="15.6640625" customWidth="1"/>
-    <col min="6" max="8" width="11.6640625" customWidth="1"/>
+    <col min="4" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="8" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>483</v>
       </c>
@@ -4590,7 +4628,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4615,7 +4653,7 @@
       </c>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4640,7 +4678,7 @@
       </c>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4665,7 +4703,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -4690,7 +4728,7 @@
       </c>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -4714,7 +4752,7 @@
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -4738,7 +4776,7 @@
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -4762,7 +4800,7 @@
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>10</v>
       </c>
@@ -4786,7 +4824,7 @@
       </c>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>12</v>
       </c>
@@ -4800,7 +4838,7 @@
       <c r="H10" s="4"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>13</v>
       </c>
@@ -4824,7 +4862,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>14</v>
       </c>
@@ -4848,7 +4886,7 @@
       </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>15</v>
       </c>
@@ -4872,7 +4910,7 @@
       </c>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>16</v>
       </c>
@@ -4896,7 +4934,7 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>17</v>
       </c>
@@ -4910,7 +4948,7 @@
       <c r="H15" s="6"/>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>19</v>
       </c>
@@ -4934,7 +4972,7 @@
       </c>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>20</v>
       </c>
@@ -4958,7 +4996,7 @@
       </c>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>22</v>
       </c>
@@ -4982,7 +5020,7 @@
       </c>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>23</v>
       </c>
@@ -5006,7 +5044,7 @@
       </c>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>24</v>
       </c>
@@ -5030,7 +5068,7 @@
       </c>
       <c r="I20" s="3"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>27</v>
       </c>
@@ -5054,7 +5092,7 @@
       </c>
       <c r="I21" s="3"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>28</v>
       </c>
@@ -5078,7 +5116,7 @@
       </c>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>29</v>
       </c>
@@ -5102,7 +5140,7 @@
       </c>
       <c r="I23" s="3"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>30</v>
       </c>
@@ -5126,7 +5164,7 @@
       </c>
       <c r="I24" s="3"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>31</v>
       </c>
@@ -5140,7 +5178,7 @@
       <c r="H25" s="4"/>
       <c r="I25" s="3"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>32</v>
       </c>
@@ -5164,7 +5202,7 @@
       </c>
       <c r="I26" s="3"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>33</v>
       </c>
@@ -5188,7 +5226,7 @@
       </c>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>34</v>
       </c>
@@ -5212,7 +5250,7 @@
       </c>
       <c r="I28" s="3"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>35</v>
       </c>
@@ -5226,7 +5264,7 @@
       <c r="H29" s="6"/>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>36</v>
       </c>
@@ -5250,7 +5288,7 @@
       </c>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>37</v>
       </c>
@@ -5264,7 +5302,7 @@
       <c r="H31" s="6"/>
       <c r="I31" s="3"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>38</v>
       </c>
@@ -5278,7 +5316,7 @@
       <c r="H32" s="4"/>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>39</v>
       </c>
@@ -5292,7 +5330,7 @@
       <c r="H33" s="4"/>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>40</v>
       </c>
@@ -5316,7 +5354,7 @@
       </c>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>41</v>
       </c>
@@ -5340,7 +5378,7 @@
       </c>
       <c r="I35" s="3"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>43</v>
       </c>
@@ -5364,7 +5402,7 @@
       </c>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>44</v>
       </c>
@@ -5388,7 +5426,7 @@
       </c>
       <c r="I37" s="3"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>46</v>
       </c>
@@ -5412,7 +5450,7 @@
       </c>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>47</v>
       </c>
@@ -5436,7 +5474,7 @@
       </c>
       <c r="I39" s="3"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>48</v>
       </c>
@@ -5460,7 +5498,7 @@
       </c>
       <c r="I40" s="3"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>49</v>
       </c>
@@ -5484,7 +5522,7 @@
       </c>
       <c r="I41" s="3"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>50</v>
       </c>
@@ -5508,7 +5546,7 @@
       </c>
       <c r="I42" s="3"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>51</v>
       </c>
@@ -5532,7 +5570,7 @@
       </c>
       <c r="I43" s="3"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>52</v>
       </c>
@@ -5556,7 +5594,7 @@
       </c>
       <c r="I44" s="3"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>53</v>
       </c>
@@ -5580,7 +5618,7 @@
       </c>
       <c r="I45" s="3"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>56</v>
       </c>
@@ -5604,7 +5642,7 @@
       </c>
       <c r="I46" s="3"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>57</v>
       </c>
@@ -5628,7 +5666,7 @@
       </c>
       <c r="I47" s="3"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>58</v>
       </c>
@@ -5642,7 +5680,7 @@
       <c r="H48" s="4"/>
       <c r="I48" s="3"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>59</v>
       </c>
@@ -5656,7 +5694,7 @@
       <c r="H49" s="4"/>
       <c r="I49" s="3"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>60</v>
       </c>
@@ -5680,7 +5718,7 @@
       </c>
       <c r="I50" s="3"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>63</v>
       </c>
@@ -5704,7 +5742,7 @@
       </c>
       <c r="I51" s="3"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>64</v>
       </c>
@@ -5728,7 +5766,7 @@
       </c>
       <c r="I52" s="3"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>65</v>
       </c>
@@ -5752,7 +5790,7 @@
       </c>
       <c r="I53" s="3"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>66</v>
       </c>
@@ -5776,7 +5814,7 @@
       </c>
       <c r="I54" s="3"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>67</v>
       </c>
@@ -5800,7 +5838,7 @@
       </c>
       <c r="I55" s="3"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>68</v>
       </c>
@@ -5824,7 +5862,7 @@
       </c>
       <c r="I56" s="3"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>69</v>
       </c>
@@ -5848,7 +5886,7 @@
       </c>
       <c r="I57" s="3"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>72</v>
       </c>
@@ -5872,7 +5910,7 @@
       </c>
       <c r="I58" s="3"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>73</v>
       </c>
@@ -5896,7 +5934,7 @@
       </c>
       <c r="I59" s="3"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>75</v>
       </c>
@@ -5920,7 +5958,7 @@
       </c>
       <c r="I60" s="3"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>77</v>
       </c>
@@ -5944,7 +5982,7 @@
       </c>
       <c r="I61" s="3"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>78</v>
       </c>
@@ -5958,637 +5996,1149 @@
       <c r="H62" s="6"/>
       <c r="I62" s="3"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>82</v>
       </c>
       <c r="B63" t="s">
         <v>580</v>
       </c>
-      <c r="D63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
+      <c r="D63" s="3">
+        <v>6</v>
+      </c>
+      <c r="E63" t="s">
+        <v>964</v>
+      </c>
+      <c r="F63" s="3">
+        <v>136</v>
+      </c>
+      <c r="G63" s="3">
+        <v>768</v>
+      </c>
+      <c r="H63" s="3">
+        <v>384</v>
+      </c>
       <c r="I63" s="3"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>83</v>
       </c>
       <c r="B64" t="s">
         <v>581</v>
       </c>
-      <c r="D64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
+      <c r="D64" s="3">
+        <v>6</v>
+      </c>
+      <c r="E64" t="s">
+        <v>964</v>
+      </c>
+      <c r="F64" s="3">
+        <v>230</v>
+      </c>
+      <c r="G64" s="3">
+        <v>768</v>
+      </c>
+      <c r="H64" s="3">
+        <v>384</v>
+      </c>
       <c r="I64" s="3"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>84</v>
       </c>
       <c r="B65" t="s">
         <v>582</v>
       </c>
-      <c r="D65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
+      <c r="D65" s="3">
+        <v>3</v>
+      </c>
+      <c r="E65" t="s">
+        <v>969</v>
+      </c>
+      <c r="F65" s="3">
+        <v>100</v>
+      </c>
+      <c r="G65" s="3">
+        <v>256</v>
+      </c>
+      <c r="H65" s="3">
+        <v>192</v>
+      </c>
       <c r="I65" s="3"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>85</v>
       </c>
       <c r="B66" t="s">
         <v>583</v>
       </c>
-      <c r="D66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
+      <c r="D66" s="3">
+        <v>3</v>
+      </c>
+      <c r="E66" t="s">
+        <v>969</v>
+      </c>
+      <c r="F66" s="3">
+        <v>183</v>
+      </c>
+      <c r="G66" s="3">
+        <v>256</v>
+      </c>
+      <c r="H66" s="3">
+        <v>192</v>
+      </c>
       <c r="I66" s="3"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>86</v>
       </c>
       <c r="B67" t="s">
         <v>584</v>
       </c>
-      <c r="D67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
+      <c r="D67" s="3">
+        <v>10</v>
+      </c>
+      <c r="E67" t="s">
+        <v>979</v>
+      </c>
+      <c r="F67" s="3">
+        <v>11106</v>
+      </c>
+      <c r="G67" s="3">
+        <v>1088</v>
+      </c>
+      <c r="H67" s="3">
+        <v>640</v>
+      </c>
       <c r="I67" s="3"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>87</v>
       </c>
       <c r="B68" t="s">
         <v>585</v>
       </c>
-      <c r="D68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
+      <c r="D68" s="3">
+        <v>3</v>
+      </c>
+      <c r="E68" t="s">
+        <v>980</v>
+      </c>
+      <c r="F68" s="3">
+        <v>655</v>
+      </c>
+      <c r="G68" s="3">
+        <v>192</v>
+      </c>
+      <c r="H68" s="3">
+        <v>192</v>
+      </c>
       <c r="I68" s="3"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>88</v>
       </c>
       <c r="B69" t="s">
         <v>586</v>
       </c>
-      <c r="D69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
+      <c r="D69" s="3">
+        <v>11</v>
+      </c>
+      <c r="E69" t="s">
+        <v>981</v>
+      </c>
+      <c r="F69" s="3">
+        <v>2306</v>
+      </c>
+      <c r="G69" s="3">
+        <v>1152</v>
+      </c>
+      <c r="H69" s="3">
+        <v>704</v>
+      </c>
       <c r="I69" s="3"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>100</v>
       </c>
       <c r="B70" t="s">
         <v>587</v>
       </c>
-      <c r="D70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
+      <c r="D70" s="3">
+        <v>10</v>
+      </c>
+      <c r="E70" t="s">
+        <v>979</v>
+      </c>
+      <c r="F70" s="3">
+        <v>1843</v>
+      </c>
+      <c r="G70" s="3">
+        <v>1088</v>
+      </c>
+      <c r="H70" s="3">
+        <v>640</v>
+      </c>
       <c r="I70" s="3"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>102</v>
       </c>
       <c r="B71" t="s">
         <v>589</v>
       </c>
-      <c r="D71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
+      <c r="D71" s="3">
+        <v>6</v>
+      </c>
+      <c r="E71" t="s">
+        <v>964</v>
+      </c>
+      <c r="F71" s="3">
+        <v>218</v>
+      </c>
+      <c r="G71" s="3">
+        <v>768</v>
+      </c>
+      <c r="H71" s="3">
+        <v>384</v>
+      </c>
       <c r="I71" s="3"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>103</v>
       </c>
       <c r="B72" t="s">
         <v>590</v>
       </c>
-      <c r="D72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
+      <c r="D72" s="3">
+        <v>4</v>
+      </c>
+      <c r="E72" t="s">
+        <v>972</v>
+      </c>
+      <c r="F72" s="3">
+        <v>87</v>
+      </c>
+      <c r="G72" s="3">
+        <v>448</v>
+      </c>
+      <c r="H72" s="3">
+        <v>256</v>
+      </c>
       <c r="I72" s="3"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>106</v>
       </c>
       <c r="B73" t="s">
         <v>591</v>
       </c>
-      <c r="D73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
+      <c r="D73" s="3">
+        <v>14</v>
+      </c>
+      <c r="E73" t="s">
+        <v>960</v>
+      </c>
+      <c r="F73" s="3">
+        <v>106118</v>
+      </c>
+      <c r="G73" s="3">
+        <v>1786</v>
+      </c>
+      <c r="H73" s="3">
+        <v>896</v>
+      </c>
       <c r="I73" s="3"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>107</v>
       </c>
       <c r="B74" t="s">
         <v>592</v>
       </c>
-      <c r="D74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
       <c r="I74" s="3"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>108</v>
       </c>
       <c r="B75" t="s">
         <v>593</v>
       </c>
-      <c r="D75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
+      <c r="D75" s="3">
+        <v>8</v>
+      </c>
+      <c r="E75" t="s">
+        <v>961</v>
+      </c>
+      <c r="F75" s="3">
+        <v>300</v>
+      </c>
+      <c r="G75" s="3">
+        <v>960</v>
+      </c>
+      <c r="H75" s="3">
+        <v>512</v>
+      </c>
       <c r="I75" s="3"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>109</v>
       </c>
       <c r="B76" t="s">
         <v>594</v>
       </c>
-      <c r="D76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
+      <c r="D76" s="3">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>976</v>
+      </c>
+      <c r="F76" s="3">
+        <v>14</v>
+      </c>
+      <c r="G76" s="3">
+        <v>64</v>
+      </c>
+      <c r="H76" s="3">
+        <v>64</v>
+      </c>
       <c r="I76" s="3"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>110</v>
       </c>
       <c r="B77" t="s">
         <v>595</v>
       </c>
-      <c r="D77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
+      <c r="D77" s="3">
+        <v>7</v>
+      </c>
+      <c r="E77" t="s">
+        <v>982</v>
+      </c>
+      <c r="F77" s="3">
+        <v>17</v>
+      </c>
+      <c r="G77" s="3">
+        <v>832</v>
+      </c>
+      <c r="H77" s="3">
+        <v>448</v>
+      </c>
       <c r="I77" s="3"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>112</v>
       </c>
       <c r="B78" t="s">
         <v>596</v>
       </c>
-      <c r="D78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
+      <c r="D78" s="3">
+        <v>2</v>
+      </c>
+      <c r="E78" t="s">
+        <v>963</v>
+      </c>
+      <c r="F78" s="3">
+        <v>55</v>
+      </c>
+      <c r="G78" s="3">
+        <v>128</v>
+      </c>
+      <c r="H78" s="3">
+        <v>128</v>
+      </c>
       <c r="I78" s="3"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>113</v>
       </c>
       <c r="B79" t="s">
         <v>597</v>
       </c>
-      <c r="D79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
+      <c r="D79" s="3">
+        <v>9</v>
+      </c>
+      <c r="E79" t="s">
+        <v>983</v>
+      </c>
+      <c r="F79" s="3">
+        <v>152</v>
+      </c>
+      <c r="G79" s="3">
+        <v>1024</v>
+      </c>
+      <c r="H79" s="3">
+        <v>576</v>
+      </c>
       <c r="I79" s="3"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>114</v>
       </c>
       <c r="B80" t="s">
         <v>598</v>
       </c>
-      <c r="D80" s="3"/>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
+      <c r="D80" s="3">
+        <v>9</v>
+      </c>
+      <c r="E80" t="s">
+        <v>983</v>
+      </c>
+      <c r="F80" s="3">
+        <v>33</v>
+      </c>
+      <c r="G80" s="3">
+        <v>1024</v>
+      </c>
+      <c r="H80" s="3">
+        <v>576</v>
+      </c>
       <c r="I80" s="3"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>115</v>
       </c>
       <c r="B81" t="s">
         <v>599</v>
       </c>
-      <c r="D81" s="3"/>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
+      <c r="D81" s="3">
+        <v>2</v>
+      </c>
+      <c r="E81" t="s">
+        <v>978</v>
+      </c>
+      <c r="F81" s="3">
+        <v>72</v>
+      </c>
+      <c r="G81" s="3">
+        <v>128</v>
+      </c>
+      <c r="H81" s="3">
+        <v>128</v>
+      </c>
       <c r="I81" s="3"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>116</v>
       </c>
       <c r="B82" t="s">
         <v>600</v>
       </c>
-      <c r="D82" s="3"/>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
+      <c r="D82" s="3">
+        <v>2</v>
+      </c>
+      <c r="E82" t="s">
+        <v>963</v>
+      </c>
+      <c r="F82" s="3">
+        <v>69</v>
+      </c>
+      <c r="G82" s="3">
+        <v>128</v>
+      </c>
+      <c r="H82" s="3">
+        <v>128</v>
+      </c>
       <c r="I82" s="3"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>117</v>
       </c>
       <c r="B83" t="s">
         <v>601</v>
       </c>
-      <c r="D83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
+      <c r="D83" s="3">
+        <v>2</v>
+      </c>
+      <c r="E83" t="s">
+        <v>963</v>
+      </c>
+      <c r="F83" s="3">
+        <v>7</v>
+      </c>
+      <c r="G83" s="3">
+        <v>128</v>
+      </c>
+      <c r="H83" s="3">
+        <v>128</v>
+      </c>
       <c r="I83" s="3"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>118</v>
       </c>
       <c r="B84" t="s">
         <v>602</v>
       </c>
-      <c r="D84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
+      <c r="D84" s="3">
+        <v>1</v>
+      </c>
+      <c r="E84" t="s">
+        <v>962</v>
+      </c>
+      <c r="F84" s="3">
+        <v>41</v>
+      </c>
+      <c r="G84" s="3">
+        <v>64</v>
+      </c>
+      <c r="H84" s="3">
+        <v>64</v>
+      </c>
       <c r="I84" s="3"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>119</v>
       </c>
       <c r="B85" t="s">
         <v>603</v>
       </c>
-      <c r="D85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
+      <c r="D85" s="3">
+        <v>1</v>
+      </c>
+      <c r="E85" t="s">
+        <v>962</v>
+      </c>
+      <c r="F85" s="3">
+        <v>32</v>
+      </c>
+      <c r="G85" s="3">
+        <v>64</v>
+      </c>
+      <c r="H85" s="3">
+        <v>64</v>
+      </c>
       <c r="I85" s="3"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>121</v>
       </c>
       <c r="B86" t="s">
         <v>604</v>
       </c>
-      <c r="D86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
+      <c r="D86" s="3">
+        <v>6</v>
+      </c>
+      <c r="E86" t="s">
+        <v>964</v>
+      </c>
+      <c r="F86" s="3">
+        <v>748</v>
+      </c>
+      <c r="G86" s="3">
+        <v>768</v>
+      </c>
+      <c r="H86" s="3">
+        <v>384</v>
+      </c>
       <c r="I86" s="3"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>122</v>
       </c>
       <c r="B87" t="s">
         <v>605</v>
       </c>
-      <c r="D87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
+      <c r="D87" s="3">
+        <v>4</v>
+      </c>
+      <c r="E87" t="s">
+        <v>972</v>
+      </c>
+      <c r="F87" s="3">
+        <v>456</v>
+      </c>
+      <c r="G87" s="3">
+        <v>320</v>
+      </c>
+      <c r="H87" s="3">
+        <v>256</v>
+      </c>
       <c r="I87" s="3"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>124</v>
       </c>
       <c r="B88" t="s">
         <v>606</v>
       </c>
-      <c r="D88" s="3"/>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
+      <c r="D88" s="3">
+        <v>6</v>
+      </c>
+      <c r="E88" t="s">
+        <v>964</v>
+      </c>
+      <c r="F88" s="3">
+        <v>92438</v>
+      </c>
+      <c r="G88" s="3">
+        <v>768</v>
+      </c>
+      <c r="H88" s="3">
+        <v>384</v>
+      </c>
       <c r="I88" s="3"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>125</v>
       </c>
       <c r="B89" t="s">
         <v>607</v>
       </c>
-      <c r="D89" s="3"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
+      <c r="D89" s="3">
+        <v>8</v>
+      </c>
+      <c r="E89" t="s">
+        <v>984</v>
+      </c>
+      <c r="F89" s="3">
+        <v>92832</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1018</v>
+      </c>
+      <c r="H89" s="3">
+        <v>512</v>
+      </c>
       <c r="I89" s="3"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>128</v>
       </c>
       <c r="B90" t="s">
         <v>608</v>
       </c>
-      <c r="D90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
+      <c r="D90" s="3">
+        <v>3</v>
+      </c>
+      <c r="E90" t="s">
+        <v>985</v>
+      </c>
+      <c r="F90" s="3">
+        <v>1030</v>
+      </c>
+      <c r="G90" s="3">
+        <v>192</v>
+      </c>
+      <c r="H90" s="3">
+        <v>192</v>
+      </c>
       <c r="I90" s="3"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>129</v>
       </c>
       <c r="B91" t="s">
         <v>609</v>
       </c>
-      <c r="D91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
+      <c r="D91" s="3">
+        <v>8</v>
+      </c>
+      <c r="E91" t="s">
+        <v>961</v>
+      </c>
+      <c r="F91" s="3">
+        <v>6068</v>
+      </c>
+      <c r="G91" s="3">
+        <v>1024</v>
+      </c>
+      <c r="H91" s="3">
+        <v>512</v>
+      </c>
       <c r="I91" s="3"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>130</v>
       </c>
       <c r="B92" t="s">
         <v>610</v>
       </c>
-      <c r="D92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
+      <c r="D92" s="3">
+        <v>2</v>
+      </c>
+      <c r="E92" t="s">
+        <v>967</v>
+      </c>
+      <c r="F92" s="3">
+        <v>9761</v>
+      </c>
+      <c r="G92" s="3">
+        <v>256</v>
+      </c>
+      <c r="H92" s="3">
+        <v>128</v>
+      </c>
       <c r="I92" s="3"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>131</v>
       </c>
       <c r="B93" t="s">
         <v>611</v>
       </c>
-      <c r="D93" s="3"/>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
+      <c r="D93" s="3">
+        <v>2</v>
+      </c>
+      <c r="E93" t="s">
+        <v>986</v>
+      </c>
+      <c r="F93" s="3">
+        <v>9877</v>
+      </c>
+      <c r="G93" s="3">
+        <v>256</v>
+      </c>
+      <c r="H93" s="3">
+        <v>128</v>
+      </c>
       <c r="I93" s="3"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>132</v>
       </c>
       <c r="B94" t="s">
         <v>612</v>
       </c>
-      <c r="D94" s="3"/>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
+      <c r="D94" s="3">
+        <v>5</v>
+      </c>
+      <c r="E94" t="s">
+        <v>987</v>
+      </c>
+      <c r="F94" s="3">
+        <v>58017</v>
+      </c>
+      <c r="G94" s="3">
+        <v>634</v>
+      </c>
+      <c r="H94" s="3">
+        <v>320</v>
+      </c>
       <c r="I94" s="3"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>133</v>
       </c>
       <c r="B95" t="s">
         <v>613</v>
       </c>
-      <c r="D95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
+      <c r="D95" s="3">
+        <v>6</v>
+      </c>
+      <c r="E95" t="s">
+        <v>988</v>
+      </c>
+      <c r="F95" s="3">
+        <v>8767</v>
+      </c>
+      <c r="G95" s="3">
+        <v>768</v>
+      </c>
+      <c r="H95" s="3">
+        <v>384</v>
+      </c>
       <c r="I95" s="3"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>134</v>
       </c>
       <c r="B96" t="s">
         <v>614</v>
       </c>
-      <c r="D96" s="3"/>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
+      <c r="D96" s="3">
+        <v>5</v>
+      </c>
+      <c r="E96" t="s">
+        <v>971</v>
+      </c>
+      <c r="F96" s="3">
+        <v>5417</v>
+      </c>
+      <c r="G96" s="3">
+        <v>640</v>
+      </c>
+      <c r="H96" s="3">
+        <v>320</v>
+      </c>
       <c r="I96" s="3"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>135</v>
       </c>
       <c r="B97" t="s">
         <v>615</v>
       </c>
-      <c r="D97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
+      <c r="D97" s="3">
+        <v>6</v>
+      </c>
+      <c r="E97" t="s">
+        <v>964</v>
+      </c>
+      <c r="F97" s="3">
+        <v>26586</v>
+      </c>
+      <c r="G97" s="3">
+        <v>768</v>
+      </c>
+      <c r="H97" s="3">
+        <v>384</v>
+      </c>
       <c r="I97" s="3"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>136</v>
       </c>
       <c r="B98" t="s">
         <v>616</v>
       </c>
-      <c r="D98" s="3"/>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
+      <c r="D98" s="3">
+        <v>6</v>
+      </c>
+      <c r="E98" t="s">
+        <v>964</v>
+      </c>
+      <c r="F98" s="3">
+        <v>10188</v>
+      </c>
+      <c r="G98" s="3">
+        <v>768</v>
+      </c>
+      <c r="H98" s="3">
+        <v>384</v>
+      </c>
       <c r="I98" s="3"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>137</v>
       </c>
       <c r="B99" t="s">
         <v>617</v>
       </c>
-      <c r="D99" s="3"/>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
+      <c r="D99" s="3">
+        <v>6</v>
+      </c>
+      <c r="E99" t="s">
+        <v>964</v>
+      </c>
+      <c r="F99" s="3">
+        <v>24206</v>
+      </c>
+      <c r="G99" s="3">
+        <v>768</v>
+      </c>
+      <c r="H99" s="3">
+        <v>384</v>
+      </c>
       <c r="I99" s="3"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>138</v>
       </c>
       <c r="B100" t="s">
         <v>618</v>
       </c>
-      <c r="D100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
+      <c r="D100" s="3">
+        <v>6</v>
+      </c>
+      <c r="E100" t="s">
+        <v>964</v>
+      </c>
+      <c r="F100" s="3">
+        <v>75498</v>
+      </c>
+      <c r="G100" s="3">
+        <v>768</v>
+      </c>
+      <c r="H100" s="3">
+        <v>384</v>
+      </c>
       <c r="I100" s="3"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>139</v>
       </c>
       <c r="B101" t="s">
         <v>619</v>
       </c>
-      <c r="D101" s="3"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
+      <c r="D101" s="3">
+        <v>6</v>
+      </c>
+      <c r="E101" t="s">
+        <v>964</v>
+      </c>
+      <c r="F101" s="3">
+        <v>3723</v>
+      </c>
+      <c r="G101" s="3">
+        <v>768</v>
+      </c>
+      <c r="H101" s="3">
+        <v>384</v>
+      </c>
       <c r="I101" s="3"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>140</v>
       </c>
       <c r="B102" t="s">
         <v>620</v>
       </c>
-      <c r="D102" s="4"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
+      <c r="D102" s="4">
+        <v>2</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="F102" s="4">
+        <v>1157</v>
+      </c>
+      <c r="G102" s="4">
+        <v>256</v>
+      </c>
+      <c r="H102" s="4">
+        <v>128</v>
+      </c>
       <c r="I102" s="3"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>141</v>
       </c>
       <c r="B103" t="s">
         <v>621</v>
       </c>
-      <c r="D103" s="4"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
+      <c r="D103" s="4">
+        <v>2</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="F103" s="4">
+        <v>2425</v>
+      </c>
+      <c r="G103" s="4">
+        <v>256</v>
+      </c>
+      <c r="H103" s="4">
+        <v>128</v>
+      </c>
       <c r="I103" s="3"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>142</v>
       </c>
       <c r="B104" t="s">
         <v>622</v>
       </c>
-      <c r="D104" s="4"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
+      <c r="D104" s="4">
+        <v>7</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>989</v>
+      </c>
+      <c r="F104" s="4">
+        <v>16907</v>
+      </c>
+      <c r="G104" s="4">
+        <v>832</v>
+      </c>
+      <c r="H104" s="4">
+        <v>448</v>
+      </c>
       <c r="I104" s="3"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>143</v>
       </c>
       <c r="B105" t="s">
         <v>623</v>
       </c>
-      <c r="D105" s="4"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="4"/>
-      <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
+      <c r="D105" s="4">
+        <v>2</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>978</v>
+      </c>
+      <c r="F105" s="4">
+        <v>961</v>
+      </c>
+      <c r="G105" s="4">
+        <v>186</v>
+      </c>
+      <c r="H105" s="4">
+        <v>128</v>
+      </c>
       <c r="I105" s="3"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>144</v>
       </c>
       <c r="B106" t="s">
         <v>624</v>
       </c>
-      <c r="D106" s="4"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
+      <c r="D106" s="8">
+        <v>4</v>
+      </c>
+      <c r="E106" s="9" t="s">
+        <v>972</v>
+      </c>
+      <c r="F106" s="8">
+        <v>20421</v>
+      </c>
+      <c r="G106" s="8">
+        <v>512</v>
+      </c>
+      <c r="H106" s="8">
+        <v>256</v>
+      </c>
       <c r="I106" s="3"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>145</v>
       </c>
       <c r="B107" t="s">
         <v>625</v>
       </c>
-      <c r="D107" s="4"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
+      <c r="D107" s="4">
+        <v>2</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="F107" s="4">
+        <v>653</v>
+      </c>
+      <c r="G107" s="4">
+        <v>256</v>
+      </c>
+      <c r="H107" s="4">
+        <v>128</v>
+      </c>
       <c r="I107" s="3"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>146</v>
       </c>
       <c r="B108" t="s">
         <v>626</v>
       </c>
-      <c r="D108" s="3"/>
-      <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
+      <c r="D108" s="4">
+        <v>2</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="F108" s="4">
+        <v>2104</v>
+      </c>
+      <c r="G108" s="4">
+        <v>192</v>
+      </c>
+      <c r="H108" s="4">
+        <v>128</v>
+      </c>
       <c r="I108" s="3"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>148</v>
       </c>
       <c r="B109" t="s">
         <v>627</v>
       </c>
-      <c r="D109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
+      <c r="D109" s="3">
+        <v>6</v>
+      </c>
+      <c r="E109" t="s">
+        <v>964</v>
+      </c>
+      <c r="F109" s="3">
+        <v>524</v>
+      </c>
+      <c r="G109" s="3">
+        <v>768</v>
+      </c>
+      <c r="H109" s="3">
+        <v>384</v>
+      </c>
       <c r="I109" s="3"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>149</v>
       </c>
       <c r="B110" t="s">
         <v>628</v>
       </c>
-      <c r="D110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
+      <c r="D110" s="3">
+        <v>2</v>
+      </c>
+      <c r="E110" t="s">
+        <v>967</v>
+      </c>
+      <c r="F110" s="3">
+        <v>70</v>
+      </c>
+      <c r="G110" s="3">
+        <v>256</v>
+      </c>
+      <c r="H110" s="3">
+        <v>128</v>
+      </c>
       <c r="I110" s="3"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>152</v>
       </c>
@@ -6602,7 +7152,7 @@
       <c r="H111" s="4"/>
       <c r="I111" s="3"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>153</v>
       </c>
@@ -6616,203 +7166,357 @@
       <c r="H112" s="4"/>
       <c r="I112" s="3"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>154</v>
       </c>
       <c r="B113" t="s">
         <v>631</v>
       </c>
-      <c r="D113" s="4"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
-      <c r="H113" s="4"/>
+      <c r="D113" s="4">
+        <v>2</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>990</v>
+      </c>
+      <c r="F113" s="4">
+        <v>1115</v>
+      </c>
+      <c r="G113" s="4">
+        <v>128</v>
+      </c>
+      <c r="H113" s="4">
+        <v>128</v>
+      </c>
       <c r="I113" s="3"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>155</v>
       </c>
       <c r="B114" t="s">
         <v>632</v>
       </c>
-      <c r="D114" s="3"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
+      <c r="D114" s="3">
+        <v>1</v>
+      </c>
+      <c r="E114" t="s">
+        <v>974</v>
+      </c>
+      <c r="F114" s="3">
+        <v>0</v>
+      </c>
+      <c r="G114" s="3">
+        <v>128</v>
+      </c>
+      <c r="H114" s="3">
+        <v>64</v>
+      </c>
       <c r="I114" s="3"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>156</v>
       </c>
       <c r="B115" t="s">
         <v>633</v>
       </c>
-      <c r="D115" s="3"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
+      <c r="D115" s="3">
+        <v>7</v>
+      </c>
+      <c r="E115" t="s">
+        <v>982</v>
+      </c>
+      <c r="F115" s="3">
+        <v>6308</v>
+      </c>
+      <c r="G115" s="3">
+        <v>896</v>
+      </c>
+      <c r="H115" s="3">
+        <v>448</v>
+      </c>
       <c r="I115" s="3"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>157</v>
       </c>
       <c r="B116" t="s">
         <v>634</v>
       </c>
-      <c r="D116" s="3"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
+      <c r="D116" s="3">
+        <v>5</v>
+      </c>
+      <c r="E116" t="s">
+        <v>970</v>
+      </c>
+      <c r="F116" s="3">
+        <v>1926</v>
+      </c>
+      <c r="G116" s="3">
+        <v>448</v>
+      </c>
+      <c r="H116" s="3">
+        <v>320</v>
+      </c>
       <c r="I116" s="3"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>158</v>
       </c>
       <c r="B117" t="s">
         <v>635</v>
       </c>
-      <c r="D117" s="3"/>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
+      <c r="D117" s="3">
+        <v>5</v>
+      </c>
+      <c r="E117" t="s">
+        <v>971</v>
+      </c>
+      <c r="F117" s="3">
+        <v>116</v>
+      </c>
+      <c r="G117" s="3">
+        <v>640</v>
+      </c>
+      <c r="H117" s="3">
+        <v>320</v>
+      </c>
       <c r="I117" s="3"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>159</v>
       </c>
       <c r="B118" t="s">
         <v>636</v>
       </c>
-      <c r="D118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
+      <c r="D118" s="3">
+        <v>1</v>
+      </c>
+      <c r="E118" t="s">
+        <v>991</v>
+      </c>
+      <c r="F118" s="3">
+        <v>1072</v>
+      </c>
+      <c r="G118" s="3">
+        <v>128</v>
+      </c>
+      <c r="H118" s="3">
+        <v>64</v>
+      </c>
       <c r="I118" s="3"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>160</v>
       </c>
       <c r="B119" t="s">
         <v>637</v>
       </c>
-      <c r="D119" s="3"/>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
+      <c r="D119" s="3">
+        <v>6</v>
+      </c>
+      <c r="E119" t="s">
+        <v>964</v>
+      </c>
+      <c r="F119" s="3">
+        <v>2151</v>
+      </c>
+      <c r="G119" s="3">
+        <v>768</v>
+      </c>
+      <c r="H119" s="3">
+        <v>384</v>
+      </c>
       <c r="I119" s="3"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>161</v>
       </c>
       <c r="B120" t="s">
         <v>638</v>
       </c>
-      <c r="D120" s="3"/>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
+      <c r="D120" s="3">
+        <v>7</v>
+      </c>
+      <c r="E120" t="s">
+        <v>982</v>
+      </c>
+      <c r="F120" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G120" s="3">
+        <v>896</v>
+      </c>
+      <c r="H120" s="3">
+        <v>448</v>
+      </c>
       <c r="I120" s="3"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>162</v>
       </c>
       <c r="B121" t="s">
         <v>639</v>
       </c>
-      <c r="D121" s="3"/>
-      <c r="F121" s="3"/>
-      <c r="G121" s="3"/>
-      <c r="H121" s="3"/>
+      <c r="D121" s="3">
+        <v>7</v>
+      </c>
+      <c r="E121" t="s">
+        <v>982</v>
+      </c>
+      <c r="F121" s="3">
+        <v>1756</v>
+      </c>
+      <c r="G121" s="3">
+        <v>896</v>
+      </c>
+      <c r="H121" s="3">
+        <v>448</v>
+      </c>
       <c r="I121" s="3"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>163</v>
       </c>
       <c r="B122" t="s">
         <v>640</v>
       </c>
-      <c r="D122" s="3"/>
-      <c r="F122" s="3"/>
-      <c r="G122" s="3"/>
-      <c r="H122" s="3"/>
+      <c r="D122" s="3">
+        <v>7</v>
+      </c>
+      <c r="E122" t="s">
+        <v>982</v>
+      </c>
+      <c r="F122" s="3">
+        <v>588</v>
+      </c>
+      <c r="G122" s="3">
+        <v>896</v>
+      </c>
+      <c r="H122" s="3">
+        <v>448</v>
+      </c>
       <c r="I122" s="3"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>164</v>
       </c>
       <c r="B123" t="s">
         <v>641</v>
       </c>
-      <c r="D123" s="3"/>
-      <c r="F123" s="3"/>
-      <c r="G123" s="3"/>
-      <c r="H123" s="3"/>
+      <c r="D123" s="3">
+        <v>7</v>
+      </c>
+      <c r="E123" t="s">
+        <v>982</v>
+      </c>
+      <c r="F123" s="3">
+        <v>8596</v>
+      </c>
+      <c r="G123" s="3">
+        <v>896</v>
+      </c>
+      <c r="H123" s="3">
+        <v>448</v>
+      </c>
       <c r="I123" s="3"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>165</v>
       </c>
       <c r="B124" t="s">
         <v>642</v>
       </c>
-      <c r="D124" s="3"/>
-      <c r="F124" s="3"/>
-      <c r="G124" s="3"/>
-      <c r="H124" s="3"/>
+      <c r="D124" s="3">
+        <v>1</v>
+      </c>
+      <c r="E124" t="s">
+        <v>962</v>
+      </c>
+      <c r="F124" s="3">
+        <v>733</v>
+      </c>
+      <c r="G124" s="3">
+        <v>64</v>
+      </c>
+      <c r="H124" s="3">
+        <v>64</v>
+      </c>
       <c r="I124" s="3"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>166</v>
       </c>
       <c r="B125" t="s">
         <v>643</v>
       </c>
-      <c r="D125" s="3"/>
-      <c r="F125" s="3"/>
-      <c r="G125" s="3"/>
-      <c r="H125" s="3"/>
+      <c r="D125" s="3">
+        <v>2</v>
+      </c>
+      <c r="E125" t="s">
+        <v>990</v>
+      </c>
+      <c r="F125" s="3">
+        <v>1508</v>
+      </c>
+      <c r="G125" s="3">
+        <v>192</v>
+      </c>
+      <c r="H125" s="3">
+        <v>128</v>
+      </c>
       <c r="I125" s="3"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>167</v>
       </c>
       <c r="B126" t="s">
         <v>644</v>
       </c>
-      <c r="D126" s="3"/>
-      <c r="F126" s="3"/>
-      <c r="G126" s="3"/>
-      <c r="H126" s="3"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="6"/>
+      <c r="H126" s="6"/>
       <c r="I126" s="3"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>168</v>
       </c>
       <c r="B127" t="s">
         <v>645</v>
       </c>
-      <c r="D127" s="3"/>
-      <c r="F127" s="3"/>
-      <c r="G127" s="3"/>
-      <c r="H127" s="3"/>
+      <c r="D127" s="3">
+        <v>1</v>
+      </c>
+      <c r="E127" t="s">
+        <v>992</v>
+      </c>
+      <c r="F127" s="3">
+        <v>3439</v>
+      </c>
+      <c r="G127" s="3">
+        <v>128</v>
+      </c>
+      <c r="H127" s="3">
+        <v>64</v>
+      </c>
       <c r="I127" s="3"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>169</v>
       </c>
@@ -6826,7 +7530,7 @@
       <c r="H128" s="4"/>
       <c r="I128" s="3"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>170</v>
       </c>
@@ -6840,7 +7544,7 @@
       <c r="H129" s="4"/>
       <c r="I129" s="3"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>171</v>
       </c>
@@ -6854,7 +7558,7 @@
       <c r="H130" s="4"/>
       <c r="I130" s="3"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>172</v>
       </c>
@@ -6868,21 +7572,31 @@
       <c r="H131" s="4"/>
       <c r="I131" s="3"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>173</v>
       </c>
       <c r="B132" t="s">
         <v>650</v>
       </c>
-      <c r="D132" s="4"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="4"/>
-      <c r="G132" s="4"/>
-      <c r="H132" s="4"/>
+      <c r="D132" s="4">
+        <v>2</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>990</v>
+      </c>
+      <c r="F132" s="4">
+        <v>251</v>
+      </c>
+      <c r="G132" s="4">
+        <v>128</v>
+      </c>
+      <c r="H132" s="4">
+        <v>128</v>
+      </c>
       <c r="I132" s="3"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>174</v>
       </c>
@@ -6896,7 +7610,7 @@
       <c r="H133" s="4"/>
       <c r="I133" s="3"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>175</v>
       </c>
@@ -6910,7 +7624,7 @@
       <c r="H134" s="4"/>
       <c r="I134" s="3"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>176</v>
       </c>
@@ -6924,7 +7638,7 @@
       <c r="H135" s="4"/>
       <c r="I135" s="3"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>177</v>
       </c>
@@ -6938,59 +7652,103 @@
       <c r="H136" s="4"/>
       <c r="I136" s="3"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>178</v>
       </c>
       <c r="B137" t="s">
         <v>655</v>
       </c>
-      <c r="D137" s="3"/>
-      <c r="F137" s="3"/>
-      <c r="G137" s="3"/>
-      <c r="H137" s="3"/>
+      <c r="D137" s="3">
+        <v>1</v>
+      </c>
+      <c r="E137" t="s">
+        <v>962</v>
+      </c>
+      <c r="F137" s="3">
+        <v>462</v>
+      </c>
+      <c r="G137" s="3">
+        <v>64</v>
+      </c>
+      <c r="H137" s="3">
+        <v>64</v>
+      </c>
       <c r="I137" s="3"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>179</v>
       </c>
       <c r="B138" t="s">
         <v>656</v>
       </c>
-      <c r="D138" s="3"/>
-      <c r="F138" s="3"/>
-      <c r="G138" s="3"/>
-      <c r="H138" s="3"/>
+      <c r="D138" s="3">
+        <v>1</v>
+      </c>
+      <c r="E138" t="s">
+        <v>974</v>
+      </c>
+      <c r="F138" s="3">
+        <v>16897</v>
+      </c>
+      <c r="G138" s="3">
+        <v>128</v>
+      </c>
+      <c r="H138" s="3">
+        <v>64</v>
+      </c>
       <c r="I138" s="3"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>180</v>
       </c>
       <c r="B139" t="s">
         <v>657</v>
       </c>
-      <c r="D139" s="3"/>
-      <c r="F139" s="3"/>
-      <c r="G139" s="3"/>
-      <c r="H139" s="3"/>
+      <c r="D139" s="3">
+        <v>7</v>
+      </c>
+      <c r="E139" t="s">
+        <v>982</v>
+      </c>
+      <c r="F139" s="3">
+        <v>15471</v>
+      </c>
+      <c r="G139" s="3">
+        <v>896</v>
+      </c>
+      <c r="H139" s="3">
+        <v>448</v>
+      </c>
       <c r="I139" s="3"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>181</v>
       </c>
       <c r="B140" t="s">
         <v>658</v>
       </c>
-      <c r="D140" s="3"/>
-      <c r="F140" s="3"/>
-      <c r="G140" s="3"/>
-      <c r="H140" s="3"/>
+      <c r="D140" s="3">
+        <v>5</v>
+      </c>
+      <c r="E140" t="s">
+        <v>970</v>
+      </c>
+      <c r="F140" s="3">
+        <v>5540</v>
+      </c>
+      <c r="G140" s="3">
+        <v>448</v>
+      </c>
+      <c r="H140" s="3">
+        <v>320</v>
+      </c>
       <c r="I140" s="3"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>182</v>
       </c>
@@ -7003,7 +7761,7 @@
       <c r="H141" s="3"/>
       <c r="I141" s="3"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>183</v>
       </c>
@@ -7016,20 +7774,31 @@
       <c r="H142" s="3"/>
       <c r="I142" s="3"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>184</v>
       </c>
       <c r="B143" t="s">
         <v>661</v>
       </c>
-      <c r="D143" s="3"/>
-      <c r="F143" s="3"/>
-      <c r="G143" s="3"/>
-      <c r="H143" s="3"/>
+      <c r="D143" s="3">
+        <v>6</v>
+      </c>
+      <c r="E143" t="s">
+        <v>964</v>
+      </c>
+      <c r="F143" s="3">
+        <v>6646</v>
+      </c>
+      <c r="G143" s="3">
+        <v>768</v>
+      </c>
+      <c r="H143" s="3">
+        <v>384</v>
+      </c>
       <c r="I143" s="3"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>185</v>
       </c>
@@ -7042,20 +7811,31 @@
       <c r="H144" s="3"/>
       <c r="I144" s="3"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>186</v>
       </c>
       <c r="B145" t="s">
         <v>663</v>
       </c>
-      <c r="D145" s="3"/>
-      <c r="F145" s="3"/>
-      <c r="G145" s="3"/>
-      <c r="H145" s="3"/>
+      <c r="D145" s="3">
+        <v>6</v>
+      </c>
+      <c r="E145" t="s">
+        <v>964</v>
+      </c>
+      <c r="F145" s="3">
+        <v>22321</v>
+      </c>
+      <c r="G145" s="3">
+        <v>768</v>
+      </c>
+      <c r="H145" s="3">
+        <v>384</v>
+      </c>
       <c r="I145" s="3"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>187</v>
       </c>
@@ -7068,7 +7848,7 @@
       <c r="H146" s="3"/>
       <c r="I146" s="3"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>188</v>
       </c>
@@ -7081,7 +7861,7 @@
       <c r="H147" s="3"/>
       <c r="I147" s="3"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>189</v>
       </c>
@@ -7094,7 +7874,7 @@
       <c r="H148" s="3"/>
       <c r="I148" s="3"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>190</v>
       </c>
@@ -7107,7 +7887,7 @@
       <c r="H149" s="3"/>
       <c r="I149" s="3"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>191</v>
       </c>
@@ -7120,7 +7900,7 @@
       <c r="H150" s="3"/>
       <c r="I150" s="3"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>192</v>
       </c>
@@ -7133,7 +7913,7 @@
       <c r="H151" s="3"/>
       <c r="I151" s="3"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>193</v>
       </c>
@@ -7146,7 +7926,7 @@
       <c r="H152" s="3"/>
       <c r="I152" s="3"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>195</v>
       </c>
@@ -7160,7 +7940,7 @@
       <c r="H153" s="4"/>
       <c r="I153" s="3"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>196</v>
       </c>
@@ -7174,7 +7954,7 @@
       <c r="H154" s="4"/>
       <c r="I154" s="3"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>197</v>
       </c>
@@ -7188,7 +7968,7 @@
       <c r="H155" s="4"/>
       <c r="I155" s="3"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>199</v>
       </c>
@@ -7201,7 +7981,7 @@
       <c r="H156" s="3"/>
       <c r="I156" s="3"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>200</v>
       </c>
@@ -7214,7 +7994,7 @@
       <c r="H157" s="3"/>
       <c r="I157" s="3"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>205</v>
       </c>
@@ -7227,7 +8007,7 @@
       <c r="H158" s="3"/>
       <c r="I158" s="3"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>206</v>
       </c>
@@ -7240,7 +8020,7 @@
       <c r="H159" s="3"/>
       <c r="I159" s="3"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>207</v>
       </c>
@@ -7253,7 +8033,7 @@
       <c r="H160" s="3"/>
       <c r="I160" s="3"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>208</v>
       </c>
@@ -7266,7 +8046,7 @@
       <c r="H161" s="3"/>
       <c r="I161" s="3"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>209</v>
       </c>
@@ -7280,7 +8060,7 @@
       <c r="H162" s="4"/>
       <c r="I162" s="3"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>210</v>
       </c>
@@ -7294,7 +8074,7 @@
       <c r="H163" s="4"/>
       <c r="I163" s="3"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>211</v>
       </c>
@@ -7307,7 +8087,7 @@
       <c r="H164" s="3"/>
       <c r="I164" s="3"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>212</v>
       </c>
@@ -7320,7 +8100,7 @@
       <c r="H165" s="3"/>
       <c r="I165" s="3"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>213</v>
       </c>
@@ -7333,7 +8113,7 @@
       <c r="H166" s="3"/>
       <c r="I166" s="3"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>214</v>
       </c>
@@ -7347,7 +8127,7 @@
       <c r="H167" s="4"/>
       <c r="I167" s="3"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>215</v>
       </c>
@@ -7361,7 +8141,7 @@
       <c r="H168" s="4"/>
       <c r="I168" s="3"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>216</v>
       </c>
@@ -7374,7 +8154,7 @@
       <c r="H169" s="3"/>
       <c r="I169" s="3"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>217</v>
       </c>
@@ -7387,7 +8167,7 @@
       <c r="H170" s="3"/>
       <c r="I170" s="3"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>218</v>
       </c>
@@ -7400,7 +8180,7 @@
       <c r="H171" s="3"/>
       <c r="I171" s="3"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>219</v>
       </c>
@@ -7413,7 +8193,7 @@
       <c r="H172" s="3"/>
       <c r="I172" s="3"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>220</v>
       </c>
@@ -7426,7 +8206,7 @@
       <c r="H173" s="3"/>
       <c r="I173" s="3"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>221</v>
       </c>
@@ -7439,7 +8219,7 @@
       <c r="H174" s="3"/>
       <c r="I174" s="3"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>225</v>
       </c>
@@ -7452,7 +8232,7 @@
       <c r="H175" s="3"/>
       <c r="I175" s="3"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>226</v>
       </c>
@@ -7465,7 +8245,7 @@
       <c r="H176" s="3"/>
       <c r="I176" s="3"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>227</v>
       </c>
@@ -7478,7 +8258,7 @@
       <c r="H177" s="3"/>
       <c r="I177" s="3"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>228</v>
       </c>
@@ -7491,7 +8271,7 @@
       <c r="H178" s="3"/>
       <c r="I178" s="3"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>229</v>
       </c>
@@ -7504,7 +8284,7 @@
       <c r="H179" s="3"/>
       <c r="I179" s="3"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>230</v>
       </c>
@@ -7517,7 +8297,7 @@
       <c r="H180" s="3"/>
       <c r="I180" s="3"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>231</v>
       </c>
@@ -7530,7 +8310,7 @@
       <c r="H181" s="3"/>
       <c r="I181" s="3"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>232</v>
       </c>
@@ -7544,7 +8324,7 @@
       <c r="H182" s="4"/>
       <c r="I182" s="3"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>233</v>
       </c>
@@ -7558,7 +8338,7 @@
       <c r="H183" s="4"/>
       <c r="I183" s="3"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>234</v>
       </c>
@@ -7572,7 +8352,7 @@
       <c r="H184" s="4"/>
       <c r="I184" s="3"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>235</v>
       </c>
@@ -7585,7 +8365,7 @@
       <c r="H185" s="3"/>
       <c r="I185" s="3"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>236</v>
       </c>
@@ -7598,7 +8378,7 @@
       <c r="H186" s="3"/>
       <c r="I186" s="3"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>237</v>
       </c>
@@ -7611,7 +8391,7 @@
       <c r="H187" s="3"/>
       <c r="I187" s="3"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>238</v>
       </c>
@@ -7624,7 +8404,7 @@
       <c r="H188" s="3"/>
       <c r="I188" s="3"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>239</v>
       </c>
@@ -7637,7 +8417,7 @@
       <c r="H189" s="3"/>
       <c r="I189" s="3"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>240</v>
       </c>
@@ -7650,7 +8430,7 @@
       <c r="H190" s="3"/>
       <c r="I190" s="3"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>241</v>
       </c>
@@ -7663,7 +8443,7 @@
       <c r="H191" s="3"/>
       <c r="I191" s="3"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>242</v>
       </c>
@@ -7676,7 +8456,7 @@
       <c r="H192" s="3"/>
       <c r="I192" s="3"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>243</v>
       </c>
@@ -7689,7 +8469,7 @@
       <c r="H193" s="3"/>
       <c r="I193" s="3"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>244</v>
       </c>
@@ -7702,7 +8482,7 @@
       <c r="H194" s="3"/>
       <c r="I194" s="3"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>245</v>
       </c>
@@ -7715,7 +8495,7 @@
       <c r="H195" s="3"/>
       <c r="I195" s="3"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>246</v>
       </c>
@@ -7728,7 +8508,7 @@
       <c r="H196" s="3"/>
       <c r="I196" s="3"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>247</v>
       </c>
@@ -7742,7 +8522,7 @@
       <c r="H197" s="4"/>
       <c r="I197" s="3"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>248</v>
       </c>
@@ -7756,7 +8536,7 @@
       <c r="H198" s="4"/>
       <c r="I198" s="3"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>249</v>
       </c>
@@ -7769,7 +8549,7 @@
       <c r="H199" s="3"/>
       <c r="I199" s="3"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>250</v>
       </c>
@@ -7783,7 +8563,7 @@
       <c r="H200" s="4"/>
       <c r="I200" s="3"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>251</v>
       </c>
@@ -7797,7 +8577,7 @@
       <c r="H201" s="4"/>
       <c r="I201" s="3"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>252</v>
       </c>
@@ -7810,7 +8590,7 @@
       <c r="H202" s="3"/>
       <c r="I202" s="3"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>253</v>
       </c>
@@ -7823,7 +8603,7 @@
       <c r="H203" s="3"/>
       <c r="I203" s="3"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>254</v>
       </c>
@@ -7836,7 +8616,7 @@
       <c r="H204" s="3"/>
       <c r="I204" s="3"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>255</v>
       </c>
@@ -7850,7 +8630,7 @@
       <c r="H205" s="4"/>
       <c r="I205" s="3"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>256</v>
       </c>
@@ -7864,7 +8644,7 @@
       <c r="H206" s="4"/>
       <c r="I206" s="3"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>257</v>
       </c>
@@ -7878,7 +8658,7 @@
       <c r="H207" s="4"/>
       <c r="I207" s="3"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>258</v>
       </c>
@@ -7892,7 +8672,7 @@
       <c r="H208" s="4"/>
       <c r="I208" s="3"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>259</v>
       </c>
@@ -7905,7 +8685,7 @@
       <c r="H209" s="3"/>
       <c r="I209" s="3"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>260</v>
       </c>
@@ -7919,7 +8699,7 @@
       <c r="H210" s="4"/>
       <c r="I210" s="3"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>261</v>
       </c>
@@ -7933,7 +8713,7 @@
       <c r="H211" s="4"/>
       <c r="I211" s="3"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>262</v>
       </c>
@@ -7947,7 +8727,7 @@
       <c r="H212" s="4"/>
       <c r="I212" s="3"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>263</v>
       </c>
@@ -7961,7 +8741,7 @@
       <c r="H213" s="4"/>
       <c r="I213" s="3"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>264</v>
       </c>
@@ -7974,7 +8754,7 @@
       <c r="H214" s="3"/>
       <c r="I214" s="3"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>265</v>
       </c>
@@ -7987,7 +8767,7 @@
       <c r="H215" s="3"/>
       <c r="I215" s="3"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>266</v>
       </c>
@@ -8000,7 +8780,7 @@
       <c r="H216" s="3"/>
       <c r="I216" s="3"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>267</v>
       </c>
@@ -8013,7 +8793,7 @@
       <c r="H217" s="3"/>
       <c r="I217" s="3"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>268</v>
       </c>
@@ -8026,7 +8806,7 @@
       <c r="H218" s="3"/>
       <c r="I218" s="3"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>269</v>
       </c>
@@ -8039,7 +8819,7 @@
       <c r="H219" s="3"/>
       <c r="I219" s="3"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>270</v>
       </c>
@@ -8052,7 +8832,7 @@
       <c r="H220" s="3"/>
       <c r="I220" s="3"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>271</v>
       </c>
@@ -8065,7 +8845,7 @@
       <c r="H221" s="3"/>
       <c r="I221" s="3"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>272</v>
       </c>
@@ -8078,7 +8858,7 @@
       <c r="H222" s="3"/>
       <c r="I222" s="3"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>273</v>
       </c>
@@ -8091,7 +8871,7 @@
       <c r="H223" s="3"/>
       <c r="I223" s="3"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>274</v>
       </c>
@@ -8104,7 +8884,7 @@
       <c r="H224" s="3"/>
       <c r="I224" s="3"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>275</v>
       </c>
@@ -8118,7 +8898,7 @@
       <c r="H225" s="4"/>
       <c r="I225" s="3"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>276</v>
       </c>
@@ -8132,7 +8912,7 @@
       <c r="H226" s="4"/>
       <c r="I226" s="3"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>277</v>
       </c>
@@ -8145,7 +8925,7 @@
       <c r="H227" s="3"/>
       <c r="I227" s="3"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>278</v>
       </c>
@@ -8158,7 +8938,7 @@
       <c r="H228" s="3"/>
       <c r="I228" s="3"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>279</v>
       </c>
@@ -8171,7 +8951,7 @@
       <c r="H229" s="3"/>
       <c r="I229" s="3"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>280</v>
       </c>
@@ -8184,7 +8964,7 @@
       <c r="H230" s="3"/>
       <c r="I230" s="3"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>281</v>
       </c>
@@ -8197,7 +8977,7 @@
       <c r="H231" s="3"/>
       <c r="I231" s="3"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>282</v>
       </c>
@@ -8210,7 +8990,7 @@
       <c r="H232" s="3"/>
       <c r="I232" s="3"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>283</v>
       </c>
@@ -8223,7 +9003,7 @@
       <c r="H233" s="3"/>
       <c r="I233" s="3"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>284</v>
       </c>
@@ -8236,7 +9016,7 @@
       <c r="H234" s="3"/>
       <c r="I234" s="3"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>285</v>
       </c>
@@ -8249,7 +9029,7 @@
       <c r="H235" s="3"/>
       <c r="I235" s="3"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>286</v>
       </c>
@@ -8262,7 +9042,7 @@
       <c r="H236" s="3"/>
       <c r="I236" s="3"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>287</v>
       </c>
@@ -8275,7 +9055,7 @@
       <c r="H237" s="3"/>
       <c r="I237" s="3"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>288</v>
       </c>
@@ -8288,7 +9068,7 @@
       <c r="H238" s="3"/>
       <c r="I238" s="3"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>289</v>
       </c>
@@ -8301,7 +9081,7 @@
       <c r="H239" s="3"/>
       <c r="I239" s="3"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>290</v>
       </c>
@@ -8314,7 +9094,7 @@
       <c r="H240" s="3"/>
       <c r="I240" s="3"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>291</v>
       </c>
@@ -8327,7 +9107,7 @@
       <c r="H241" s="3"/>
       <c r="I241" s="3"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>292</v>
       </c>
@@ -8341,7 +9121,7 @@
       <c r="H242" s="4"/>
       <c r="I242" s="3"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>293</v>
       </c>
@@ -8355,7 +9135,7 @@
       <c r="H243" s="4"/>
       <c r="I243" s="3"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>294</v>
       </c>
@@ -8368,7 +9148,7 @@
       <c r="H244" s="3"/>
       <c r="I244" s="3"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>295</v>
       </c>
@@ -8381,7 +9161,7 @@
       <c r="H245" s="3"/>
       <c r="I245" s="3"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>296</v>
       </c>
@@ -8394,7 +9174,7 @@
       <c r="H246" s="3"/>
       <c r="I246" s="3"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>297</v>
       </c>
@@ -8407,7 +9187,7 @@
       <c r="H247" s="3"/>
       <c r="I247" s="3"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>298</v>
       </c>
@@ -8421,7 +9201,7 @@
       <c r="H248" s="4"/>
       <c r="I248" s="3"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>299</v>
       </c>
@@ -8435,7 +9215,7 @@
       <c r="H249" s="4"/>
       <c r="I249" s="3"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>300</v>
       </c>
@@ -8448,7 +9228,7 @@
       <c r="H250" s="3"/>
       <c r="I250" s="3"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>301</v>
       </c>
@@ -8461,7 +9241,7 @@
       <c r="H251" s="3"/>
       <c r="I251" s="3"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>302</v>
       </c>
@@ -8474,7 +9254,7 @@
       <c r="H252" s="3"/>
       <c r="I252" s="3"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>303</v>
       </c>
@@ -8488,7 +9268,7 @@
       <c r="H253" s="4"/>
       <c r="I253" s="3"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>304</v>
       </c>
@@ -8502,7 +9282,7 @@
       <c r="H254" s="4"/>
       <c r="I254" s="3"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>305</v>
       </c>
@@ -8515,7 +9295,7 @@
       <c r="H255" s="3"/>
       <c r="I255" s="3"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>306</v>
       </c>
@@ -8528,7 +9308,7 @@
       <c r="H256" s="3"/>
       <c r="I256" s="3"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>307</v>
       </c>
@@ -8542,7 +9322,7 @@
       <c r="H257" s="4"/>
       <c r="I257" s="3"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>308</v>
       </c>
@@ -8556,7 +9336,7 @@
       <c r="H258" s="4"/>
       <c r="I258" s="3"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>309</v>
       </c>
@@ -8569,7 +9349,7 @@
       <c r="H259" s="3"/>
       <c r="I259" s="3"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>310</v>
       </c>
@@ -8582,7 +9362,7 @@
       <c r="H260" s="3"/>
       <c r="I260" s="3"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>311</v>
       </c>
@@ -8595,7 +9375,7 @@
       <c r="H261" s="3"/>
       <c r="I261" s="3"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>312</v>
       </c>
@@ -8608,7 +9388,7 @@
       <c r="H262" s="3"/>
       <c r="I262" s="3"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>313</v>
       </c>
@@ -8621,7 +9401,7 @@
       <c r="H263" s="3"/>
       <c r="I263" s="3"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>314</v>
       </c>
@@ -8635,7 +9415,7 @@
       <c r="H264" s="4"/>
       <c r="I264" s="3"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>315</v>
       </c>
@@ -8649,7 +9429,7 @@
       <c r="H265" s="4"/>
       <c r="I265" s="3"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>316</v>
       </c>
@@ -8663,7 +9443,7 @@
       <c r="H266" s="4"/>
       <c r="I266" s="3"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>317</v>
       </c>
@@ -8677,7 +9457,7 @@
       <c r="H267" s="4"/>
       <c r="I267" s="3"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>318</v>
       </c>
@@ -8690,7 +9470,7 @@
       <c r="H268" s="3"/>
       <c r="I268" s="3"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>319</v>
       </c>
@@ -8703,7 +9483,7 @@
       <c r="H269" s="3"/>
       <c r="I269" s="3"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>320</v>
       </c>
@@ -8716,7 +9496,7 @@
       <c r="H270" s="3"/>
       <c r="I270" s="3"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>321</v>
       </c>
@@ -8729,7 +9509,7 @@
       <c r="H271" s="3"/>
       <c r="I271" s="3"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>322</v>
       </c>
@@ -8743,7 +9523,7 @@
       <c r="H272" s="4"/>
       <c r="I272" s="3"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>323</v>
       </c>
@@ -8757,7 +9537,7 @@
       <c r="H273" s="4"/>
       <c r="I273" s="3"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>324</v>
       </c>
@@ -8770,7 +9550,7 @@
       <c r="H274" s="3"/>
       <c r="I274" s="3"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>325</v>
       </c>
@@ -8783,7 +9563,7 @@
       <c r="H275" s="3"/>
       <c r="I275" s="3"/>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>326</v>
       </c>
@@ -8796,7 +9576,7 @@
       <c r="H276" s="3"/>
       <c r="I276" s="3"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>327</v>
       </c>
@@ -8809,7 +9589,7 @@
       <c r="H277" s="3"/>
       <c r="I277" s="3"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>328</v>
       </c>
@@ -8822,7 +9602,7 @@
       <c r="H278" s="3"/>
       <c r="I278" s="3"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>329</v>
       </c>
@@ -8835,7 +9615,7 @@
       <c r="H279" s="3"/>
       <c r="I279" s="3"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>331</v>
       </c>
@@ -8848,7 +9628,7 @@
       <c r="H280" s="3"/>
       <c r="I280" s="3"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>332</v>
       </c>
@@ -8862,7 +9642,7 @@
       <c r="H281" s="4"/>
       <c r="I281" s="3"/>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>333</v>
       </c>
@@ -8876,7 +9656,7 @@
       <c r="H282" s="4"/>
       <c r="I282" s="3"/>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>334</v>
       </c>
@@ -8889,7 +9669,7 @@
       <c r="H283" s="3"/>
       <c r="I283" s="3"/>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>335</v>
       </c>
@@ -8902,7 +9682,7 @@
       <c r="H284" s="3"/>
       <c r="I284" s="3"/>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>336</v>
       </c>
@@ -8915,7 +9695,7 @@
       <c r="H285" s="3"/>
       <c r="I285" s="3"/>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>337</v>
       </c>
@@ -8928,7 +9708,7 @@
       <c r="H286" s="3"/>
       <c r="I286" s="3"/>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>338</v>
       </c>
@@ -8941,7 +9721,7 @@
       <c r="H287" s="3"/>
       <c r="I287" s="3"/>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>339</v>
       </c>
@@ -8954,7 +9734,7 @@
       <c r="H288" s="3"/>
       <c r="I288" s="3"/>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>340</v>
       </c>
@@ -8967,7 +9747,7 @@
       <c r="H289" s="3"/>
       <c r="I289" s="3"/>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>341</v>
       </c>
@@ -8980,7 +9760,7 @@
       <c r="H290" s="3"/>
       <c r="I290" s="3"/>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>342</v>
       </c>
@@ -8993,7 +9773,7 @@
       <c r="H291" s="3"/>
       <c r="I291" s="3"/>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>343</v>
       </c>
@@ -9006,7 +9786,7 @@
       <c r="H292" s="3"/>
       <c r="I292" s="3"/>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>344</v>
       </c>
@@ -9019,7 +9799,7 @@
       <c r="H293" s="3"/>
       <c r="I293" s="3"/>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>345</v>
       </c>
@@ -9033,7 +9813,7 @@
       <c r="H294" s="4"/>
       <c r="I294" s="3"/>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>346</v>
       </c>
@@ -9047,7 +9827,7 @@
       <c r="H295" s="4"/>
       <c r="I295" s="3"/>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>347</v>
       </c>
@@ -9060,7 +9840,7 @@
       <c r="H296" s="3"/>
       <c r="I296" s="3"/>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>348</v>
       </c>
@@ -9073,7 +9853,7 @@
       <c r="H297" s="3"/>
       <c r="I297" s="3"/>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>349</v>
       </c>
@@ -9086,7 +9866,7 @@
       <c r="H298" s="3"/>
       <c r="I298" s="3"/>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>350</v>
       </c>
@@ -9099,7 +9879,7 @@
       <c r="H299" s="3"/>
       <c r="I299" s="3"/>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>351</v>
       </c>
@@ -9112,7 +9892,7 @@
       <c r="H300" s="3"/>
       <c r="I300" s="3"/>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>352</v>
       </c>
@@ -9125,7 +9905,7 @@
       <c r="H301" s="3"/>
       <c r="I301" s="3"/>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>353</v>
       </c>
@@ -9138,7 +9918,7 @@
       <c r="H302" s="3"/>
       <c r="I302" s="3"/>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>354</v>
       </c>
@@ -9151,7 +9931,7 @@
       <c r="H303" s="3"/>
       <c r="I303" s="3"/>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>355</v>
       </c>
@@ -9164,7 +9944,7 @@
       <c r="H304" s="3"/>
       <c r="I304" s="3"/>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>356</v>
       </c>
@@ -9177,7 +9957,7 @@
       <c r="H305" s="3"/>
       <c r="I305" s="3"/>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>357</v>
       </c>
@@ -9190,7 +9970,7 @@
       <c r="H306" s="3"/>
       <c r="I306" s="3"/>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>358</v>
       </c>
@@ -9203,7 +9983,7 @@
       <c r="H307" s="3"/>
       <c r="I307" s="3"/>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>359</v>
       </c>
@@ -9216,7 +9996,7 @@
       <c r="H308" s="3"/>
       <c r="I308" s="3"/>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>360</v>
       </c>
@@ -9229,7 +10009,7 @@
       <c r="H309" s="3"/>
       <c r="I309" s="3"/>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>361</v>
       </c>
@@ -9242,7 +10022,7 @@
       <c r="H310" s="3"/>
       <c r="I310" s="3"/>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>362</v>
       </c>
@@ -9255,7 +10035,7 @@
       <c r="H311" s="3"/>
       <c r="I311" s="3"/>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>363</v>
       </c>
@@ -9268,7 +10048,7 @@
       <c r="H312" s="3"/>
       <c r="I312" s="3"/>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>364</v>
       </c>
@@ -9281,7 +10061,7 @@
       <c r="H313" s="3"/>
       <c r="I313" s="3"/>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>365</v>
       </c>
@@ -9295,7 +10075,7 @@
       <c r="H314" s="4"/>
       <c r="I314" s="3"/>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>366</v>
       </c>
@@ -9309,7 +10089,7 @@
       <c r="H315" s="4"/>
       <c r="I315" s="3"/>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>367</v>
       </c>
@@ -9322,7 +10102,7 @@
       <c r="H316" s="3"/>
       <c r="I316" s="3"/>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>368</v>
       </c>
@@ -9336,7 +10116,7 @@
       <c r="H317" s="4"/>
       <c r="I317" s="3"/>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>369</v>
       </c>
@@ -9350,7 +10130,7 @@
       <c r="H318" s="4"/>
       <c r="I318" s="3"/>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>370</v>
       </c>
@@ -9364,7 +10144,7 @@
       <c r="H319" s="4"/>
       <c r="I319" s="3"/>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>371</v>
       </c>
@@ -9378,7 +10158,7 @@
       <c r="H320" s="4"/>
       <c r="I320" s="3"/>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>372</v>
       </c>
@@ -9392,7 +10172,7 @@
       <c r="H321" s="4"/>
       <c r="I321" s="3"/>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>373</v>
       </c>
@@ -9405,7 +10185,7 @@
       <c r="H322" s="3"/>
       <c r="I322" s="3"/>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>374</v>
       </c>
@@ -9418,7 +10198,7 @@
       <c r="H323" s="3"/>
       <c r="I323" s="3"/>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>375</v>
       </c>
@@ -9432,7 +10212,7 @@
       <c r="H324" s="4"/>
       <c r="I324" s="3"/>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>376</v>
       </c>
@@ -9446,7 +10226,7 @@
       <c r="H325" s="4"/>
       <c r="I325" s="3"/>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>377</v>
       </c>
@@ -9460,7 +10240,7 @@
       <c r="H326" s="4"/>
       <c r="I326" s="3"/>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>378</v>
       </c>
@@ -9474,7 +10254,7 @@
       <c r="H327" s="4"/>
       <c r="I327" s="3"/>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>379</v>
       </c>
@@ -9487,7 +10267,7 @@
       <c r="H328" s="3"/>
       <c r="I328" s="3"/>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>380</v>
       </c>
@@ -9500,7 +10280,7 @@
       <c r="H329" s="3"/>
       <c r="I329" s="3"/>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>381</v>
       </c>
@@ -9513,7 +10293,7 @@
       <c r="H330" s="3"/>
       <c r="I330" s="3"/>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>382</v>
       </c>
@@ -9526,7 +10306,7 @@
       <c r="H331" s="3"/>
       <c r="I331" s="3"/>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>383</v>
       </c>
@@ -9539,7 +10319,7 @@
       <c r="H332" s="3"/>
       <c r="I332" s="3"/>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>384</v>
       </c>
@@ -9552,7 +10332,7 @@
       <c r="H333" s="3"/>
       <c r="I333" s="3"/>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>385</v>
       </c>
@@ -9565,7 +10345,7 @@
       <c r="H334" s="3"/>
       <c r="I334" s="3"/>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>386</v>
       </c>
@@ -9578,7 +10358,7 @@
       <c r="H335" s="3"/>
       <c r="I335" s="3"/>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>387</v>
       </c>
@@ -9591,7 +10371,7 @@
       <c r="H336" s="3"/>
       <c r="I336" s="3"/>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>388</v>
       </c>
@@ -9604,7 +10384,7 @@
       <c r="H337" s="3"/>
       <c r="I337" s="3"/>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>389</v>
       </c>
@@ -9617,7 +10397,7 @@
       <c r="H338" s="3"/>
       <c r="I338" s="3"/>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>390</v>
       </c>
@@ -9630,7 +10410,7 @@
       <c r="H339" s="3"/>
       <c r="I339" s="3"/>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>391</v>
       </c>
@@ -9643,7 +10423,7 @@
       <c r="H340" s="3"/>
       <c r="I340" s="3"/>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>392</v>
       </c>
@@ -9656,7 +10436,7 @@
       <c r="H341" s="3"/>
       <c r="I341" s="3"/>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>393</v>
       </c>
@@ -9669,7 +10449,7 @@
       <c r="H342" s="3"/>
       <c r="I342" s="3"/>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>394</v>
       </c>
@@ -9682,7 +10462,7 @@
       <c r="H343" s="3"/>
       <c r="I343" s="3"/>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>395</v>
       </c>
@@ -9696,7 +10476,7 @@
       <c r="H344" s="4"/>
       <c r="I344" s="3"/>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>396</v>
       </c>
@@ -9710,7 +10490,7 @@
       <c r="H345" s="4"/>
       <c r="I345" s="3"/>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>397</v>
       </c>
@@ -9723,7 +10503,7 @@
       <c r="H346" s="3"/>
       <c r="I346" s="3"/>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>398</v>
       </c>
@@ -9736,7 +10516,7 @@
       <c r="H347" s="3"/>
       <c r="I347" s="3"/>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>399</v>
       </c>
@@ -9749,7 +10529,7 @@
       <c r="H348" s="3"/>
       <c r="I348" s="3"/>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>400</v>
       </c>
@@ -9762,7 +10542,7 @@
       <c r="H349" s="3"/>
       <c r="I349" s="3"/>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>401</v>
       </c>
@@ -9775,7 +10555,7 @@
       <c r="H350" s="3"/>
       <c r="I350" s="3"/>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>402</v>
       </c>
@@ -9788,7 +10568,7 @@
       <c r="H351" s="3"/>
       <c r="I351" s="3"/>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>403</v>
       </c>
@@ -9801,7 +10581,7 @@
       <c r="H352" s="3"/>
       <c r="I352" s="3"/>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>404</v>
       </c>
@@ -9814,7 +10594,7 @@
       <c r="H353" s="3"/>
       <c r="I353" s="3"/>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>405</v>
       </c>
@@ -9827,7 +10607,7 @@
       <c r="H354" s="3"/>
       <c r="I354" s="3"/>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>406</v>
       </c>
@@ -9840,7 +10620,7 @@
       <c r="H355" s="3"/>
       <c r="I355" s="3"/>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>407</v>
       </c>
@@ -9853,7 +10633,7 @@
       <c r="H356" s="3"/>
       <c r="I356" s="3"/>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>408</v>
       </c>
@@ -9866,7 +10646,7 @@
       <c r="H357" s="3"/>
       <c r="I357" s="3"/>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>409</v>
       </c>
@@ -9879,7 +10659,7 @@
       <c r="H358" s="3"/>
       <c r="I358" s="3"/>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>410</v>
       </c>
@@ -9892,7 +10672,7 @@
       <c r="H359" s="3"/>
       <c r="I359" s="3"/>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>411</v>
       </c>
@@ -9905,7 +10685,7 @@
       <c r="H360" s="3"/>
       <c r="I360" s="3"/>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>412</v>
       </c>
@@ -9918,7 +10698,7 @@
       <c r="H361" s="3"/>
       <c r="I361" s="3"/>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>413</v>
       </c>
@@ -9931,7 +10711,7 @@
       <c r="H362" s="3"/>
       <c r="I362" s="3"/>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>414</v>
       </c>
@@ -9944,7 +10724,7 @@
       <c r="H363" s="3"/>
       <c r="I363" s="3"/>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>415</v>
       </c>
@@ -9957,7 +10737,7 @@
       <c r="H364" s="3"/>
       <c r="I364" s="3"/>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>416</v>
       </c>
@@ -9970,7 +10750,7 @@
       <c r="H365" s="3"/>
       <c r="I365" s="3"/>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>417</v>
       </c>
@@ -9983,7 +10763,7 @@
       <c r="H366" s="3"/>
       <c r="I366" s="3"/>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>418</v>
       </c>
@@ -9996,7 +10776,7 @@
       <c r="H367" s="3"/>
       <c r="I367" s="3"/>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>419</v>
       </c>
@@ -10009,7 +10789,7 @@
       <c r="H368" s="3"/>
       <c r="I368" s="3"/>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>420</v>
       </c>
@@ -10022,7 +10802,7 @@
       <c r="H369" s="3"/>
       <c r="I369" s="3"/>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>421</v>
       </c>
@@ -10035,7 +10815,7 @@
       <c r="H370" s="3"/>
       <c r="I370" s="3"/>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>422</v>
       </c>
@@ -10048,7 +10828,7 @@
       <c r="H371" s="3"/>
       <c r="I371" s="3"/>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>423</v>
       </c>
@@ -10061,7 +10841,7 @@
       <c r="H372" s="3"/>
       <c r="I372" s="3"/>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>424</v>
       </c>
@@ -10074,7 +10854,7 @@
       <c r="H373" s="3"/>
       <c r="I373" s="3"/>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>425</v>
       </c>
@@ -10087,7 +10867,7 @@
       <c r="H374" s="3"/>
       <c r="I374" s="3"/>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>426</v>
       </c>
@@ -10101,7 +10881,7 @@
       <c r="H375" s="4"/>
       <c r="I375" s="3"/>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>427</v>
       </c>
@@ -10115,7 +10895,7 @@
       <c r="H376" s="4"/>
       <c r="I376" s="3"/>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>429</v>
       </c>
@@ -10128,7 +10908,7 @@
       <c r="H377" s="3"/>
       <c r="I377" s="3"/>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>430</v>
       </c>
@@ -10141,7 +10921,7 @@
       <c r="H378" s="3"/>
       <c r="I378" s="3"/>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>431</v>
       </c>
@@ -10154,7 +10934,7 @@
       <c r="H379" s="3"/>
       <c r="I379" s="3"/>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>432</v>
       </c>
@@ -10167,7 +10947,7 @@
       <c r="H380" s="3"/>
       <c r="I380" s="3"/>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>433</v>
       </c>
@@ -10180,7 +10960,7 @@
       <c r="H381" s="3"/>
       <c r="I381" s="3"/>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>434</v>
       </c>
@@ -10193,7 +10973,7 @@
       <c r="H382" s="3"/>
       <c r="I382" s="3"/>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>435</v>
       </c>
@@ -10206,7 +10986,7 @@
       <c r="H383" s="3"/>
       <c r="I383" s="3"/>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>436</v>
       </c>
@@ -10219,7 +10999,7 @@
       <c r="H384" s="3"/>
       <c r="I384" s="3"/>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>437</v>
       </c>
@@ -10232,7 +11012,7 @@
       <c r="H385" s="3"/>
       <c r="I385" s="3"/>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>438</v>
       </c>
@@ -10245,7 +11025,7 @@
       <c r="H386" s="3"/>
       <c r="I386" s="3"/>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>439</v>
       </c>
@@ -10258,7 +11038,7 @@
       <c r="H387" s="3"/>
       <c r="I387" s="3"/>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>440</v>
       </c>
@@ -10271,7 +11051,7 @@
       <c r="H388" s="3"/>
       <c r="I388" s="3"/>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>441</v>
       </c>
@@ -10284,7 +11064,7 @@
       <c r="H389" s="3"/>
       <c r="I389" s="3"/>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>442</v>
       </c>
@@ -10297,7 +11077,7 @@
       <c r="H390" s="3"/>
       <c r="I390" s="3"/>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>443</v>
       </c>
@@ -10310,7 +11090,7 @@
       <c r="H391" s="3"/>
       <c r="I391" s="3"/>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>444</v>
       </c>
@@ -10323,7 +11103,7 @@
       <c r="H392" s="3"/>
       <c r="I392" s="3"/>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>445</v>
       </c>
@@ -10336,7 +11116,7 @@
       <c r="H393" s="3"/>
       <c r="I393" s="3"/>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>446</v>
       </c>
@@ -10349,7 +11129,7 @@
       <c r="H394" s="3"/>
       <c r="I394" s="3"/>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>447</v>
       </c>
@@ -10362,7 +11142,7 @@
       <c r="H395" s="3"/>
       <c r="I395" s="3"/>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>448</v>
       </c>
@@ -10375,7 +11155,7 @@
       <c r="H396" s="3"/>
       <c r="I396" s="3"/>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>449</v>
       </c>
@@ -10388,7 +11168,7 @@
       <c r="H397" s="3"/>
       <c r="I397" s="3"/>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>450</v>
       </c>
@@ -10401,7 +11181,7 @@
       <c r="H398" s="3"/>
       <c r="I398" s="3"/>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>451</v>
       </c>
@@ -10415,7 +11195,7 @@
       <c r="H399" s="4"/>
       <c r="I399" s="3"/>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>452</v>
       </c>
@@ -10429,7 +11209,7 @@
       <c r="H400" s="4"/>
       <c r="I400" s="3"/>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>453</v>
       </c>
@@ -10442,7 +11222,7 @@
       <c r="H401" s="3"/>
       <c r="I401" s="3"/>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>454</v>
       </c>
@@ -10455,7 +11235,7 @@
       <c r="H402" s="3"/>
       <c r="I402" s="3"/>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>455</v>
       </c>
@@ -10468,7 +11248,7 @@
       <c r="H403" s="3"/>
       <c r="I403" s="3"/>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>456</v>
       </c>
@@ -10481,7 +11261,7 @@
       <c r="H404" s="3"/>
       <c r="I404" s="3"/>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>457</v>
       </c>
@@ -10494,7 +11274,7 @@
       <c r="H405" s="3"/>
       <c r="I405" s="3"/>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>458</v>
       </c>
@@ -10507,7 +11287,7 @@
       <c r="H406" s="3"/>
       <c r="I406" s="3"/>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>459</v>
       </c>
@@ -10520,7 +11300,7 @@
       <c r="H407" s="3"/>
       <c r="I407" s="3"/>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>460</v>
       </c>
@@ -10533,7 +11313,7 @@
       <c r="H408" s="3"/>
       <c r="I408" s="3"/>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>461</v>
       </c>
@@ -10546,7 +11326,7 @@
       <c r="H409" s="3"/>
       <c r="I409" s="3"/>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>462</v>
       </c>
@@ -10559,7 +11339,7 @@
       <c r="H410" s="3"/>
       <c r="I410" s="3"/>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>463</v>
       </c>
@@ -10572,7 +11352,7 @@
       <c r="H411" s="3"/>
       <c r="I411" s="3"/>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>464</v>
       </c>
@@ -10585,7 +11365,7 @@
       <c r="H412" s="3"/>
       <c r="I412" s="3"/>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>465</v>
       </c>
@@ -10598,7 +11378,7 @@
       <c r="H413" s="3"/>
       <c r="I413" s="3"/>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>466</v>
       </c>
@@ -10611,7 +11391,7 @@
       <c r="H414" s="3"/>
       <c r="I414" s="3"/>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>467</v>
       </c>
@@ -10625,7 +11405,7 @@
       <c r="H415" s="4"/>
       <c r="I415" s="3"/>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>468</v>
       </c>
@@ -10639,7 +11419,7 @@
       <c r="H416" s="4"/>
       <c r="I416" s="3"/>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>469</v>
       </c>
@@ -10653,7 +11433,7 @@
       <c r="H417" s="4"/>
       <c r="I417" s="3"/>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>470</v>
       </c>
@@ -10667,7 +11447,7 @@
       <c r="H418" s="4"/>
       <c r="I418" s="3"/>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>471</v>
       </c>
@@ -10680,7 +11460,7 @@
       <c r="H419" s="3"/>
       <c r="I419" s="3"/>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>472</v>
       </c>
@@ -10693,7 +11473,7 @@
       <c r="H420" s="3"/>
       <c r="I420" s="3"/>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>473</v>
       </c>
@@ -10706,7 +11486,7 @@
       <c r="H421" s="3"/>
       <c r="I421" s="3"/>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>474</v>
       </c>
@@ -10719,7 +11499,7 @@
       <c r="H422" s="3"/>
       <c r="I422" s="3"/>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>475</v>
       </c>
@@ -10732,7 +11512,7 @@
       <c r="H423" s="3"/>
       <c r="I423" s="3"/>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>476</v>
       </c>
@@ -10745,7 +11525,7 @@
       <c r="H424" s="3"/>
       <c r="I424" s="3"/>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>477</v>
       </c>
@@ -10759,7 +11539,7 @@
       <c r="H425" s="4"/>
       <c r="I425" s="3"/>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>478</v>
       </c>
@@ -10773,7 +11553,7 @@
       <c r="H426" s="4"/>
       <c r="I426" s="3"/>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>479</v>
       </c>
@@ -10786,7 +11566,7 @@
       <c r="H427" s="3"/>
       <c r="I427" s="3"/>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>480</v>
       </c>
@@ -10799,7 +11579,7 @@
       <c r="H428" s="3"/>
       <c r="I428" s="3"/>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>481</v>
       </c>
@@ -10812,7 +11592,7 @@
       <c r="H429" s="3"/>
       <c r="I429" s="3"/>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>482</v>
       </c>
@@ -10825,7 +11605,7 @@
       <c r="H430" s="3"/>
       <c r="I430" s="3"/>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>483</v>
       </c>
@@ -10838,7 +11618,7 @@
       <c r="H431" s="3"/>
       <c r="I431" s="3"/>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>484</v>
       </c>
@@ -10852,7 +11632,7 @@
       <c r="H432" s="4"/>
       <c r="I432" s="3"/>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>485</v>
       </c>
@@ -10866,7 +11646,7 @@
       <c r="H433" s="4"/>
       <c r="I433" s="3"/>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>486</v>
       </c>
@@ -10879,7 +11659,7 @@
       <c r="H434" s="3"/>
       <c r="I434" s="3"/>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>487</v>
       </c>
@@ -10892,21 +11672,21 @@
       <c r="H435" s="3"/>
       <c r="I435" s="3"/>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D436" s="3"/>
       <c r="F436" s="3"/>
       <c r="G436" s="3"/>
       <c r="H436" s="3"/>
       <c r="I436" s="3"/>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D437" s="3"/>
       <c r="F437" s="3"/>
       <c r="G437" s="3"/>
       <c r="H437" s="3"/>
       <c r="I437" s="3"/>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D438" s="3"/>
       <c r="F438" s="3"/>
       <c r="G438" s="3"/>
@@ -10926,14 +11706,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040BF47F-E9DD-47FE-8A77-28B9CE7118A4}">
   <dimension ref="B1:E421"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="80.33203125" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="3" max="3" width="80.28515625" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>33</v>
       </c>
@@ -10947,7 +11727,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>288</v>
       </c>
@@ -10959,7 +11739,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>282</v>
       </c>
@@ -10971,7 +11751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>318</v>
       </c>
@@ -10983,7 +11763,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>288</v>
       </c>
@@ -10995,7 +11775,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>231</v>
       </c>
@@ -11007,7 +11787,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>288</v>
       </c>
@@ -11019,7 +11799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>318</v>
       </c>
@@ -11031,7 +11811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>318</v>
       </c>
@@ -11043,7 +11823,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>318</v>
       </c>
@@ -11055,7 +11835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>318</v>
       </c>
@@ -11067,7 +11847,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>318</v>
       </c>
@@ -11079,7 +11859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>318</v>
       </c>
@@ -11091,7 +11871,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>318</v>
       </c>
@@ -11103,7 +11883,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>180</v>
       </c>
@@ -11115,7 +11895,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>152</v>
       </c>
@@ -11127,7 +11907,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>231</v>
       </c>
@@ -11139,7 +11919,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>115</v>
       </c>
@@ -11151,7 +11931,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>115</v>
       </c>
@@ -11163,7 +11943,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>282</v>
       </c>
@@ -11175,7 +11955,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>264</v>
       </c>
@@ -11187,7 +11967,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>330</v>
       </c>
@@ -11199,7 +11979,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>330</v>
       </c>
@@ -11211,7 +11991,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>335</v>
       </c>
@@ -11223,7 +12003,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>71</v>
       </c>
@@ -11235,7 +12015,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>71</v>
       </c>
@@ -11247,7 +12027,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>61</v>
       </c>
@@ -11259,7 +12039,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>71</v>
       </c>
@@ -11271,7 +12051,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>71</v>
       </c>
@@ -11283,7 +12063,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>86</v>
       </c>
@@ -11295,7 +12075,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>86</v>
       </c>
@@ -11307,7 +12087,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>67</v>
       </c>
@@ -11319,7 +12099,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>139</v>
       </c>
@@ -11331,7 +12111,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>166</v>
       </c>
@@ -11343,7 +12123,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>52</v>
       </c>
@@ -11355,7 +12135,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>52</v>
       </c>
@@ -11367,7 +12147,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>195</v>
       </c>
@@ -11379,7 +12159,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>52</v>
       </c>
@@ -11391,7 +12171,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>238</v>
       </c>
@@ -11403,7 +12183,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>243</v>
       </c>
@@ -11415,7 +12195,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>360</v>
       </c>
@@ -11427,7 +12207,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>243</v>
       </c>
@@ -11439,7 +12219,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>180</v>
       </c>
@@ -11451,7 +12231,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>152</v>
       </c>
@@ -11463,7 +12243,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>335</v>
       </c>
@@ -11475,7 +12255,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>166</v>
       </c>
@@ -11487,7 +12267,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>335</v>
       </c>
@@ -11499,7 +12279,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>166</v>
       </c>
@@ -11511,7 +12291,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>330</v>
       </c>
@@ -11523,7 +12303,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>231</v>
       </c>
@@ -11535,7 +12315,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>152</v>
       </c>
@@ -11547,7 +12327,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>238</v>
       </c>
@@ -11559,7 +12339,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>335</v>
       </c>
@@ -11571,7 +12351,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>152</v>
       </c>
@@ -11583,7 +12363,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>152</v>
       </c>
@@ -11595,7 +12375,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>335</v>
       </c>
@@ -11607,7 +12387,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>335</v>
       </c>
@@ -11619,7 +12399,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>152</v>
       </c>
@@ -11631,7 +12411,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>270</v>
       </c>
@@ -11643,7 +12423,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>308</v>
       </c>
@@ -11655,7 +12435,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>270</v>
       </c>
@@ -11667,7 +12447,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>80</v>
       </c>
@@ -11679,7 +12459,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>308</v>
       </c>
@@ -11691,7 +12471,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>270</v>
       </c>
@@ -11703,7 +12483,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>308</v>
       </c>
@@ -11715,7 +12495,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>308</v>
       </c>
@@ -11727,7 +12507,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>80</v>
       </c>
@@ -11739,7 +12519,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>355</v>
       </c>
@@ -11751,7 +12531,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>308</v>
       </c>
@@ -11763,7 +12543,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>355</v>
       </c>
@@ -11775,7 +12555,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>308</v>
       </c>
@@ -11787,7 +12567,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>355</v>
       </c>
@@ -11799,7 +12579,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>260</v>
       </c>
@@ -11811,7 +12591,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>260</v>
       </c>
@@ -11823,7 +12603,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>260</v>
       </c>
@@ -11835,7 +12615,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>260</v>
       </c>
@@ -11847,7 +12627,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>260</v>
       </c>
@@ -11859,7 +12639,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>260</v>
       </c>
@@ -11871,7 +12651,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>260</v>
       </c>
@@ -11883,7 +12663,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>260</v>
       </c>
@@ -11895,7 +12675,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>260</v>
       </c>
@@ -11907,7 +12687,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>260</v>
       </c>
@@ -11919,7 +12699,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>260</v>
       </c>
@@ -11931,7 +12711,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>260</v>
       </c>
@@ -11943,7 +12723,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>260</v>
       </c>
@@ -11955,7 +12735,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
         <v>218</v>
       </c>
@@ -11967,7 +12747,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>218</v>
       </c>
@@ -11979,7 +12759,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>218</v>
       </c>
@@ -11991,7 +12771,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>103</v>
       </c>
@@ -12003,7 +12783,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>103</v>
       </c>
@@ -12015,7 +12795,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>103</v>
       </c>
@@ -12027,7 +12807,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>103</v>
       </c>
@@ -12039,7 +12819,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
         <v>103</v>
       </c>
@@ -12051,7 +12831,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
         <v>103</v>
       </c>
@@ -12063,7 +12843,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>103</v>
       </c>
@@ -12075,7 +12855,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>103</v>
       </c>
@@ -12087,7 +12867,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>103</v>
       </c>
@@ -12099,7 +12879,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>243</v>
       </c>
@@ -12111,7 +12891,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>231</v>
       </c>
@@ -12123,7 +12903,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>330</v>
       </c>
@@ -12135,7 +12915,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>238</v>
       </c>
@@ -12147,7 +12927,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>103</v>
       </c>
@@ -12159,7 +12939,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>103</v>
       </c>
@@ -12171,7 +12951,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>166</v>
       </c>
@@ -12183,7 +12963,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>335</v>
       </c>
@@ -12195,7 +12975,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>166</v>
       </c>
@@ -12207,7 +12987,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>152</v>
       </c>
@@ -12219,7 +12999,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>166</v>
       </c>
@@ -12231,7 +13011,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>166</v>
       </c>
@@ -12243,7 +13023,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>335</v>
       </c>
@@ -12255,7 +13035,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>218</v>
       </c>
@@ -12267,7 +13047,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>152</v>
       </c>
@@ -12279,7 +13059,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>218</v>
       </c>
@@ -12291,7 +13071,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>218</v>
       </c>
@@ -12303,7 +13083,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>335</v>
       </c>
@@ -12315,7 +13095,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
         <v>166</v>
       </c>
@@ -12327,7 +13107,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
         <v>166</v>
       </c>
@@ -12339,7 +13119,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>103</v>
       </c>
@@ -12351,7 +13131,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>103</v>
       </c>
@@ -12363,7 +13143,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
         <v>103</v>
       </c>
@@ -12375,7 +13155,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>103</v>
       </c>
@@ -12387,7 +13167,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>103</v>
       </c>
@@ -12399,7 +13179,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>103</v>
       </c>
@@ -12411,7 +13191,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>103</v>
       </c>
@@ -12423,7 +13203,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>133</v>
       </c>
@@ -12435,7 +13215,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
         <v>243</v>
       </c>
@@ -12447,7 +13227,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>243</v>
       </c>
@@ -12459,7 +13239,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>243</v>
       </c>
@@ -12471,7 +13251,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>152</v>
       </c>
@@ -12483,7 +13263,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>335</v>
       </c>
@@ -12495,7 +13275,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
         <v>166</v>
       </c>
@@ -12507,7 +13287,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
         <v>335</v>
       </c>
@@ -12519,7 +13299,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
         <v>335</v>
       </c>
@@ -12531,7 +13311,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
         <v>335</v>
       </c>
@@ -12543,7 +13323,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
         <v>260</v>
       </c>
@@ -12555,7 +13335,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
         <v>260</v>
       </c>
@@ -12567,7 +13347,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
         <v>260</v>
       </c>
@@ -12579,7 +13359,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
         <v>218</v>
       </c>
@@ -12591,7 +13371,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
         <v>335</v>
       </c>
@@ -12603,7 +13383,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
         <v>218</v>
       </c>
@@ -12615,7 +13395,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
         <v>335</v>
       </c>
@@ -12627,7 +13407,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
         <v>152</v>
       </c>
@@ -12639,7 +13419,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
         <v>152</v>
       </c>
@@ -12651,7 +13431,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
         <v>166</v>
       </c>
@@ -12663,7 +13443,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
         <v>152</v>
       </c>
@@ -12675,7 +13455,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
         <v>330</v>
       </c>
@@ -12687,7 +13467,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
         <v>166</v>
       </c>
@@ -12699,7 +13479,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
         <v>166</v>
       </c>
@@ -12711,7 +13491,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
         <v>335</v>
       </c>
@@ -12723,7 +13503,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
         <v>238</v>
       </c>
@@ -12735,7 +13515,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
         <v>335</v>
       </c>
@@ -12747,7 +13527,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
         <v>218</v>
       </c>
@@ -12759,7 +13539,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
         <v>152</v>
       </c>
@@ -12771,7 +13551,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
         <v>335</v>
       </c>
@@ -12783,7 +13563,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
         <v>270</v>
       </c>
@@ -12795,7 +13575,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
         <v>133</v>
       </c>
@@ -12807,7 +13587,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
         <v>133</v>
       </c>
@@ -12819,7 +13599,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
         <v>231</v>
       </c>
@@ -12831,7 +13611,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
         <v>231</v>
       </c>
@@ -12843,7 +13623,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
         <v>288</v>
       </c>
@@ -12855,7 +13635,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
         <v>288</v>
       </c>
@@ -12867,7 +13647,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
         <v>288</v>
       </c>
@@ -12879,7 +13659,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
         <v>288</v>
       </c>
@@ -12891,7 +13671,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
         <v>288</v>
       </c>
@@ -12903,7 +13683,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
         <v>288</v>
       </c>
@@ -12915,7 +13695,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
         <v>288</v>
       </c>
@@ -12927,7 +13707,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
         <v>115</v>
       </c>
@@ -12939,7 +13719,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
         <v>288</v>
       </c>
@@ -12951,7 +13731,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
         <v>103</v>
       </c>
@@ -12963,7 +13743,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B170" t="s">
         <v>103</v>
       </c>
@@ -12975,7 +13755,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
         <v>103</v>
       </c>
@@ -12987,7 +13767,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
         <v>103</v>
       </c>
@@ -12999,7 +13779,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
         <v>133</v>
       </c>
@@ -13011,7 +13791,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>133</v>
       </c>
@@ -13023,7 +13803,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
         <v>355</v>
       </c>
@@ -13035,7 +13815,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
         <v>249</v>
       </c>
@@ -13047,7 +13827,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
         <v>103</v>
       </c>
@@ -13059,7 +13839,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
         <v>103</v>
       </c>
@@ -13071,7 +13851,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>115</v>
       </c>
@@ -13083,7 +13863,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
         <v>115</v>
       </c>
@@ -13095,7 +13875,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
         <v>115</v>
       </c>
@@ -13107,7 +13887,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
         <v>139</v>
       </c>
@@ -13119,7 +13899,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
         <v>139</v>
       </c>
@@ -13131,7 +13911,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
         <v>139</v>
       </c>
@@ -13143,7 +13923,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
         <v>139</v>
       </c>
@@ -13155,7 +13935,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
         <v>139</v>
       </c>
@@ -13167,7 +13947,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
         <v>139</v>
       </c>
@@ -13179,7 +13959,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
         <v>139</v>
       </c>
@@ -13191,7 +13971,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>139</v>
       </c>
@@ -13203,7 +13983,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
         <v>139</v>
       </c>
@@ -13215,7 +13995,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
         <v>139</v>
       </c>
@@ -13227,7 +14007,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B192" t="s">
         <v>139</v>
       </c>
@@ -13239,7 +14019,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B193" t="s">
         <v>274</v>
       </c>
@@ -13251,7 +14031,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B194" t="s">
         <v>274</v>
       </c>
@@ -13263,7 +14043,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B195" t="s">
         <v>274</v>
       </c>
@@ -13275,7 +14055,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
         <v>274</v>
       </c>
@@ -13287,7 +14067,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
         <v>86</v>
       </c>
@@ -13299,7 +14079,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
         <v>86</v>
       </c>
@@ -13311,7 +14091,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
         <v>86</v>
       </c>
@@ -13323,7 +14103,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
         <v>86</v>
       </c>
@@ -13335,7 +14115,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
         <v>86</v>
       </c>
@@ -13347,7 +14127,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
         <v>86</v>
       </c>
@@ -13359,7 +14139,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B203" t="s">
         <v>86</v>
       </c>
@@ -13371,7 +14151,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B204" t="s">
         <v>86</v>
       </c>
@@ -13383,7 +14163,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B205" t="s">
         <v>86</v>
       </c>
@@ -13395,7 +14175,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B206" t="s">
         <v>86</v>
       </c>
@@ -13407,7 +14187,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>86</v>
       </c>
@@ -13419,7 +14199,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B208" t="s">
         <v>86</v>
       </c>
@@ -13431,7 +14211,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="209" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B209" t="s">
         <v>86</v>
       </c>
@@ -13443,7 +14223,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="210" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B210" t="s">
         <v>274</v>
       </c>
@@ -13455,7 +14235,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="211" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B211" t="s">
         <v>274</v>
       </c>
@@ -13467,7 +14247,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="212" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B212" t="s">
         <v>360</v>
       </c>
@@ -13479,7 +14259,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="213" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B213" t="s">
         <v>231</v>
       </c>
@@ -13491,7 +14271,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="214" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B214" t="s">
         <v>231</v>
       </c>
@@ -13503,7 +14283,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="215" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B215" t="s">
         <v>51</v>
       </c>
@@ -13518,7 +14298,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="216" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B216" t="s">
         <v>86</v>
       </c>
@@ -13530,7 +14310,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="217" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B217" t="s">
         <v>35</v>
       </c>
@@ -13542,7 +14322,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="218" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B218" t="s">
         <v>35</v>
       </c>
@@ -13554,7 +14334,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="219" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B219" t="s">
         <v>35</v>
       </c>
@@ -13566,7 +14346,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="220" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
         <v>35</v>
       </c>
@@ -13578,7 +14358,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="221" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
         <v>35</v>
       </c>
@@ -13590,7 +14370,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="222" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
         <v>35</v>
       </c>
@@ -13602,7 +14382,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="223" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
         <v>35</v>
       </c>
@@ -13614,7 +14394,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="224" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
         <v>35</v>
       </c>
@@ -13626,7 +14406,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="225" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
         <v>35</v>
       </c>
@@ -13638,7 +14418,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="226" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B226" t="s">
         <v>35</v>
       </c>
@@ -13650,7 +14430,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="227" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B227" t="s">
         <v>35</v>
       </c>
@@ -13662,7 +14442,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="228" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
         <v>35</v>
       </c>
@@ -13674,7 +14454,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="229" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
         <v>35</v>
       </c>
@@ -13686,7 +14466,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="230" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
         <v>35</v>
       </c>
@@ -13698,7 +14478,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="231" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
         <v>35</v>
       </c>
@@ -13710,7 +14490,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="232" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
         <v>35</v>
       </c>
@@ -13722,7 +14502,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="233" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
         <v>35</v>
       </c>
@@ -13734,7 +14514,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="234" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B234" t="s">
         <v>35</v>
       </c>
@@ -13746,7 +14526,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="235" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B235" t="s">
         <v>35</v>
       </c>
@@ -13758,7 +14538,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="236" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B236" t="s">
         <v>35</v>
       </c>
@@ -13770,7 +14550,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="237" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
         <v>35</v>
       </c>
@@ -13782,7 +14562,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="238" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B238" t="s">
         <v>35</v>
       </c>
@@ -13794,7 +14574,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="239" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>35</v>
       </c>
@@ -13806,7 +14586,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="240" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
         <v>35</v>
       </c>
@@ -13818,7 +14598,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="241" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
         <v>35</v>
       </c>
@@ -13830,7 +14610,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="242" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
         <v>115</v>
       </c>
@@ -13842,7 +14622,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="243" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B243" t="s">
         <v>80</v>
       </c>
@@ -13854,7 +14634,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="244" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B244" t="s">
         <v>115</v>
       </c>
@@ -13866,7 +14646,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="245" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B245" t="s">
         <v>318</v>
       </c>
@@ -13878,7 +14658,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="246" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B246" t="s">
         <v>180</v>
       </c>
@@ -13890,7 +14670,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="247" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B247" t="s">
         <v>180</v>
       </c>
@@ -13902,7 +14682,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="248" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B248" t="s">
         <v>180</v>
       </c>
@@ -13914,7 +14694,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="249" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B249" t="s">
         <v>180</v>
       </c>
@@ -13926,7 +14706,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="250" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B250" t="s">
         <v>180</v>
       </c>
@@ -13938,7 +14718,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="251" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B251" t="s">
         <v>180</v>
       </c>
@@ -13950,7 +14730,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="252" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B252" t="s">
         <v>318</v>
       </c>
@@ -13962,7 +14742,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="253" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B253" t="s">
         <v>318</v>
       </c>
@@ -13974,7 +14754,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="254" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B254" t="s">
         <v>282</v>
       </c>
@@ -13986,7 +14766,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="255" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B255" t="s">
         <v>218</v>
       </c>
@@ -13998,7 +14778,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="256" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B256" t="s">
         <v>67</v>
       </c>
@@ -14010,7 +14790,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="257" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B257" t="s">
         <v>61</v>
       </c>
@@ -14022,7 +14802,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="258" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B258" t="s">
         <v>264</v>
       </c>
@@ -14034,7 +14814,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="259" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B259" t="s">
         <v>264</v>
       </c>
@@ -14046,7 +14826,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="260" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B260" t="s">
         <v>264</v>
       </c>
@@ -14058,7 +14838,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="261" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B261" t="s">
         <v>264</v>
       </c>
@@ -14070,7 +14850,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="262" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B262" t="s">
         <v>218</v>
       </c>
@@ -14082,7 +14862,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="263" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B263" t="s">
         <v>218</v>
       </c>
@@ -14094,7 +14874,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="264" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B264" t="s">
         <v>260</v>
       </c>
@@ -14106,7 +14886,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="265" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B265" t="s">
         <v>249</v>
       </c>
@@ -14118,7 +14898,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="266" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B266" t="s">
         <v>260</v>
       </c>
@@ -14130,7 +14910,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="267" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B267" t="s">
         <v>249</v>
       </c>
@@ -14142,7 +14922,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="268" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B268" t="s">
         <v>249</v>
       </c>
@@ -14154,7 +14934,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="269" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B269" t="s">
         <v>249</v>
       </c>
@@ -14166,7 +14946,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="270" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B270" t="s">
         <v>249</v>
       </c>
@@ -14178,7 +14958,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="271" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B271" t="s">
         <v>260</v>
       </c>
@@ -14190,7 +14970,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="272" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B272" t="s">
         <v>249</v>
       </c>
@@ -14202,7 +14982,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="273" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B273" t="s">
         <v>360</v>
       </c>
@@ -14214,7 +14994,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="274" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B274" t="s">
         <v>360</v>
       </c>
@@ -14226,7 +15006,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="275" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B275" t="s">
         <v>360</v>
       </c>
@@ -14238,7 +15018,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="276" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B276" t="s">
         <v>360</v>
       </c>
@@ -14250,7 +15030,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="277" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B277" t="s">
         <v>360</v>
       </c>
@@ -14262,7 +15042,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="278" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B278" t="s">
         <v>360</v>
       </c>
@@ -14274,7 +15054,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="279" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B279" t="s">
         <v>360</v>
       </c>
@@ -14286,7 +15066,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="280" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B280" t="s">
         <v>360</v>
       </c>
@@ -14298,7 +15078,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="281" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B281" t="s">
         <v>360</v>
       </c>
@@ -14310,7 +15090,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="282" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B282" t="s">
         <v>360</v>
       </c>
@@ -14322,7 +15102,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="283" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B283" t="s">
         <v>282</v>
       </c>
@@ -14334,7 +15114,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="284" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B284" t="s">
         <v>51</v>
       </c>
@@ -14349,7 +15129,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="285" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B285" t="s">
         <v>51</v>
       </c>
@@ -14364,7 +15144,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="286" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B286" t="s">
         <v>51</v>
       </c>
@@ -14379,7 +15159,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="287" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B287" t="s">
         <v>35</v>
       </c>
@@ -14391,7 +15171,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="288" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B288" t="s">
         <v>35</v>
       </c>
@@ -14403,7 +15183,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="289" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B289" t="s">
         <v>35</v>
       </c>
@@ -14415,7 +15195,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="290" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B290" t="s">
         <v>35</v>
       </c>
@@ -14427,7 +15207,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="291" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
         <v>71</v>
       </c>
@@ -14439,7 +15219,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="292" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B292" t="s">
         <v>249</v>
       </c>
@@ -14451,7 +15231,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="293" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B293" t="s">
         <v>71</v>
       </c>
@@ -14463,7 +15243,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="294" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B294" t="s">
         <v>71</v>
       </c>
@@ -14475,7 +15255,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="295" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B295" t="s">
         <v>71</v>
       </c>
@@ -14487,7 +15267,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="296" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B296" t="s">
         <v>282</v>
       </c>
@@ -14499,7 +15279,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="297" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B297" t="s">
         <v>218</v>
       </c>
@@ -14511,7 +15291,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="298" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B298" t="s">
         <v>61</v>
       </c>
@@ -14523,7 +15303,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="299" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B299" t="s">
         <v>218</v>
       </c>
@@ -14535,7 +15315,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="300" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B300" t="s">
         <v>218</v>
       </c>
@@ -14547,7 +15327,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="301" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B301" t="s">
         <v>218</v>
       </c>
@@ -14559,7 +15339,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="302" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B302" t="s">
         <v>218</v>
       </c>
@@ -14571,7 +15351,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="303" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B303" t="s">
         <v>218</v>
       </c>
@@ -14583,7 +15363,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="304" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B304" t="s">
         <v>218</v>
       </c>
@@ -14595,7 +15375,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="305" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B305" t="s">
         <v>260</v>
       </c>
@@ -14607,7 +15387,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="306" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B306" t="s">
         <v>71</v>
       </c>
@@ -14619,7 +15399,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="307" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B307" t="s">
         <v>282</v>
       </c>
@@ -14631,7 +15411,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="308" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B308" t="s">
         <v>308</v>
       </c>
@@ -14643,7 +15423,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="309" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B309" t="s">
         <v>308</v>
       </c>
@@ -14655,7 +15435,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="310" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B310" t="s">
         <v>67</v>
       </c>
@@ -14667,7 +15447,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="311" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B311" t="s">
         <v>61</v>
       </c>
@@ -14679,7 +15459,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="312" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B312" t="s">
         <v>61</v>
       </c>
@@ -14691,7 +15471,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="313" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B313" t="s">
         <v>218</v>
       </c>
@@ -14703,7 +15483,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="314" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B314" t="s">
         <v>71</v>
       </c>
@@ -14715,7 +15495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="315" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B315" t="s">
         <v>249</v>
       </c>
@@ -14727,7 +15507,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="316" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B316" t="s">
         <v>71</v>
       </c>
@@ -14739,7 +15519,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="317" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B317" t="s">
         <v>71</v>
       </c>
@@ -14751,7 +15531,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="318" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B318" t="s">
         <v>71</v>
       </c>
@@ -14763,7 +15543,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="319" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B319" t="s">
         <v>71</v>
       </c>
@@ -14775,7 +15555,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="320" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B320" t="s">
         <v>195</v>
       </c>
@@ -14787,7 +15567,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B321" t="s">
         <v>195</v>
       </c>
@@ -14799,7 +15579,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="322" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B322" t="s">
         <v>195</v>
       </c>
@@ -14811,7 +15591,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="323" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B323" t="s">
         <v>195</v>
       </c>
@@ -14823,7 +15603,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="324" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B324" t="s">
         <v>195</v>
       </c>
@@ -14835,7 +15615,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="325" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>195</v>
       </c>
@@ -14847,7 +15627,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="326" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B326" t="s">
         <v>195</v>
       </c>
@@ -14859,7 +15639,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="327" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B327" t="s">
         <v>195</v>
       </c>
@@ -14871,7 +15651,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="328" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B328" t="s">
         <v>195</v>
       </c>
@@ -14883,7 +15663,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="329" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B329" t="s">
         <v>195</v>
       </c>
@@ -14895,7 +15675,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="330" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B330" t="s">
         <v>195</v>
       </c>
@@ -14907,7 +15687,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="331" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B331" t="s">
         <v>195</v>
       </c>
@@ -14919,7 +15699,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="332" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B332" t="s">
         <v>195</v>
       </c>
@@ -14931,7 +15711,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="333" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B333" t="s">
         <v>195</v>
       </c>
@@ -14943,7 +15723,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="334" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B334" t="s">
         <v>195</v>
       </c>
@@ -14955,7 +15735,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="335" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B335" t="s">
         <v>195</v>
       </c>
@@ -14967,7 +15747,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="336" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>195</v>
       </c>
@@ -14979,7 +15759,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="337" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B337" t="s">
         <v>195</v>
       </c>
@@ -14991,7 +15771,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="338" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>195</v>
       </c>
@@ -15003,7 +15783,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="339" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B339" t="s">
         <v>195</v>
       </c>
@@ -15015,7 +15795,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="340" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B340" t="s">
         <v>218</v>
       </c>
@@ -15027,7 +15807,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="341" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B341" t="s">
         <v>218</v>
       </c>
@@ -15039,7 +15819,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="342" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B342" t="s">
         <v>308</v>
       </c>
@@ -15051,7 +15831,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="343" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B343" t="s">
         <v>318</v>
       </c>
@@ -15063,7 +15843,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="344" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B344" t="s">
         <v>318</v>
       </c>
@@ -15075,7 +15855,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="345" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B345" t="s">
         <v>318</v>
       </c>
@@ -15087,7 +15867,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="346" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B346" t="s">
         <v>318</v>
       </c>
@@ -15099,7 +15879,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="347" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B347" t="s">
         <v>318</v>
       </c>
@@ -15111,7 +15891,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="348" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B348" t="s">
         <v>360</v>
       </c>
@@ -15123,7 +15903,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="349" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B349" t="s">
         <v>360</v>
       </c>
@@ -15135,7 +15915,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="350" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B350" t="s">
         <v>308</v>
       </c>
@@ -15147,7 +15927,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="351" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B351" t="s">
         <v>318</v>
       </c>
@@ -15159,7 +15939,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="352" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B352" t="s">
         <v>115</v>
       </c>
@@ -15171,7 +15951,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="353" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B353" t="s">
         <v>115</v>
       </c>
@@ -15183,7 +15963,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="354" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>115</v>
       </c>
@@ -15195,7 +15975,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="355" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B355" t="s">
         <v>115</v>
       </c>
@@ -15207,7 +15987,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="356" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>152</v>
       </c>
@@ -15219,7 +15999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="357" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B357" t="s">
         <v>152</v>
       </c>
@@ -15231,7 +16011,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="358" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B358" t="s">
         <v>152</v>
       </c>
@@ -15243,7 +16023,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="359" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B359" t="s">
         <v>152</v>
       </c>
@@ -15255,7 +16035,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="360" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B360" t="s">
         <v>152</v>
       </c>
@@ -15267,7 +16047,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="361" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B361" t="s">
         <v>52</v>
       </c>
@@ -15279,7 +16059,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="362" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B362" t="s">
         <v>52</v>
       </c>
@@ -15291,7 +16071,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="363" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B363" t="s">
         <v>52</v>
       </c>
@@ -15303,7 +16083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="364" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B364" t="s">
         <v>152</v>
       </c>
@@ -15315,7 +16095,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="365" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B365" t="s">
         <v>152</v>
       </c>
@@ -15327,7 +16107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="366" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B366" t="s">
         <v>52</v>
       </c>
@@ -15339,7 +16119,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="367" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B367" t="s">
         <v>152</v>
       </c>
@@ -15351,7 +16131,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="368" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B368" t="s">
         <v>152</v>
       </c>
@@ -15363,7 +16143,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="369" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B369" t="s">
         <v>152</v>
       </c>
@@ -15375,7 +16155,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="370" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B370" t="s">
         <v>52</v>
       </c>
@@ -15387,7 +16167,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="371" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B371" t="s">
         <v>152</v>
       </c>
@@ -15399,7 +16179,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="372" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>152</v>
       </c>
@@ -15411,7 +16191,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="373" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B373" t="s">
         <v>52</v>
       </c>
@@ -15423,7 +16203,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="374" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B374" t="s">
         <v>52</v>
       </c>
@@ -15435,7 +16215,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="375" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B375" t="s">
         <v>52</v>
       </c>
@@ -15447,7 +16227,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="376" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B376" t="s">
         <v>288</v>
       </c>
@@ -15459,7 +16239,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="377" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B377" t="s">
         <v>180</v>
       </c>
@@ -15471,7 +16251,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="378" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B378" t="s">
         <v>180</v>
       </c>
@@ -15483,7 +16263,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="379" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B379" t="s">
         <v>180</v>
       </c>
@@ -15495,7 +16275,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="380" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B380" t="s">
         <v>180</v>
       </c>
@@ -15507,7 +16287,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="381" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B381" t="s">
         <v>274</v>
       </c>
@@ -15519,7 +16299,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="382" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>318</v>
       </c>
@@ -15531,7 +16311,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="383" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B383" t="s">
         <v>318</v>
       </c>
@@ -15543,7 +16323,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="384" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B384" t="s">
         <v>318</v>
       </c>
@@ -15555,7 +16335,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="385" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B385" t="s">
         <v>318</v>
       </c>
@@ -15567,7 +16347,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B386" t="s">
         <v>318</v>
       </c>
@@ -15579,7 +16359,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="387" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B387" t="s">
         <v>308</v>
       </c>
@@ -15591,7 +16371,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="388" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B388" t="s">
         <v>249</v>
       </c>
@@ -15603,7 +16383,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="389" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B389" t="s">
         <v>195</v>
       </c>
@@ -15615,7 +16395,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="390" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B390" t="s">
         <v>274</v>
       </c>
@@ -15627,7 +16407,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="391" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B391" t="s">
         <v>282</v>
       </c>
@@ -15639,7 +16419,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="392" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B392" t="s">
         <v>282</v>
       </c>
@@ -15651,7 +16431,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="393" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B393" t="s">
         <v>288</v>
       </c>
@@ -15663,7 +16443,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B394" t="s">
         <v>288</v>
       </c>
@@ -15675,7 +16455,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="395" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B395" t="s">
         <v>288</v>
       </c>
@@ -15687,7 +16467,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="396" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B396" t="s">
         <v>288</v>
       </c>
@@ -15699,7 +16479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="397" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B397" t="s">
         <v>115</v>
       </c>
@@ -15711,7 +16491,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="398" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B398" t="s">
         <v>80</v>
       </c>
@@ -15723,7 +16503,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="399" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B399" t="s">
         <v>288</v>
       </c>
@@ -15735,7 +16515,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="400" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B400" t="s">
         <v>318</v>
       </c>
@@ -15747,7 +16527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="401" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B401" t="s">
         <v>335</v>
       </c>
@@ -15759,7 +16539,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="402" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B402" t="s">
         <v>288</v>
       </c>
@@ -15771,7 +16551,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="403" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B403" t="s">
         <v>288</v>
       </c>
@@ -15783,7 +16563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="404" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B404" t="s">
         <v>288</v>
       </c>
@@ -15795,7 +16575,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="405" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B405" t="s">
         <v>318</v>
       </c>
@@ -15807,7 +16587,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="406" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B406" t="s">
         <v>115</v>
       </c>
@@ -15819,7 +16599,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="407" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B407" t="s">
         <v>288</v>
       </c>
@@ -15831,7 +16611,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="408" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B408" t="s">
         <v>180</v>
       </c>
@@ -15843,7 +16623,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="409" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B409" t="s">
         <v>80</v>
       </c>
@@ -15855,7 +16635,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="410" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B410" t="s">
         <v>115</v>
       </c>
@@ -15867,7 +16647,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="411" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B411" t="s">
         <v>115</v>
       </c>
@@ -15879,7 +16659,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="412" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B412" t="s">
         <v>115</v>
       </c>
@@ -15891,7 +16671,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="413" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B413" t="s">
         <v>180</v>
       </c>
@@ -15903,7 +16683,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="414" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B414" t="s">
         <v>282</v>
       </c>
@@ -15915,7 +16695,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="415" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B415" t="s">
         <v>318</v>
       </c>
@@ -15927,7 +16707,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="416" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B416" t="s">
         <v>288</v>
       </c>
@@ -15939,7 +16719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="417" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B417" t="s">
         <v>34</v>
       </c>
@@ -15951,7 +16731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B418" t="s">
         <v>67</v>
       </c>
@@ -15963,7 +16743,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="419" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B419" t="s">
         <v>218</v>
       </c>
@@ -15975,7 +16755,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="420" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B420" t="s">
         <v>318</v>
       </c>
@@ -15987,7 +16767,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="421" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B421" t="s">
         <v>34</v>
       </c>
